--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
@@ -1429,7 +1429,7 @@
     <t>Barracas Central</t>
   </si>
   <si>
-    <t>2026-08-07 00:22:25</t>
+    <t>2026-08-07 02:45:46</t>
   </si>
 </sst>
 </file>
@@ -2035,154 +2035,154 @@
         <v>3.15</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
         <v>1.92</v>
       </c>
       <c r="Q2">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W2">
         <v>1.58</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
         <v>48</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP2">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>1.4</v>
+        <v>17.5</v>
       </c>
       <c r="AS2">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT2">
-        <v>1.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX2">
-        <v>1.31</v>
+        <v>14.5</v>
       </c>
       <c r="AY2">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>1.36</v>
+        <v>5</v>
       </c>
       <c r="BB2">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="BC2">
-        <v>1.4</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE2">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF2">
-        <v>1.4</v>
+        <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -2265,10 +2265,10 @@
         <v>324</v>
       </c>
       <c r="F3">
-        <v>1.94</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="H3">
         <v>1.84</v>
@@ -2316,7 +2316,7 @@
         <v>1.9</v>
       </c>
       <c r="W3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2770,10 +2770,10 @@
         <v>1.35</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5">
         <v>1.38</v>
@@ -2788,7 +2788,7 @@
         <v>1.26</v>
       </c>
       <c r="S5">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
         <v>1.94</v>
@@ -2803,10 +2803,10 @@
         <v>2.18</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z5">
         <v>44</v>
@@ -2815,25 +2815,25 @@
         <v>200</v>
       </c>
       <c r="AB5">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE5">
         <v>100</v>
       </c>
       <c r="AF5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI5">
         <v>130</v>
@@ -2842,73 +2842,73 @@
         <v>22</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM5">
         <v>210</v>
       </c>
       <c r="AN5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO5">
         <v>160</v>
       </c>
       <c r="AP5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR5">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="AS5">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AW5">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX5">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AY5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>5.2</v>
+        <v>65</v>
       </c>
       <c r="BB5">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD5">
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BG5">
-        <v>5.3</v>
+        <v>70</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -3490,7 +3490,7 @@
         <v>3.25</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -3723,7 +3723,7 @@
         <v>5.2</v>
       </c>
       <c r="H9">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I9">
         <v>2.22</v>
@@ -3732,7 +3732,7 @@
         <v>3.05</v>
       </c>
       <c r="K9">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3747,7 +3747,7 @@
         <v>1.46</v>
       </c>
       <c r="P9">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q9">
         <v>2.28</v>
@@ -3992,13 +3992,13 @@
         <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R10">
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -4201,22 +4201,22 @@
         <v>332</v>
       </c>
       <c r="F11">
-        <v>2.12</v>
+        <v>1.05</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="H11">
         <v>3.2</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="J11">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -4225,7 +4225,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="O11">
         <v>1.5</v>
@@ -4249,10 +4249,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X11">
         <v>12</v>
@@ -4455,7 +4455,7 @@
         <v>2.02</v>
       </c>
       <c r="J12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
         <v>3.95</v>
@@ -4685,13 +4685,13 @@
         <v>334</v>
       </c>
       <c r="F13">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G13">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H13">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>3.55</v>
@@ -4715,10 +4715,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4927,22 +4927,22 @@
         <v>335</v>
       </c>
       <c r="F14">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H14">
-        <v>3.05</v>
+        <v>1.71</v>
       </c>
       <c r="I14">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J14">
         <v>3.4</v>
       </c>
       <c r="K14">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4957,10 +4957,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q14">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -5662,10 +5662,10 @@
         <v>1.72</v>
       </c>
       <c r="I17">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K17">
         <v>170</v>
@@ -6385,7 +6385,7 @@
         <v>3.45</v>
       </c>
       <c r="H20">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I20">
         <v>2.76</v>
@@ -6412,7 +6412,7 @@
         <v>1.74</v>
       </c>
       <c r="Q20">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         <v>4.6</v>
       </c>
       <c r="G22">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H22">
         <v>1.71</v>
@@ -6884,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -6893,10 +6893,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q22">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6905,10 +6905,10 @@
         <v>0</v>
       </c>
       <c r="T22">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U22">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -7114,10 +7114,10 @@
         <v>5.8</v>
       </c>
       <c r="I23">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J23">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K23">
         <v>4.7</v>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -7135,10 +7135,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q23">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>345</v>
       </c>
       <c r="F24">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="G24">
         <v>2.82</v>
@@ -7362,7 +7362,7 @@
         <v>3.45</v>
       </c>
       <c r="K24">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -8321,7 +8321,7 @@
         <v>3.6</v>
       </c>
       <c r="H28">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I28">
         <v>2.22</v>
@@ -8366,7 +8366,7 @@
         <v>1.81</v>
       </c>
       <c r="W28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X28">
         <v>28</v>
@@ -8384,7 +8384,7 @@
         <v>19.5</v>
       </c>
       <c r="AC28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD28">
         <v>13.5</v>
@@ -8459,22 +8459,22 @@
         <v>19.5</v>
       </c>
       <c r="BB28">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC28">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD28">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE28">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF28">
         <v>19.5</v>
       </c>
       <c r="BG28">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -8557,7 +8557,7 @@
         <v>350</v>
       </c>
       <c r="F29">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G29">
         <v>2.46</v>
@@ -8581,19 +8581,19 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O29">
         <v>1.24</v>
       </c>
       <c r="P29">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q29">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R29">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S29">
         <v>2.78</v>
@@ -8632,7 +8632,7 @@
         <v>15</v>
       </c>
       <c r="AE29">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF29">
         <v>17.5</v>
@@ -8656,13 +8656,13 @@
         <v>34</v>
       </c>
       <c r="AM29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN29">
         <v>16</v>
       </c>
       <c r="AO29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP29">
         <v>15.5</v>
@@ -8674,7 +8674,7 @@
         <v>20</v>
       </c>
       <c r="AS29">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT29">
         <v>10.5</v>
@@ -8686,7 +8686,7 @@
         <v>12</v>
       </c>
       <c r="AW29">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX29">
         <v>14</v>
@@ -8698,19 +8698,19 @@
         <v>13</v>
       </c>
       <c r="BA29">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BB29">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC29">
         <v>19</v>
       </c>
       <c r="BD29">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="BE29">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF29">
         <v>10.5</v>
@@ -8799,13 +8799,13 @@
         <v>351</v>
       </c>
       <c r="F30">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G30">
         <v>2.16</v>
       </c>
       <c r="H30">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I30">
         <v>4.4</v>
@@ -8814,7 +8814,7 @@
         <v>3.45</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8829,10 +8829,10 @@
         <v>0</v>
       </c>
       <c r="P30">
+        <v>1.81</v>
+      </c>
+      <c r="Q30">
         <v>1.92</v>
-      </c>
-      <c r="Q30">
-        <v>1.8</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>1.25</v>
       </c>
       <c r="Q31">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         <v>2.02</v>
       </c>
       <c r="H32">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I32">
         <v>4.4</v>
       </c>
       <c r="J32">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K32">
         <v>4.3</v>
@@ -9313,13 +9313,13 @@
         <v>1.22</v>
       </c>
       <c r="P32">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q32">
         <v>1.65</v>
       </c>
       <c r="R32">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S32">
         <v>2.62</v>
@@ -9328,7 +9328,7 @@
         <v>1.64</v>
       </c>
       <c r="U32">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V32">
         <v>1.29</v>
@@ -9373,10 +9373,10 @@
         <v>65</v>
       </c>
       <c r="AJ32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK32">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL32">
         <v>29</v>
@@ -9385,7 +9385,7 @@
         <v>100</v>
       </c>
       <c r="AN32">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AO32">
         <v>38</v>
@@ -9400,7 +9400,7 @@
         <v>26</v>
       </c>
       <c r="AS32">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="AT32">
         <v>10</v>
@@ -9436,13 +9436,13 @@
         <v>21</v>
       </c>
       <c r="BE32">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF32">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG32">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -9773,7 +9773,7 @@
         <v>1.55</v>
       </c>
       <c r="H34">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I34">
         <v>7.8</v>
@@ -10021,7 +10021,7 @@
         <v>7.4</v>
       </c>
       <c r="J35">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K35">
         <v>5.1</v>
@@ -10254,7 +10254,7 @@
         <v>1.47</v>
       </c>
       <c r="G36">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H36">
         <v>6.6</v>
@@ -10493,7 +10493,7 @@
         <v>358</v>
       </c>
       <c r="F37">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G37">
         <v>1.57</v>
@@ -10523,10 +10523,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q37">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         <v>1.68</v>
       </c>
       <c r="H38">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I38">
         <v>6.6</v>
@@ -10768,7 +10768,7 @@
         <v>2.22</v>
       </c>
       <c r="Q38">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10777,7 +10777,7 @@
         <v>0</v>
       </c>
       <c r="T38">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="U38">
         <v>2.1</v>
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="X38">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y38">
         <v>32</v>
@@ -10816,7 +10816,7 @@
         <v>13</v>
       </c>
       <c r="AG38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH38">
         <v>24</v>
@@ -10849,10 +10849,10 @@
         <v>16.5</v>
       </c>
       <c r="AR38">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS38">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT38">
         <v>7.4</v>
@@ -10864,7 +10864,7 @@
         <v>16.5</v>
       </c>
       <c r="AW38">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX38">
         <v>8</v>
@@ -10876,7 +10876,7 @@
         <v>14.5</v>
       </c>
       <c r="BA38">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB38">
         <v>11.5</v>
@@ -10885,16 +10885,16 @@
         <v>11.5</v>
       </c>
       <c r="BD38">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE38">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF38">
+        <v>6</v>
+      </c>
+      <c r="BG38">
         <v>5.9</v>
-      </c>
-      <c r="BG38">
-        <v>5.6</v>
       </c>
       <c r="BH38">
         <v>0</v>
@@ -10977,7 +10977,7 @@
         <v>360</v>
       </c>
       <c r="F39">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G39">
         <v>1.92</v>
@@ -10992,7 +10992,7 @@
         <v>4.1</v>
       </c>
       <c r="K39">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -11007,10 +11007,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q39">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -11464,7 +11464,7 @@
         <v>6.2</v>
       </c>
       <c r="G41">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H41">
         <v>1.52</v>
@@ -11476,7 +11476,7 @@
         <v>4.8</v>
       </c>
       <c r="K41">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -11703,7 +11703,7 @@
         <v>363</v>
       </c>
       <c r="F42">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G42">
         <v>2.54</v>
@@ -11733,7 +11733,7 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q42">
         <v>1.78</v>
@@ -11948,7 +11948,7 @@
         <v>2.36</v>
       </c>
       <c r="G43">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H43">
         <v>2.86</v>
@@ -11978,7 +11978,7 @@
         <v>2.36</v>
       </c>
       <c r="Q43">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -12053,13 +12053,13 @@
         <v>23</v>
       </c>
       <c r="AP43">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AQ43">
         <v>11.5</v>
       </c>
       <c r="AR43">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AS43">
         <v>32</v>
@@ -12077,10 +12077,10 @@
         <v>20</v>
       </c>
       <c r="AX43">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AY43">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ43">
         <v>11</v>
@@ -12089,10 +12089,10 @@
         <v>25</v>
       </c>
       <c r="BB43">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BC43">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD43">
         <v>3.8</v>
@@ -12435,16 +12435,16 @@
         <v>8.4</v>
       </c>
       <c r="H45">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I45">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="J45">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K45">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -12459,7 +12459,7 @@
         <v>1.16</v>
       </c>
       <c r="P45">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="Q45">
         <v>1.46</v>
@@ -12513,16 +12513,16 @@
         <v>32</v>
       </c>
       <c r="AH45">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI45">
         <v>29</v>
       </c>
       <c r="AJ45">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AK45">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL45">
         <v>90</v>
@@ -12531,13 +12531,13 @@
         <v>110</v>
       </c>
       <c r="AN45">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO45">
         <v>4.8</v>
       </c>
       <c r="AP45">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ45">
         <v>10.5</v>
@@ -12549,7 +12549,7 @@
         <v>11</v>
       </c>
       <c r="AT45">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU45">
         <v>11.5</v>
@@ -12561,31 +12561,31 @@
         <v>11.5</v>
       </c>
       <c r="AX45">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY45">
+        <v>6.8</v>
+      </c>
+      <c r="AZ45">
+        <v>6.2</v>
+      </c>
+      <c r="BA45">
         <v>6.6</v>
       </c>
-      <c r="AZ45">
-        <v>6</v>
-      </c>
-      <c r="BA45">
-        <v>6.4</v>
-      </c>
       <c r="BB45">
+        <v>8.4</v>
+      </c>
+      <c r="BC45">
         <v>8</v>
       </c>
-      <c r="BC45">
+      <c r="BD45">
+        <v>8</v>
+      </c>
+      <c r="BE45">
+        <v>8</v>
+      </c>
+      <c r="BF45">
         <v>7.8</v>
-      </c>
-      <c r="BD45">
-        <v>7.6</v>
-      </c>
-      <c r="BE45">
-        <v>7.6</v>
-      </c>
-      <c r="BF45">
-        <v>7.6</v>
       </c>
       <c r="BG45">
         <v>4</v>
@@ -13412,7 +13412,7 @@
         <v>3.9</v>
       </c>
       <c r="K49">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -14640,7 +14640,7 @@
         <v>1.24</v>
       </c>
       <c r="Q54">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14852,10 +14852,10 @@
         <v>1.68</v>
       </c>
       <c r="G55">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H55">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I55">
         <v>5.6</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q55">
         <v>1.58</v>
@@ -14894,7 +14894,7 @@
         <v>1.7</v>
       </c>
       <c r="U55">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V55">
         <v>0</v>
@@ -14972,7 +14972,7 @@
         <v>7.8</v>
       </c>
       <c r="AU55">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV55">
         <v>6</v>
@@ -15100,7 +15100,7 @@
         <v>14.5</v>
       </c>
       <c r="I56">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="J56">
         <v>6.6</v>
@@ -15121,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q56">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -16543,16 +16543,16 @@
         <v>383</v>
       </c>
       <c r="F62">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G62">
         <v>1.94</v>
       </c>
       <c r="H62">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I62">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J62">
         <v>3.9</v>
@@ -17027,7 +17027,7 @@
         <v>385</v>
       </c>
       <c r="F64">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G64">
         <v>4.2</v>
@@ -17048,19 +17048,19 @@
         <v>1.01</v>
       </c>
       <c r="M64">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N64">
-        <v>4.8</v>
+        <v>2.32</v>
       </c>
       <c r="O64">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P64">
         <v>2.32</v>
       </c>
       <c r="Q64">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R64">
         <v>1.52</v>
@@ -17147,7 +17147,7 @@
         <v>18.5</v>
       </c>
       <c r="AT64">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AU64">
         <v>3.75</v>
@@ -17517,7 +17517,7 @@
         <v>2.24</v>
       </c>
       <c r="H66">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I66">
         <v>3.5</v>
@@ -17544,7 +17544,7 @@
         <v>2.14</v>
       </c>
       <c r="Q66">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="R66">
         <v>0</v>
@@ -17753,7 +17753,7 @@
         <v>388</v>
       </c>
       <c r="F67">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G67">
         <v>1.76</v>
@@ -17762,7 +17762,7 @@
         <v>5.7</v>
       </c>
       <c r="I67">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J67">
         <v>3.95</v>
@@ -17995,61 +17995,61 @@
         <v>389</v>
       </c>
       <c r="F68">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="G68">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H68">
         <v>4.8</v>
       </c>
       <c r="I68">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J68">
+        <v>3.6</v>
+      </c>
+      <c r="K68">
+        <v>3.95</v>
+      </c>
+      <c r="L68">
+        <v>1.01</v>
+      </c>
+      <c r="M68">
+        <v>1.07</v>
+      </c>
+      <c r="N68">
         <v>3.5</v>
-      </c>
-      <c r="K68">
-        <v>4</v>
-      </c>
-      <c r="L68">
-        <v>1.01</v>
-      </c>
-      <c r="M68">
-        <v>1.08</v>
-      </c>
-      <c r="N68">
-        <v>3.35</v>
       </c>
       <c r="O68">
         <v>1.35</v>
       </c>
       <c r="P68">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q68">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R68">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S68">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="T68">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U68">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V68">
         <v>1.22</v>
       </c>
       <c r="W68">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X68">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y68">
         <v>17</v>
@@ -18091,16 +18091,16 @@
         <v>22</v>
       </c>
       <c r="AL68">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM68">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN68">
         <v>16.5</v>
       </c>
       <c r="AO68">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP68">
         <v>11</v>
@@ -18109,10 +18109,10 @@
         <v>14</v>
       </c>
       <c r="AR68">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS68">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT68">
         <v>7</v>
@@ -18124,7 +18124,7 @@
         <v>17.5</v>
       </c>
       <c r="AW68">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX68">
         <v>9.4</v>
@@ -18136,7 +18136,7 @@
         <v>17.5</v>
       </c>
       <c r="BA68">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BB68">
         <v>17</v>
@@ -18145,16 +18145,16 @@
         <v>17.5</v>
       </c>
       <c r="BD68">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE68">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF68">
         <v>10</v>
       </c>
       <c r="BG68">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH68">
         <v>1000</v>
@@ -18237,22 +18237,22 @@
         <v>390</v>
       </c>
       <c r="F69">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G69">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H69">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I69">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J69">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K69">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -18267,10 +18267,10 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q69">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -18491,10 +18491,10 @@
         <v>5.3</v>
       </c>
       <c r="J70">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K70">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -18503,28 +18503,28 @@
         <v>1.07</v>
       </c>
       <c r="N70">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O70">
+        <v>1.33</v>
+      </c>
+      <c r="P70">
+        <v>1.91</v>
+      </c>
+      <c r="Q70">
+        <v>1.94</v>
+      </c>
+      <c r="R70">
         <v>1.34</v>
       </c>
-      <c r="P70">
-        <v>1.81</v>
-      </c>
-      <c r="Q70">
-        <v>2.02</v>
-      </c>
-      <c r="R70">
-        <v>1.32</v>
-      </c>
       <c r="S70">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T70">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U70">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V70">
         <v>1.25</v>
@@ -18578,10 +18578,10 @@
         <v>42</v>
       </c>
       <c r="AM70">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN70">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO70">
         <v>90</v>
@@ -18593,13 +18593,13 @@
         <v>12</v>
       </c>
       <c r="AR70">
+        <v>7</v>
+      </c>
+      <c r="AS70">
+        <v>8</v>
+      </c>
+      <c r="AT70">
         <v>6.8</v>
-      </c>
-      <c r="AS70">
-        <v>7.8</v>
-      </c>
-      <c r="AT70">
-        <v>6.6</v>
       </c>
       <c r="AU70">
         <v>7.2</v>
@@ -18608,7 +18608,7 @@
         <v>14.5</v>
       </c>
       <c r="AW70">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX70">
         <v>8.6</v>
@@ -18632,13 +18632,13 @@
         <v>7</v>
       </c>
       <c r="BE70">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF70">
         <v>11</v>
       </c>
       <c r="BG70">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH70">
         <v>1000</v>
@@ -19456,7 +19456,7 @@
         <v>3.9</v>
       </c>
       <c r="I74">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J74">
         <v>4.4</v>
@@ -19489,7 +19489,7 @@
         <v>0</v>
       </c>
       <c r="T74">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U74">
         <v>2.74</v>
@@ -19692,7 +19692,7 @@
         <v>2.5</v>
       </c>
       <c r="G75">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H75">
         <v>2.92</v>
@@ -19931,19 +19931,19 @@
         <v>397</v>
       </c>
       <c r="F76">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="G76">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H76">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="I76">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="J76">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K76">
         <v>4.4</v>
@@ -20418,16 +20418,16 @@
         <v>2.66</v>
       </c>
       <c r="G78">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H78">
         <v>2.36</v>
       </c>
       <c r="I78">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="J78">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K78">
         <v>5</v>
@@ -20899,22 +20899,22 @@
         <v>401</v>
       </c>
       <c r="F80">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G80">
         <v>3.3</v>
       </c>
       <c r="H80">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I80">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J80">
         <v>4</v>
       </c>
       <c r="K80">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -20929,10 +20929,10 @@
         <v>0</v>
       </c>
       <c r="P80">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q80">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -20941,10 +20941,10 @@
         <v>0</v>
       </c>
       <c r="T80">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U80">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V80">
         <v>0</v>
@@ -20986,10 +20986,10 @@
         <v>17</v>
       </c>
       <c r="AI80">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ80">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK80">
         <v>34</v>
@@ -21001,13 +21001,13 @@
         <v>60</v>
       </c>
       <c r="AN80">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO80">
         <v>12</v>
       </c>
       <c r="AP80">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ80">
         <v>14</v>
@@ -21016,7 +21016,7 @@
         <v>16</v>
       </c>
       <c r="AS80">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT80">
         <v>17</v>
@@ -21031,7 +21031,7 @@
         <v>17.5</v>
       </c>
       <c r="AX80">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY80">
         <v>12.5</v>
@@ -21040,19 +21040,19 @@
         <v>12.5</v>
       </c>
       <c r="BA80">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB80">
+        <v>5</v>
+      </c>
+      <c r="BC80">
+        <v>4.7</v>
+      </c>
+      <c r="BD80">
         <v>4.8</v>
       </c>
-      <c r="BC80">
-        <v>4.5</v>
-      </c>
-      <c r="BD80">
-        <v>4.6</v>
-      </c>
       <c r="BE80">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF80">
         <v>15</v>
@@ -21631,7 +21631,7 @@
         <v>1.83</v>
       </c>
       <c r="H83">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I83">
         <v>8.199999999999999</v>
@@ -21867,22 +21867,22 @@
         <v>405</v>
       </c>
       <c r="F84">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G84">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H84">
         <v>3.15</v>
       </c>
       <c r="I84">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J84">
         <v>4</v>
       </c>
       <c r="K84">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -21897,7 +21897,7 @@
         <v>0</v>
       </c>
       <c r="P84">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q84">
         <v>1.56</v>
@@ -21933,7 +21933,7 @@
         <v>65</v>
       </c>
       <c r="AB84">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC84">
         <v>12</v>
@@ -21942,25 +21942,25 @@
         <v>17</v>
       </c>
       <c r="AE84">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF84">
         <v>20</v>
       </c>
       <c r="AG84">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH84">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI84">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AJ84">
         <v>34</v>
       </c>
       <c r="AK84">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL84">
         <v>34</v>
@@ -21972,7 +21972,7 @@
         <v>10.5</v>
       </c>
       <c r="AO84">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP84">
         <v>16</v>
@@ -21996,7 +21996,7 @@
         <v>11</v>
       </c>
       <c r="AW84">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX84">
         <v>12.5</v>
@@ -22112,7 +22112,7 @@
         <v>5.1</v>
       </c>
       <c r="G85">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="H85">
         <v>1.51</v>
@@ -22142,7 +22142,7 @@
         <v>3.7</v>
       </c>
       <c r="Q85">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         <v>0</v>
       </c>
       <c r="T85">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U85">
         <v>2.8</v>
@@ -22268,7 +22268,7 @@
         <v>3.9</v>
       </c>
       <c r="BG85">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BH85">
         <v>0</v>
@@ -22363,7 +22363,7 @@
         <v>7.4</v>
       </c>
       <c r="J86">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K86">
         <v>6.6</v>
@@ -22384,7 +22384,7 @@
         <v>3.65</v>
       </c>
       <c r="Q86">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -22510,7 +22510,7 @@
         <v>3.1</v>
       </c>
       <c r="BG86">
-        <v>27</v>
+        <v>4.1</v>
       </c>
       <c r="BH86">
         <v>0</v>
@@ -23083,7 +23083,7 @@
         <v>1.63</v>
       </c>
       <c r="H89">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I89">
         <v>6.6</v>
@@ -23107,10 +23107,10 @@
         <v>1.19</v>
       </c>
       <c r="P89">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q89">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R89">
         <v>1.58</v>
@@ -23122,7 +23122,7 @@
         <v>1.67</v>
       </c>
       <c r="U89">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
         <v>0</v>
@@ -23322,7 +23322,7 @@
         <v>2.56</v>
       </c>
       <c r="G90">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="H90">
         <v>2.4</v>
@@ -23421,13 +23421,13 @@
         <v>55</v>
       </c>
       <c r="AN90">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO90">
         <v>12.5</v>
       </c>
       <c r="AP90">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ90">
         <v>3.7</v>
@@ -23436,7 +23436,7 @@
         <v>20</v>
       </c>
       <c r="AS90">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT90">
         <v>18.5</v>
@@ -23448,7 +23448,7 @@
         <v>11.5</v>
       </c>
       <c r="AW90">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AX90">
         <v>3.8</v>
@@ -23463,7 +23463,7 @@
         <v>3.8</v>
       </c>
       <c r="BB90">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC90">
         <v>20</v>
@@ -24045,7 +24045,7 @@
         <v>414</v>
       </c>
       <c r="F93">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G93">
         <v>1.37</v>
@@ -24084,7 +24084,7 @@
         <v>1.63</v>
       </c>
       <c r="S93">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="T93">
         <v>1.01</v>
@@ -24290,10 +24290,10 @@
         <v>2.28</v>
       </c>
       <c r="G94">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H94">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I94">
         <v>4</v>
@@ -24302,7 +24302,7 @@
         <v>3.15</v>
       </c>
       <c r="K94">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -24529,7 +24529,7 @@
         <v>416</v>
       </c>
       <c r="F95">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="G95">
         <v>1.8</v>
@@ -24774,13 +24774,13 @@
         <v>3</v>
       </c>
       <c r="G96">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H96">
         <v>2.44</v>
       </c>
       <c r="I96">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J96">
         <v>3.2</v>
@@ -25022,7 +25022,7 @@
         <v>3.45</v>
       </c>
       <c r="I97">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J97">
         <v>3.85</v>
@@ -25739,16 +25739,16 @@
         <v>421</v>
       </c>
       <c r="F100">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G100">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H100">
         <v>2.64</v>
       </c>
       <c r="I100">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J100">
         <v>3.05</v>
@@ -25787,10 +25787,10 @@
         <v>1.01</v>
       </c>
       <c r="V100">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W100">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X100">
         <v>1000</v>
@@ -26226,7 +26226,7 @@
         <v>1.51</v>
       </c>
       <c r="G102">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H102">
         <v>4.9</v>
@@ -26259,7 +26259,7 @@
         <v>1.56</v>
       </c>
       <c r="R102">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S102">
         <v>2.3</v>
@@ -26274,7 +26274,7 @@
         <v>1.13</v>
       </c>
       <c r="W102">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X102">
         <v>1000</v>
@@ -26740,7 +26740,7 @@
         <v>1.84</v>
       </c>
       <c r="Q104">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -27433,10 +27433,10 @@
         <v>428</v>
       </c>
       <c r="F107">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G107">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H107">
         <v>2.24</v>
@@ -27466,7 +27466,7 @@
         <v>2.14</v>
       </c>
       <c r="Q107">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R107">
         <v>1.44</v>
@@ -27484,7 +27484,7 @@
         <v>1.74</v>
       </c>
       <c r="W107">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X107">
         <v>22</v>
@@ -27502,7 +27502,7 @@
         <v>18</v>
       </c>
       <c r="AC107">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD107">
         <v>14</v>
@@ -27511,19 +27511,19 @@
         <v>28</v>
       </c>
       <c r="AF107">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG107">
         <v>17</v>
       </c>
       <c r="AH107">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI107">
         <v>40</v>
       </c>
       <c r="AJ107">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK107">
         <v>42</v>
@@ -27535,7 +27535,7 @@
         <v>90</v>
       </c>
       <c r="AN107">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO107">
         <v>17.5</v>
@@ -27550,7 +27550,7 @@
         <v>13.5</v>
       </c>
       <c r="AS107">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT107">
         <v>12.5</v>
@@ -27574,19 +27574,19 @@
         <v>13.5</v>
       </c>
       <c r="BA107">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BB107">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC107">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BD107">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE107">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF107">
         <v>20</v>
@@ -27675,7 +27675,7 @@
         <v>429</v>
       </c>
       <c r="F108">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G108">
         <v>3.95</v>
@@ -27684,10 +27684,10 @@
         <v>2.18</v>
       </c>
       <c r="I108">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J108">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K108">
         <v>3.6</v>
@@ -27696,25 +27696,25 @@
         <v>1.01</v>
       </c>
       <c r="M108">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N108">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O108">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P108">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q108">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R108">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S108">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="T108">
         <v>1.01</v>
@@ -28646,7 +28646,7 @@
         <v>2.5</v>
       </c>
       <c r="G112">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H112">
         <v>2.74</v>
@@ -28655,7 +28655,7 @@
         <v>3.15</v>
       </c>
       <c r="J112">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K112">
         <v>3.75</v>
@@ -29127,22 +29127,22 @@
         <v>435</v>
       </c>
       <c r="F114">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G114">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H114">
         <v>4.8</v>
       </c>
       <c r="I114">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J114">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K114">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -29853,16 +29853,16 @@
         <v>438</v>
       </c>
       <c r="F117">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G117">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="H117">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I117">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J117">
         <v>3.7</v>
@@ -30101,7 +30101,7 @@
         <v>5.5</v>
       </c>
       <c r="H118">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="I118">
         <v>1.74</v>
@@ -30161,7 +30161,7 @@
         <v>21</v>
       </c>
       <c r="AB118">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC118">
         <v>12</v>
@@ -30203,25 +30203,25 @@
         <v>7.6</v>
       </c>
       <c r="AP118">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ118">
         <v>4.3</v>
       </c>
       <c r="AR118">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS118">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT118">
         <v>20</v>
       </c>
       <c r="AU118">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV118">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW118">
         <v>4.6</v>
@@ -30233,7 +30233,7 @@
         <v>17</v>
       </c>
       <c r="AZ118">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA118">
         <v>5.1</v>
@@ -31066,19 +31066,19 @@
         <v>2.24</v>
       </c>
       <c r="G122">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H122">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I122">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J122">
         <v>3.05</v>
       </c>
       <c r="K122">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -31093,10 +31093,10 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q122">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -32303,7 +32303,7 @@
         <v>0</v>
       </c>
       <c r="P127">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q127">
         <v>1.86</v>
@@ -32515,22 +32515,22 @@
         <v>449</v>
       </c>
       <c r="F128">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G128">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="H128">
         <v>3.05</v>
       </c>
       <c r="I128">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J128">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="K128">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L128">
         <v>0</v>
@@ -32548,7 +32548,7 @@
         <v>1.74</v>
       </c>
       <c r="Q128">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -33002,7 +33002,7 @@
         <v>1.63</v>
       </c>
       <c r="G130">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H130">
         <v>5</v>
@@ -33032,7 +33032,7 @@
         <v>1.66</v>
       </c>
       <c r="Q130">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R130">
         <v>1.18</v>
@@ -33050,7 +33050,7 @@
         <v>1.15</v>
       </c>
       <c r="W130">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X130">
         <v>1000</v>
@@ -33731,16 +33731,16 @@
         <v>2.08</v>
       </c>
       <c r="H133">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I133">
         <v>4.2</v>
       </c>
       <c r="J133">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K133">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -33758,7 +33758,7 @@
         <v>1.95</v>
       </c>
       <c r="Q133">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -33967,13 +33967,13 @@
         <v>455</v>
       </c>
       <c r="F134">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G134">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H134">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="I134">
         <v>4.8</v>
@@ -34696,16 +34696,16 @@
         <v>2.02</v>
       </c>
       <c r="G137">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H137">
         <v>1.92</v>
       </c>
       <c r="I137">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J137">
-        <v>3.75</v>
+        <v>1.32</v>
       </c>
       <c r="K137">
         <v>190</v>
@@ -34935,7 +34935,7 @@
         <v>459</v>
       </c>
       <c r="F138">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G138">
         <v>1.64</v>
@@ -34944,7 +34944,7 @@
         <v>6.8</v>
       </c>
       <c r="I138">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J138">
         <v>3.95</v>
@@ -34968,7 +34968,7 @@
         <v>1.86</v>
       </c>
       <c r="Q138">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R138">
         <v>0</v>
@@ -36393,7 +36393,7 @@
         <v>2.08</v>
       </c>
       <c r="H144">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I144">
         <v>4.6</v>
@@ -36638,7 +36638,7 @@
         <v>25</v>
       </c>
       <c r="I145">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J145">
         <v>9.800000000000001</v>
@@ -36659,7 +36659,7 @@
         <v>0</v>
       </c>
       <c r="P145">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q145">
         <v>1.43</v>
@@ -36686,7 +36686,7 @@
         <v>38</v>
       </c>
       <c r="Y145">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Z145">
         <v>360</v>
@@ -36755,7 +36755,7 @@
         <v>20</v>
       </c>
       <c r="AV145">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW145">
         <v>9.199999999999999</v>
@@ -36767,7 +36767,7 @@
         <v>13</v>
       </c>
       <c r="AZ145">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA145">
         <v>9</v>
@@ -36779,13 +36779,13 @@
         <v>13.5</v>
       </c>
       <c r="BD145">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE145">
         <v>9</v>
       </c>
       <c r="BF145">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BG145">
         <v>9.199999999999999</v>
@@ -36877,7 +36877,7 @@
         <v>6</v>
       </c>
       <c r="H146">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I146">
         <v>1.78</v>
@@ -37355,19 +37355,19 @@
         <v>469</v>
       </c>
       <c r="F148">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="G148">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H148">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I148">
         <v>4.1</v>
       </c>
       <c r="J148">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K148">
         <v>3.25</v>
@@ -37597,19 +37597,19 @@
         <v>470</v>
       </c>
       <c r="F149">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G149">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H149">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I149">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J149">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K149">
         <v>3.55</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
@@ -1429,7 +1429,7 @@
     <t>Barracas Central</t>
   </si>
   <si>
-    <t>2026-08-07 02:45:46</t>
+    <t>2026-08-07 05:09:07</t>
   </si>
 </sst>
 </file>
@@ -2023,13 +2023,13 @@
         <v>323</v>
       </c>
       <c r="F2">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G2">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H2">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>3.15</v>
@@ -2047,37 +2047,37 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
         <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
         <v>1.47</v>
       </c>
       <c r="W2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
@@ -2092,7 +2092,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2">
         <v>16</v>
@@ -2101,10 +2101,10 @@
         <v>42</v>
       </c>
       <c r="AF2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH2">
         <v>17.5</v>
@@ -2113,7 +2113,7 @@
         <v>48</v>
       </c>
       <c r="AJ2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK2">
         <v>36</v>
@@ -2125,7 +2125,7 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO2">
         <v>38</v>
@@ -2140,10 +2140,10 @@
         <v>17.5</v>
       </c>
       <c r="AS2">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -2152,7 +2152,7 @@
         <v>11.5</v>
       </c>
       <c r="AW2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX2">
         <v>14.5</v>
@@ -2164,25 +2164,25 @@
         <v>14</v>
       </c>
       <c r="BA2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC2">
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE2">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
         <v>17.5</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -2191,7 +2191,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
@@ -2203,43 +2203,43 @@
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -2316,7 +2316,7 @@
         <v>1.9</v>
       </c>
       <c r="W3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2749,7 +2749,7 @@
         <v>326</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G5">
         <v>1.84</v>
@@ -2767,37 +2767,37 @@
         <v>3.8</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U5">
         <v>1.85</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
         <v>2.18</v>
@@ -2806,7 +2806,7 @@
         <v>12</v>
       </c>
       <c r="Y5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z5">
         <v>44</v>
@@ -2842,10 +2842,10 @@
         <v>22</v>
       </c>
       <c r="AK5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM5">
         <v>210</v>
@@ -2863,10 +2863,10 @@
         <v>14</v>
       </c>
       <c r="AR5">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="AS5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
         <v>6.4</v>
@@ -2878,22 +2878,22 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA5">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="BB5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC5">
         <v>18</v>
@@ -2902,13 +2902,13 @@
         <v>34</v>
       </c>
       <c r="BE5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2991,19 +2991,19 @@
         <v>327</v>
       </c>
       <c r="F6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G6">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H6">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I6">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
         <v>950</v>
@@ -3027,10 +3027,10 @@
         <v>1.56</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -3042,7 +3042,7 @@
         <v>1.06</v>
       </c>
       <c r="W6">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -3236,19 +3236,19 @@
         <v>1.66</v>
       </c>
       <c r="G7">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="H7">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>2.36</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3478,13 +3478,13 @@
         <v>1.73</v>
       </c>
       <c r="G8">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H8">
         <v>5.9</v>
       </c>
       <c r="I8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>3.25</v>
@@ -3505,10 +3505,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q8">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -3717,13 +3717,13 @@
         <v>330</v>
       </c>
       <c r="F9">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="G9">
         <v>5.2</v>
       </c>
       <c r="H9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I9">
         <v>2.22</v>
@@ -3732,7 +3732,7 @@
         <v>3.05</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3962,13 +3962,13 @@
         <v>1.02</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H10">
         <v>1.02</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J10">
         <v>1.02</v>
@@ -4201,166 +4201,166 @@
         <v>332</v>
       </c>
       <c r="F11">
-        <v>1.05</v>
+        <v>2.44</v>
       </c>
       <c r="G11">
         <v>2.72</v>
       </c>
       <c r="H11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I11">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="J11">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="P11">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Q11">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W11">
         <v>1.58</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="AR11">
-        <v>1.09</v>
+        <v>19</v>
       </c>
       <c r="AS11">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="AT11">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="AU11">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="AV11">
-        <v>1.09</v>
+        <v>13</v>
       </c>
       <c r="AW11">
-        <v>1.09</v>
+        <v>7.4</v>
       </c>
       <c r="AX11">
-        <v>1.09</v>
+        <v>12.5</v>
       </c>
       <c r="AY11">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>1.09</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>1.09</v>
+        <v>7.8</v>
       </c>
       <c r="BB11">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="BC11">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="BD11">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="BE11">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="BG11">
-        <v>1.09</v>
+        <v>7.6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -4455,7 +4455,7 @@
         <v>2.02</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12">
         <v>3.95</v>
@@ -4685,7 +4685,7 @@
         <v>334</v>
       </c>
       <c r="F13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G13">
         <v>2.4</v>
@@ -4718,7 +4718,7 @@
         <v>2.08</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4957,10 +4957,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -5411,19 +5411,19 @@
         <v>337</v>
       </c>
       <c r="F16">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="G16">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="H16">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="I16">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J16">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="K16">
         <v>3.45</v>
@@ -5441,10 +5441,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q16">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -5907,7 +5907,7 @@
         <v>1000</v>
       </c>
       <c r="J18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K18">
         <v>950</v>
@@ -6385,10 +6385,10 @@
         <v>3.45</v>
       </c>
       <c r="H20">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I20">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J20">
         <v>3.2</v>
@@ -6409,10 +6409,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q20">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6621,22 +6621,22 @@
         <v>342</v>
       </c>
       <c r="F21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G21">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H21">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I21">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J21">
         <v>3.65</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -6872,19 +6872,19 @@
         <v>1.71</v>
       </c>
       <c r="I22">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="J22">
         <v>4.2</v>
       </c>
       <c r="K22">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -7111,13 +7111,13 @@
         <v>1.7</v>
       </c>
       <c r="H23">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J23">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K23">
         <v>4.7</v>
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>2.18</v>
       </c>
       <c r="Q23">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -7347,13 +7347,13 @@
         <v>345</v>
       </c>
       <c r="F24">
-        <v>1.45</v>
+        <v>2.42</v>
       </c>
       <c r="G24">
         <v>2.82</v>
       </c>
       <c r="H24">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I24">
         <v>3.3</v>
@@ -7362,7 +7362,7 @@
         <v>3.45</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>1000</v>
       </c>
       <c r="J26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K26">
         <v>950</v>
@@ -8085,7 +8085,7 @@
         <v>1000</v>
       </c>
       <c r="J27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -8345,7 +8345,7 @@
         <v>1.2</v>
       </c>
       <c r="P28">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q28">
         <v>1.59</v>
@@ -8557,7 +8557,7 @@
         <v>350</v>
       </c>
       <c r="F29">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G29">
         <v>2.46</v>
@@ -8566,7 +8566,7 @@
         <v>3.05</v>
       </c>
       <c r="I29">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J29">
         <v>3.6</v>
@@ -8581,19 +8581,19 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O29">
         <v>1.24</v>
       </c>
       <c r="P29">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q29">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R29">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S29">
         <v>2.78</v>
@@ -8602,10 +8602,10 @@
         <v>1.62</v>
       </c>
       <c r="U29">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
         <v>1.68</v>
@@ -8665,7 +8665,7 @@
         <v>26</v>
       </c>
       <c r="AP29">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ29">
         <v>13</v>
@@ -8832,7 +8832,7 @@
         <v>1.81</v>
       </c>
       <c r="Q30">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -9044,7 +9044,7 @@
         <v>2.16</v>
       </c>
       <c r="G31">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="H31">
         <v>1.7</v>
@@ -9053,7 +9053,7 @@
         <v>1.89</v>
       </c>
       <c r="J31">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="K31">
         <v>320</v>
@@ -9286,7 +9286,7 @@
         <v>1.87</v>
       </c>
       <c r="G32">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H32">
         <v>4</v>
@@ -9295,7 +9295,7 @@
         <v>4.4</v>
       </c>
       <c r="J32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K32">
         <v>4.3</v>
@@ -9307,19 +9307,19 @@
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O32">
         <v>1.22</v>
       </c>
       <c r="P32">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q32">
         <v>1.65</v>
       </c>
       <c r="R32">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S32">
         <v>2.62</v>
@@ -9334,7 +9334,7 @@
         <v>1.29</v>
       </c>
       <c r="W32">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X32">
         <v>21</v>
@@ -9385,7 +9385,7 @@
         <v>100</v>
       </c>
       <c r="AN32">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AO32">
         <v>38</v>
@@ -9400,7 +9400,7 @@
         <v>26</v>
       </c>
       <c r="AS32">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AT32">
         <v>10</v>
@@ -9436,10 +9436,10 @@
         <v>21</v>
       </c>
       <c r="BE32">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF32">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BG32">
         <v>29</v>
@@ -9528,7 +9528,7 @@
         <v>3.35</v>
       </c>
       <c r="G33">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H33">
         <v>2.1</v>
@@ -9770,7 +9770,7 @@
         <v>1.49</v>
       </c>
       <c r="G34">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H34">
         <v>7.4</v>
@@ -9779,7 +9779,7 @@
         <v>7.8</v>
       </c>
       <c r="J34">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K34">
         <v>5</v>
@@ -9797,7 +9797,7 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q34">
         <v>1.68</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q35">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -10284,7 +10284,7 @@
         <v>2.38</v>
       </c>
       <c r="Q36">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>1.57</v>
       </c>
       <c r="H37">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I37">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J37">
         <v>5</v>
@@ -10523,10 +10523,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>359</v>
       </c>
       <c r="F38">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="G38">
         <v>1.68</v>
@@ -10750,7 +10750,7 @@
         <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -11219,10 +11219,10 @@
         <v>361</v>
       </c>
       <c r="F40">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G40">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H40">
         <v>3.3</v>
@@ -11231,10 +11231,10 @@
         <v>3.8</v>
       </c>
       <c r="J40">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K40">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -11467,13 +11467,13 @@
         <v>7.2</v>
       </c>
       <c r="H41">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="I41">
         <v>1.56</v>
       </c>
       <c r="J41">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K41">
         <v>5.5</v>
@@ -11703,7 +11703,7 @@
         <v>363</v>
       </c>
       <c r="F42">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G42">
         <v>2.54</v>
@@ -11712,10 +11712,10 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J42">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K42">
         <v>3.8</v>
@@ -11948,7 +11948,7 @@
         <v>2.36</v>
       </c>
       <c r="G43">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H43">
         <v>2.86</v>
@@ -11957,7 +11957,7 @@
         <v>3.1</v>
       </c>
       <c r="J43">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K43">
         <v>4.1</v>
@@ -11966,7 +11966,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -11978,7 +11978,7 @@
         <v>2.36</v>
       </c>
       <c r="Q43">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -12023,7 +12023,7 @@
         <v>36</v>
       </c>
       <c r="AF43">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG43">
         <v>15</v>
@@ -12050,7 +12050,7 @@
         <v>17</v>
       </c>
       <c r="AO43">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP43">
         <v>16</v>
@@ -12059,7 +12059,7 @@
         <v>11.5</v>
       </c>
       <c r="AR43">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS43">
         <v>32</v>
@@ -12074,7 +12074,7 @@
         <v>10</v>
       </c>
       <c r="AW43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX43">
         <v>16</v>
@@ -12086,7 +12086,7 @@
         <v>11</v>
       </c>
       <c r="BA43">
-        <v>25</v>
+        <v>3.85</v>
       </c>
       <c r="BB43">
         <v>3.85</v>
@@ -12104,7 +12104,7 @@
         <v>10</v>
       </c>
       <c r="BG43">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH43">
         <v>0</v>
@@ -12187,16 +12187,16 @@
         <v>365</v>
       </c>
       <c r="F44">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G44">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H44">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I44">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J44">
         <v>3.8</v>
@@ -12429,28 +12429,28 @@
         <v>366</v>
       </c>
       <c r="F45">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G45">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H45">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="I45">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J45">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K45">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N45">
         <v>6.2</v>
@@ -12462,13 +12462,13 @@
         <v>2.82</v>
       </c>
       <c r="Q45">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R45">
         <v>1.75</v>
       </c>
       <c r="S45">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T45">
         <v>1.71</v>
@@ -12507,10 +12507,10 @@
         <v>14.5</v>
       </c>
       <c r="AF45">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG45">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH45">
         <v>22</v>
@@ -12519,7 +12519,7 @@
         <v>29</v>
       </c>
       <c r="AJ45">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AK45">
         <v>110</v>
@@ -12534,10 +12534,10 @@
         <v>90</v>
       </c>
       <c r="AO45">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AP45">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ45">
         <v>10.5</v>
@@ -12549,7 +12549,7 @@
         <v>11</v>
       </c>
       <c r="AT45">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU45">
         <v>11.5</v>
@@ -12561,31 +12561,31 @@
         <v>11.5</v>
       </c>
       <c r="AX45">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY45">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ45">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA45">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB45">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC45">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BD45">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BE45">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF45">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG45">
         <v>4</v>
@@ -12674,7 +12674,7 @@
         <v>1.01</v>
       </c>
       <c r="G46">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="H46">
         <v>1.19</v>
@@ -12683,7 +12683,7 @@
         <v>1000</v>
       </c>
       <c r="J46">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="K46">
         <v>320</v>
@@ -12925,7 +12925,7 @@
         <v>1000</v>
       </c>
       <c r="J47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -13161,13 +13161,13 @@
         <v>1000</v>
       </c>
       <c r="H48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I48">
         <v>3.55</v>
       </c>
       <c r="J48">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K48">
         <v>140</v>
@@ -13397,19 +13397,19 @@
         <v>370</v>
       </c>
       <c r="F49">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G49">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="H49">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I49">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J49">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K49">
         <v>4.5</v>
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q49">
         <v>1.62</v>
@@ -13651,7 +13651,7 @@
         <v>1000</v>
       </c>
       <c r="J50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K50">
         <v>950</v>
@@ -14637,7 +14637,7 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q54">
         <v>2.12</v>
@@ -14879,10 +14879,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q55">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14957,7 +14957,7 @@
         <v>70</v>
       </c>
       <c r="AP55">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AQ55">
         <v>15</v>
@@ -14972,7 +14972,7 @@
         <v>7.8</v>
       </c>
       <c r="AU55">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV55">
         <v>6</v>
@@ -14999,7 +14999,7 @@
         <v>12.5</v>
       </c>
       <c r="BD55">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BE55">
         <v>7.8</v>
@@ -15333,7 +15333,7 @@
         <v>378</v>
       </c>
       <c r="F57">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G57">
         <v>11.5</v>
@@ -15587,7 +15587,7 @@
         <v>1000</v>
       </c>
       <c r="J58">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K58">
         <v>950</v>
@@ -15614,7 +15614,7 @@
         <v>1.15</v>
       </c>
       <c r="S58">
-        <v>1.31</v>
+        <v>2.44</v>
       </c>
       <c r="T58">
         <v>1.01</v>
@@ -15829,7 +15829,7 @@
         <v>1000</v>
       </c>
       <c r="J59">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K59">
         <v>950</v>
@@ -16071,7 +16071,7 @@
         <v>1000</v>
       </c>
       <c r="J60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K60">
         <v>950</v>
@@ -16307,13 +16307,13 @@
         <v>1.75</v>
       </c>
       <c r="H61">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I61">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J61">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K61">
         <v>4.6</v>
@@ -16331,7 +16331,7 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q61">
         <v>1.76</v>
@@ -16552,7 +16552,7 @@
         <v>4.1</v>
       </c>
       <c r="I62">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J62">
         <v>3.9</v>
@@ -16785,7 +16785,7 @@
         <v>384</v>
       </c>
       <c r="F63">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G63">
         <v>11.5</v>
@@ -17027,37 +17027,37 @@
         <v>385</v>
       </c>
       <c r="F64">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="G64">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H64">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I64">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J64">
         <v>3.95</v>
       </c>
       <c r="K64">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L64">
         <v>1.01</v>
       </c>
       <c r="M64">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N64">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="O64">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P64">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q64">
         <v>1.63</v>
@@ -17072,13 +17072,13 @@
         <v>1.62</v>
       </c>
       <c r="U64">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V64">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W64">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X64">
         <v>25</v>
@@ -17093,7 +17093,7 @@
         <v>25</v>
       </c>
       <c r="AB64">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC64">
         <v>11</v>
@@ -17108,7 +17108,7 @@
         <v>36</v>
       </c>
       <c r="AG64">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH64">
         <v>19</v>
@@ -17117,40 +17117,40 @@
         <v>34</v>
       </c>
       <c r="AJ64">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK64">
+        <v>46</v>
+      </c>
+      <c r="AL64">
         <v>48</v>
       </c>
-      <c r="AL64">
-        <v>50</v>
-      </c>
       <c r="AM64">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN64">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO64">
         <v>11</v>
       </c>
       <c r="AP64">
-        <v>4.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ64">
         <v>10</v>
       </c>
       <c r="AR64">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS64">
         <v>18.5</v>
       </c>
       <c r="AT64">
-        <v>16</v>
+        <v>4.6</v>
       </c>
       <c r="AU64">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AV64">
         <v>8.4</v>
@@ -17159,34 +17159,34 @@
         <v>15.5</v>
       </c>
       <c r="AX64">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AY64">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AZ64">
         <v>14</v>
       </c>
       <c r="BA64">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB64">
+        <v>5.5</v>
+      </c>
+      <c r="BC64">
+        <v>5.2</v>
+      </c>
+      <c r="BD64">
         <v>5.3</v>
       </c>
-      <c r="BC64">
+      <c r="BE64">
+        <v>5.5</v>
+      </c>
+      <c r="BF64">
         <v>5.1</v>
       </c>
-      <c r="BD64">
-        <v>5.1</v>
-      </c>
-      <c r="BE64">
-        <v>5.3</v>
-      </c>
-      <c r="BF64">
-        <v>4.9</v>
-      </c>
       <c r="BG64">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="BH64">
         <v>1000</v>
@@ -17517,7 +17517,7 @@
         <v>2.24</v>
       </c>
       <c r="H66">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I66">
         <v>3.5</v>
@@ -17544,7 +17544,7 @@
         <v>2.14</v>
       </c>
       <c r="Q66">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="R66">
         <v>0</v>
@@ -17753,19 +17753,19 @@
         <v>388</v>
       </c>
       <c r="F67">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="G67">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H67">
         <v>5.7</v>
       </c>
       <c r="I67">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J67">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K67">
         <v>4.1</v>
@@ -17783,7 +17783,7 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q67">
         <v>1.99</v>
@@ -17995,22 +17995,22 @@
         <v>389</v>
       </c>
       <c r="F68">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="G68">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I68">
-        <v>5.4</v>
+        <v>110</v>
       </c>
       <c r="J68">
-        <v>3.6</v>
+        <v>1.22</v>
       </c>
       <c r="K68">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -18025,49 +18025,49 @@
         <v>1.35</v>
       </c>
       <c r="P68">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q68">
+        <v>1.35</v>
+      </c>
+      <c r="R68">
+        <v>1.24</v>
+      </c>
+      <c r="S68">
+        <v>1.01</v>
+      </c>
+      <c r="T68">
+        <v>1.01</v>
+      </c>
+      <c r="U68">
+        <v>1.01</v>
+      </c>
+      <c r="V68">
+        <v>1.2</v>
+      </c>
+      <c r="W68">
         <v>2</v>
-      </c>
-      <c r="R68">
-        <v>1.33</v>
-      </c>
-      <c r="S68">
-        <v>3.4</v>
-      </c>
-      <c r="T68">
-        <v>1.88</v>
-      </c>
-      <c r="U68">
-        <v>1.98</v>
-      </c>
-      <c r="V68">
-        <v>1.22</v>
-      </c>
-      <c r="W68">
-        <v>2.08</v>
       </c>
       <c r="X68">
         <v>16.5</v>
       </c>
       <c r="Y68">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z68">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA68">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB68">
         <v>8.4</v>
       </c>
       <c r="AC68">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD68">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE68">
         <v>80</v>
@@ -18079,7 +18079,7 @@
         <v>10.5</v>
       </c>
       <c r="AH68">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI68">
         <v>80</v>
@@ -18088,7 +18088,7 @@
         <v>21</v>
       </c>
       <c r="AK68">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL68">
         <v>40</v>
@@ -18109,13 +18109,13 @@
         <v>14</v>
       </c>
       <c r="AR68">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS68">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT68">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU68">
         <v>7.2</v>
@@ -18124,10 +18124,10 @@
         <v>17.5</v>
       </c>
       <c r="AW68">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX68">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY68">
         <v>8.800000000000001</v>
@@ -18136,7 +18136,7 @@
         <v>17.5</v>
       </c>
       <c r="BA68">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB68">
         <v>17</v>
@@ -18145,16 +18145,16 @@
         <v>17.5</v>
       </c>
       <c r="BD68">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BE68">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF68">
         <v>10</v>
       </c>
       <c r="BG68">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH68">
         <v>1000</v>
@@ -18240,10 +18240,10 @@
         <v>3.15</v>
       </c>
       <c r="G69">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H69">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I69">
         <v>2.38</v>
@@ -18479,22 +18479,22 @@
         <v>391</v>
       </c>
       <c r="F70">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="G70">
         <v>1.91</v>
       </c>
       <c r="H70">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I70">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J70">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K70">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -18506,13 +18506,13 @@
         <v>3.6</v>
       </c>
       <c r="O70">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P70">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q70">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R70">
         <v>1.34</v>
@@ -18521,13 +18521,13 @@
         <v>3.45</v>
       </c>
       <c r="T70">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U70">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V70">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W70">
         <v>2.08</v>
@@ -18539,22 +18539,22 @@
         <v>16.5</v>
       </c>
       <c r="Z70">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA70">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB70">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC70">
         <v>8.800000000000001</v>
       </c>
       <c r="AD70">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE70">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF70">
         <v>12</v>
@@ -18563,28 +18563,28 @@
         <v>11</v>
       </c>
       <c r="AH70">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI70">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ70">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK70">
         <v>22</v>
       </c>
       <c r="AL70">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM70">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN70">
         <v>15</v>
       </c>
       <c r="AO70">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AP70">
         <v>10</v>
@@ -18593,13 +18593,13 @@
         <v>12</v>
       </c>
       <c r="AR70">
+        <v>7.4</v>
+      </c>
+      <c r="AS70">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT70">
         <v>7</v>
-      </c>
-      <c r="AS70">
-        <v>8</v>
-      </c>
-      <c r="AT70">
-        <v>6.8</v>
       </c>
       <c r="AU70">
         <v>7.2</v>
@@ -18608,7 +18608,7 @@
         <v>14.5</v>
       </c>
       <c r="AW70">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX70">
         <v>8.6</v>
@@ -18617,28 +18617,28 @@
         <v>8</v>
       </c>
       <c r="AZ70">
+        <v>16</v>
+      </c>
+      <c r="BA70">
+        <v>8.4</v>
+      </c>
+      <c r="BB70">
+        <v>18.5</v>
+      </c>
+      <c r="BC70">
         <v>17</v>
       </c>
-      <c r="BA70">
-        <v>7.6</v>
-      </c>
-      <c r="BB70">
-        <v>16</v>
-      </c>
-      <c r="BC70">
-        <v>16</v>
-      </c>
       <c r="BD70">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BE70">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF70">
         <v>11</v>
       </c>
       <c r="BG70">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH70">
         <v>1000</v>
@@ -19205,22 +19205,22 @@
         <v>394</v>
       </c>
       <c r="F73">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="G73">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H73">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I73">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J73">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K73">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -19235,10 +19235,10 @@
         <v>0</v>
       </c>
       <c r="P73">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q73">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -19453,16 +19453,16 @@
         <v>1.9</v>
       </c>
       <c r="H74">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I74">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J74">
         <v>4.4</v>
       </c>
       <c r="K74">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -19477,10 +19477,10 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="Q74">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -19492,7 +19492,7 @@
         <v>1.5</v>
       </c>
       <c r="U74">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V74">
         <v>0</v>
@@ -19501,25 +19501,25 @@
         <v>0</v>
       </c>
       <c r="X74">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Y74">
         <v>29</v>
       </c>
       <c r="Z74">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA74">
         <v>80</v>
       </c>
       <c r="AB74">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC74">
         <v>12.5</v>
       </c>
       <c r="AD74">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE74">
         <v>42</v>
@@ -19534,7 +19534,7 @@
         <v>18.5</v>
       </c>
       <c r="AI74">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ74">
         <v>27</v>
@@ -19549,34 +19549,34 @@
         <v>60</v>
       </c>
       <c r="AN74">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO74">
         <v>25</v>
       </c>
       <c r="AP74">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AQ74">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="AR74">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS74">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AT74">
         <v>14</v>
       </c>
       <c r="AU74">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AV74">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW74">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX74">
         <v>14</v>
@@ -19585,25 +19585,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ74">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="BA74">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB74">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC74">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD74">
         <v>20</v>
       </c>
       <c r="BE74">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF74">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG74">
         <v>20</v>
@@ -19689,22 +19689,22 @@
         <v>396</v>
       </c>
       <c r="F75">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G75">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H75">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J75">
         <v>3.7</v>
       </c>
       <c r="K75">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -19719,7 +19719,7 @@
         <v>0</v>
       </c>
       <c r="P75">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q75">
         <v>1.73</v>
@@ -19937,10 +19937,10 @@
         <v>5.8</v>
       </c>
       <c r="H76">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I76">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="J76">
         <v>4.1</v>
@@ -19961,10 +19961,10 @@
         <v>0</v>
       </c>
       <c r="P76">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q76">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -20418,16 +20418,16 @@
         <v>2.66</v>
       </c>
       <c r="G78">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H78">
         <v>2.36</v>
       </c>
       <c r="I78">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="J78">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K78">
         <v>5</v>
@@ -20657,22 +20657,22 @@
         <v>400</v>
       </c>
       <c r="F79">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G79">
         <v>3.15</v>
       </c>
       <c r="H79">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I79">
         <v>3.35</v>
       </c>
       <c r="J79">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K79">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -20687,10 +20687,10 @@
         <v>0</v>
       </c>
       <c r="P79">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q79">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -20899,16 +20899,16 @@
         <v>401</v>
       </c>
       <c r="F80">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G80">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H80">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I80">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J80">
         <v>4</v>
@@ -20929,10 +20929,10 @@
         <v>0</v>
       </c>
       <c r="P80">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="Q80">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="R80">
         <v>0</v>
@@ -21147,7 +21147,7 @@
         <v>1000</v>
       </c>
       <c r="H81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I81">
         <v>9</v>
@@ -21395,7 +21395,7 @@
         <v>1000</v>
       </c>
       <c r="J82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K82">
         <v>950</v>
@@ -21625,22 +21625,22 @@
         <v>404</v>
       </c>
       <c r="F83">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="G83">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H83">
-        <v>2.28</v>
+        <v>5.4</v>
       </c>
       <c r="I83">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J83">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K83">
-        <v>230</v>
+        <v>5.1</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -21655,10 +21655,10 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q83">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -21870,7 +21870,7 @@
         <v>2.14</v>
       </c>
       <c r="G84">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H84">
         <v>3.15</v>
@@ -21912,7 +21912,7 @@
         <v>1.54</v>
       </c>
       <c r="U84">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V84">
         <v>0</v>
@@ -22112,16 +22112,16 @@
         <v>5.1</v>
       </c>
       <c r="G85">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H85">
         <v>1.51</v>
       </c>
       <c r="I85">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="J85">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K85">
         <v>6.2</v>
@@ -22139,10 +22139,10 @@
         <v>0</v>
       </c>
       <c r="P85">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q85">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -22154,7 +22154,7 @@
         <v>1.43</v>
       </c>
       <c r="U85">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -22166,7 +22166,7 @@
         <v>65</v>
       </c>
       <c r="Y85">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z85">
         <v>21</v>
@@ -22175,22 +22175,22 @@
         <v>23</v>
       </c>
       <c r="AB85">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AC85">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AD85">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE85">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF85">
         <v>75</v>
       </c>
       <c r="AG85">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH85">
         <v>21</v>
@@ -22214,40 +22214,40 @@
         <v>36</v>
       </c>
       <c r="AO85">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AP85">
         <v>4.1</v>
       </c>
       <c r="AQ85">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR85">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS85">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT85">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="AU85">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AV85">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW85">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AX85">
         <v>4.1</v>
       </c>
       <c r="AY85">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ85">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA85">
         <v>17.5</v>
@@ -22262,13 +22262,13 @@
         <v>4</v>
       </c>
       <c r="BE85">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BF85">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BG85">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BH85">
         <v>0</v>
@@ -22351,19 +22351,19 @@
         <v>407</v>
       </c>
       <c r="F86">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G86">
         <v>1.56</v>
       </c>
       <c r="H86">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I86">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J86">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K86">
         <v>6.6</v>
@@ -22381,10 +22381,10 @@
         <v>0</v>
       </c>
       <c r="P86">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q86">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R86">
         <v>0</v>
@@ -22393,10 +22393,10 @@
         <v>0</v>
       </c>
       <c r="T86">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U86">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -22417,7 +22417,7 @@
         <v>170</v>
       </c>
       <c r="AB86">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC86">
         <v>19.5</v>
@@ -22429,13 +22429,13 @@
         <v>75</v>
       </c>
       <c r="AF86">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG86">
         <v>15</v>
       </c>
       <c r="AH86">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI86">
         <v>60</v>
@@ -22456,7 +22456,7 @@
         <v>4.6</v>
       </c>
       <c r="AO86">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP86">
         <v>4.2</v>
@@ -22471,43 +22471,43 @@
         <v>4.4</v>
       </c>
       <c r="AT86">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU86">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AV86">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="AW86">
         <v>4.3</v>
       </c>
       <c r="AX86">
+        <v>11.5</v>
+      </c>
+      <c r="AY86">
+        <v>9</v>
+      </c>
+      <c r="AZ86">
         <v>13</v>
-      </c>
-      <c r="AY86">
-        <v>10</v>
-      </c>
-      <c r="AZ86">
-        <v>15.5</v>
       </c>
       <c r="BA86">
         <v>4.2</v>
       </c>
       <c r="BB86">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC86">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BD86">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE86">
         <v>4.2</v>
       </c>
       <c r="BF86">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BG86">
         <v>4.1</v>
@@ -22608,7 +22608,7 @@
         <v>3.3</v>
       </c>
       <c r="K87">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -22835,7 +22835,7 @@
         <v>409</v>
       </c>
       <c r="F88">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="G88">
         <v>1.44</v>
@@ -22844,7 +22844,7 @@
         <v>3.35</v>
       </c>
       <c r="I88">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="J88">
         <v>6</v>
@@ -22865,7 +22865,7 @@
         <v>0</v>
       </c>
       <c r="P88">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q88">
         <v>1.22</v>
@@ -23077,10 +23077,10 @@
         <v>410</v>
       </c>
       <c r="F89">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G89">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H89">
         <v>5.6</v>
@@ -23131,40 +23131,40 @@
         <v>0</v>
       </c>
       <c r="X89">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Y89">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Z89">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA89">
         <v>170</v>
       </c>
       <c r="AB89">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC89">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD89">
         <v>28</v>
       </c>
       <c r="AE89">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF89">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG89">
         <v>11</v>
       </c>
       <c r="AH89">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI89">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ89">
         <v>16.5</v>
@@ -23173,28 +23173,28 @@
         <v>18.5</v>
       </c>
       <c r="AL89">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM89">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN89">
         <v>6.8</v>
       </c>
       <c r="AO89">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP89">
         <v>21</v>
       </c>
       <c r="AQ89">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AR89">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AS89">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT89">
         <v>9.6</v>
@@ -23206,19 +23206,19 @@
         <v>19.5</v>
       </c>
       <c r="AW89">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX89">
         <v>9.6</v>
       </c>
       <c r="AY89">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ89">
         <v>16</v>
       </c>
       <c r="BA89">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB89">
         <v>13.5</v>
@@ -23227,16 +23227,16 @@
         <v>13</v>
       </c>
       <c r="BD89">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BE89">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF89">
         <v>4.9</v>
       </c>
       <c r="BG89">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH89">
         <v>1000</v>
@@ -23322,13 +23322,13 @@
         <v>2.56</v>
       </c>
       <c r="G90">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H90">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I90">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J90">
         <v>4.1</v>
@@ -23349,7 +23349,7 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q90">
         <v>1.4</v>
@@ -23418,7 +23418,7 @@
         <v>32</v>
       </c>
       <c r="AM90">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN90">
         <v>13.5</v>
@@ -23430,7 +23430,7 @@
         <v>3.95</v>
       </c>
       <c r="AQ90">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AR90">
         <v>20</v>
@@ -23451,7 +23451,7 @@
         <v>3.75</v>
       </c>
       <c r="AX90">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AY90">
         <v>12</v>
@@ -23460,7 +23460,7 @@
         <v>12</v>
       </c>
       <c r="BA90">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB90">
         <v>4</v>
@@ -23469,7 +23469,7 @@
         <v>20</v>
       </c>
       <c r="BD90">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE90">
         <v>4</v>
@@ -23478,7 +23478,7 @@
         <v>10</v>
       </c>
       <c r="BG90">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH90">
         <v>0</v>
@@ -24054,10 +24054,10 @@
         <v>9</v>
       </c>
       <c r="I93">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J93">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K93">
         <v>6.8</v>
@@ -24069,28 +24069,28 @@
         <v>1.01</v>
       </c>
       <c r="N93">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="O93">
         <v>1.12</v>
       </c>
       <c r="P93">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="Q93">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="R93">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S93">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="T93">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U93">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V93">
         <v>1.08</v>
@@ -24287,22 +24287,22 @@
         <v>415</v>
       </c>
       <c r="F94">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G94">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H94">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I94">
         <v>4</v>
       </c>
       <c r="J94">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K94">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -24317,7 +24317,7 @@
         <v>0</v>
       </c>
       <c r="P94">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q94">
         <v>1.94</v>
@@ -24529,7 +24529,7 @@
         <v>416</v>
       </c>
       <c r="F95">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G95">
         <v>1.8</v>
@@ -24538,7 +24538,7 @@
         <v>2.3</v>
       </c>
       <c r="I95">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J95">
         <v>3.8</v>
@@ -24804,7 +24804,7 @@
         <v>1.69</v>
       </c>
       <c r="Q96">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -25013,19 +25013,19 @@
         <v>418</v>
       </c>
       <c r="F97">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G97">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H97">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I97">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J97">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K97">
         <v>4.6</v>
@@ -25067,7 +25067,7 @@
         <v>0</v>
       </c>
       <c r="X97">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y97">
         <v>23</v>
@@ -25088,7 +25088,7 @@
         <v>18.5</v>
       </c>
       <c r="AE97">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF97">
         <v>17.5</v>
@@ -25100,7 +25100,7 @@
         <v>18.5</v>
       </c>
       <c r="AI97">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ97">
         <v>28</v>
@@ -25118,61 +25118,61 @@
         <v>11.5</v>
       </c>
       <c r="AO97">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP97">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AQ97">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR97">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS97">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT97">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU97">
         <v>7.6</v>
       </c>
       <c r="AV97">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW97">
         <v>4.5</v>
       </c>
       <c r="AX97">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY97">
         <v>8.4</v>
       </c>
       <c r="AZ97">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA97">
+        <v>4.5</v>
+      </c>
+      <c r="BB97">
+        <v>18</v>
+      </c>
+      <c r="BC97">
+        <v>14</v>
+      </c>
+      <c r="BD97">
+        <v>21</v>
+      </c>
+      <c r="BE97">
         <v>4.6</v>
       </c>
-      <c r="BB97">
-        <v>20</v>
-      </c>
-      <c r="BC97">
-        <v>16</v>
-      </c>
-      <c r="BD97">
-        <v>4.4</v>
-      </c>
-      <c r="BE97">
-        <v>4.7</v>
-      </c>
       <c r="BF97">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG97">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BH97">
         <v>0</v>
@@ -25255,22 +25255,22 @@
         <v>419</v>
       </c>
       <c r="F98">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="G98">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="H98">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="I98">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J98">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K98">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -25285,10 +25285,10 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Q98">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -25739,13 +25739,13 @@
         <v>421</v>
       </c>
       <c r="F100">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G100">
         <v>3.15</v>
       </c>
       <c r="H100">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I100">
         <v>2.98</v>
@@ -25763,7 +25763,7 @@
         <v>1.06</v>
       </c>
       <c r="N100">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O100">
         <v>1.43</v>
@@ -25772,13 +25772,13 @@
         <v>1.55</v>
       </c>
       <c r="Q100">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R100">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S100">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T100">
         <v>1.01</v>
@@ -25981,10 +25981,10 @@
         <v>422</v>
       </c>
       <c r="F101">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="G101">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H101">
         <v>2.86</v>
@@ -25993,10 +25993,10 @@
         <v>3.55</v>
       </c>
       <c r="J101">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K101">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -26011,10 +26011,10 @@
         <v>0</v>
       </c>
       <c r="P101">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="Q101">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -26223,7 +26223,7 @@
         <v>423</v>
       </c>
       <c r="F102">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="G102">
         <v>1.71</v>
@@ -26235,7 +26235,7 @@
         <v>8.4</v>
       </c>
       <c r="J102">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K102">
         <v>4.9</v>
@@ -26247,19 +26247,19 @@
         <v>1.01</v>
       </c>
       <c r="N102">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O102">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P102">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q102">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="R102">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S102">
         <v>2.3</v>
@@ -26480,7 +26480,7 @@
         <v>1.01</v>
       </c>
       <c r="K103">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -26707,19 +26707,19 @@
         <v>425</v>
       </c>
       <c r="F104">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G104">
         <v>6.2</v>
       </c>
       <c r="H104">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="I104">
         <v>1.88</v>
       </c>
       <c r="J104">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K104">
         <v>4.2</v>
@@ -26737,7 +26737,7 @@
         <v>0</v>
       </c>
       <c r="P104">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q104">
         <v>2.02</v>
@@ -27436,7 +27436,7 @@
         <v>3.2</v>
       </c>
       <c r="G107">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H107">
         <v>2.24</v>
@@ -27448,7 +27448,7 @@
         <v>3.7</v>
       </c>
       <c r="K107">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L107">
         <v>1.01</v>
@@ -27484,7 +27484,7 @@
         <v>1.74</v>
       </c>
       <c r="W107">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X107">
         <v>22</v>
@@ -27675,13 +27675,13 @@
         <v>429</v>
       </c>
       <c r="F108">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G108">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H108">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I108">
         <v>2.32</v>
@@ -27696,37 +27696,37 @@
         <v>1.01</v>
       </c>
       <c r="M108">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N108">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O108">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P108">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q108">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R108">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S108">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T108">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U108">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V108">
         <v>1.76</v>
       </c>
       <c r="W108">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X108">
         <v>1000</v>
@@ -28643,7 +28643,7 @@
         <v>433</v>
       </c>
       <c r="F112">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G112">
         <v>2.82</v>
@@ -28673,10 +28673,10 @@
         <v>0</v>
       </c>
       <c r="P112">
+        <v>1.88</v>
+      </c>
+      <c r="Q112">
         <v>1.87</v>
-      </c>
-      <c r="Q112">
-        <v>1.88</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -28885,22 +28885,22 @@
         <v>434</v>
       </c>
       <c r="F113">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G113">
         <v>2.06</v>
       </c>
       <c r="H113">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I113">
         <v>5.9</v>
       </c>
       <c r="J113">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="K113">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -28918,7 +28918,7 @@
         <v>1.25</v>
       </c>
       <c r="Q113">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -29157,7 +29157,7 @@
         <v>0</v>
       </c>
       <c r="P114">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q114">
         <v>1.9</v>
@@ -29611,19 +29611,19 @@
         <v>437</v>
       </c>
       <c r="F116">
-        <v>1.43</v>
+        <v>3.6</v>
       </c>
       <c r="G116">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H116">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I116">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="J116">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K116">
         <v>3.8</v>
@@ -29641,10 +29641,10 @@
         <v>0</v>
       </c>
       <c r="P116">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q116">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -30098,7 +30098,7 @@
         <v>5</v>
       </c>
       <c r="G118">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H118">
         <v>1.69</v>
@@ -30107,7 +30107,7 @@
         <v>1.74</v>
       </c>
       <c r="J118">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K118">
         <v>4.5</v>
@@ -30149,109 +30149,109 @@
         <v>0</v>
       </c>
       <c r="X118">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y118">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z118">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA118">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AB118">
         <v>26</v>
       </c>
       <c r="AC118">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD118">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE118">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AF118">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG118">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH118">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI118">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ118">
         <v>120</v>
       </c>
       <c r="AK118">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL118">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM118">
         <v>70</v>
       </c>
       <c r="AN118">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO118">
         <v>7.6</v>
       </c>
       <c r="AP118">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="AQ118">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="AR118">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AS118">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="AT118">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AU118">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV118">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW118">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX118">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AY118">
         <v>17</v>
       </c>
       <c r="AZ118">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="BA118">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BB118">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC118">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BD118">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BE118">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF118">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG118">
         <v>5.8</v>
@@ -30337,22 +30337,22 @@
         <v>440</v>
       </c>
       <c r="F119">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="G119">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H119">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I119">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J119">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K119">
-        <v>190</v>
+        <v>4.3</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -30821,22 +30821,22 @@
         <v>442</v>
       </c>
       <c r="F121">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G121">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="H121">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I121">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="J121">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K121">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L121">
         <v>0</v>
@@ -30854,7 +30854,7 @@
         <v>1.89</v>
       </c>
       <c r="Q121">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -31066,13 +31066,13 @@
         <v>2.24</v>
       </c>
       <c r="G122">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H122">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I122">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J122">
         <v>3.05</v>
@@ -31093,10 +31093,10 @@
         <v>0</v>
       </c>
       <c r="P122">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q122">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R122">
         <v>0</v>
@@ -31789,22 +31789,22 @@
         <v>446</v>
       </c>
       <c r="F125">
-        <v>1.5</v>
+        <v>2.94</v>
       </c>
       <c r="G125">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H125">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="I125">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J125">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="K125">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -31819,10 +31819,10 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q125">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -32273,7 +32273,7 @@
         <v>448</v>
       </c>
       <c r="F127">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="G127">
         <v>8</v>
@@ -32288,7 +32288,7 @@
         <v>4.3</v>
       </c>
       <c r="K127">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L127">
         <v>0</v>
@@ -32515,19 +32515,19 @@
         <v>449</v>
       </c>
       <c r="F128">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G128">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="H128">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I128">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="J128">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K128">
         <v>4.1</v>
@@ -32545,10 +32545,10 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q128">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -32999,7 +32999,7 @@
         <v>451</v>
       </c>
       <c r="F130">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G130">
         <v>1.8</v>
@@ -33014,7 +33014,7 @@
         <v>3.7</v>
       </c>
       <c r="K130">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="L130">
         <v>1.01</v>
@@ -33023,7 +33023,7 @@
         <v>1.06</v>
       </c>
       <c r="N130">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O130">
         <v>1.37</v>
@@ -33032,7 +33032,7 @@
         <v>1.66</v>
       </c>
       <c r="Q130">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R130">
         <v>1.18</v>
@@ -33050,7 +33050,7 @@
         <v>1.15</v>
       </c>
       <c r="W130">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X130">
         <v>1000</v>
@@ -33253,7 +33253,7 @@
         <v>17.5</v>
       </c>
       <c r="J131">
-        <v>2.94</v>
+        <v>1.65</v>
       </c>
       <c r="K131">
         <v>5</v>
@@ -33728,10 +33728,10 @@
         <v>2</v>
       </c>
       <c r="G133">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H133">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I133">
         <v>4.2</v>
@@ -33967,13 +33967,13 @@
         <v>455</v>
       </c>
       <c r="F134">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G134">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H134">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="I134">
         <v>4.8</v>
@@ -34209,19 +34209,19 @@
         <v>456</v>
       </c>
       <c r="F135">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="G135">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="H135">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I135">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="J135">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="K135">
         <v>950</v>
@@ -34239,10 +34239,10 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q135">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R135">
         <v>0</v>
@@ -34693,13 +34693,13 @@
         <v>458</v>
       </c>
       <c r="F137">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G137">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H137">
-        <v>1.92</v>
+        <v>3.4</v>
       </c>
       <c r="I137">
         <v>4.1</v>
@@ -34708,7 +34708,7 @@
         <v>1.32</v>
       </c>
       <c r="K137">
-        <v>190</v>
+        <v>4.7</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -34723,10 +34723,10 @@
         <v>0</v>
       </c>
       <c r="P137">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q137">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R137">
         <v>0</v>
@@ -34935,7 +34935,7 @@
         <v>459</v>
       </c>
       <c r="F138">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G138">
         <v>1.64</v>
@@ -36145,22 +36145,22 @@
         <v>464</v>
       </c>
       <c r="F143">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G143">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="H143">
-        <v>1.45</v>
+        <v>2.8</v>
       </c>
       <c r="I143">
         <v>4.3</v>
       </c>
       <c r="J143">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="K143">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L143">
         <v>0</v>
@@ -36390,13 +36390,13 @@
         <v>1.97</v>
       </c>
       <c r="G144">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H144">
         <v>4</v>
       </c>
       <c r="I144">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J144">
         <v>3.5</v>
@@ -36417,7 +36417,7 @@
         <v>0</v>
       </c>
       <c r="P144">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q144">
         <v>1.98</v>
@@ -36629,10 +36629,10 @@
         <v>466</v>
       </c>
       <c r="F145">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="G145">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H145">
         <v>25</v>
@@ -36644,7 +36644,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="K145">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -36659,10 +36659,10 @@
         <v>0</v>
       </c>
       <c r="P145">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q145">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -36689,7 +36689,7 @@
         <v>80</v>
       </c>
       <c r="Z145">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AA145">
         <v>1000</v>
@@ -36698,7 +36698,7 @@
         <v>11.5</v>
       </c>
       <c r="AC145">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AD145">
         <v>110</v>
@@ -36716,7 +36716,7 @@
         <v>70</v>
       </c>
       <c r="AI145">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AJ145">
         <v>8</v>
@@ -36728,7 +36728,7 @@
         <v>70</v>
       </c>
       <c r="AM145">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="AN145">
         <v>3.15</v>
@@ -36737,58 +36737,58 @@
         <v>1000</v>
       </c>
       <c r="AP145">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ145">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR145">
+        <v>8.6</v>
+      </c>
+      <c r="AS145">
         <v>9</v>
-      </c>
-      <c r="AS145">
-        <v>9.199999999999999</v>
       </c>
       <c r="AT145">
         <v>9.199999999999999</v>
       </c>
       <c r="AU145">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV145">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW145">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX145">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY145">
         <v>13</v>
       </c>
       <c r="AZ145">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BA145">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB145">
         <v>6.4</v>
       </c>
       <c r="BC145">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD145">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE145">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF145">
         <v>2.7</v>
       </c>
       <c r="BG145">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH145">
         <v>0</v>
@@ -36877,7 +36877,7 @@
         <v>6</v>
       </c>
       <c r="H146">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="I146">
         <v>1.78</v>
@@ -36901,10 +36901,10 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q146">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="R146">
         <v>0</v>
@@ -37355,19 +37355,19 @@
         <v>469</v>
       </c>
       <c r="F148">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G148">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H148">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I148">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J148">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K148">
         <v>3.25</v>
@@ -37385,10 +37385,10 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q148">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -37597,16 +37597,16 @@
         <v>470</v>
       </c>
       <c r="F149">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G149">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H149">
         <v>5.8</v>
       </c>
       <c r="I149">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J149">
         <v>3.2</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
@@ -1537,7 +1537,7 @@
     <t>Barracas Central</t>
   </si>
   <si>
-    <t>2026-08-07 20:46:30</t>
+    <t>2026-08-07 23:10:50</t>
   </si>
 </sst>
 </file>
@@ -2140,13 +2140,13 @@
         <v>3.25</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2">
         <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -2155,55 +2155,55 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
         <v>1.65</v>
       </c>
       <c r="X2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
         <v>13</v>
       </c>
       <c r="Z2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="AB2">
         <v>10.5</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE2">
         <v>40</v>
@@ -2212,43 +2212,43 @@
         <v>16</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI2">
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL2">
         <v>42</v>
       </c>
       <c r="AM2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP2">
         <v>11</v>
       </c>
       <c r="AQ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT2">
         <v>9.4</v>
@@ -2260,7 +2260,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AX2">
         <v>14</v>
@@ -2272,7 +2272,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB2">
         <v>30</v>
@@ -2284,13 +2284,13 @@
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="BF2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -2373,7 +2373,7 @@
         <v>345</v>
       </c>
       <c r="F3">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="G3">
         <v>6.8</v>
@@ -2388,7 +2388,7 @@
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -2863,7 +2863,7 @@
         <v>1.81</v>
       </c>
       <c r="H5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
         <v>6.4</v>
@@ -2872,7 +2872,7 @@
         <v>3.55</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2881,13 +2881,13 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
         <v>2.12</v>
@@ -2899,7 +2899,7 @@
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U5">
         <v>1.86</v>
@@ -2923,7 +2923,7 @@
         <v>170</v>
       </c>
       <c r="AB5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC5">
         <v>8.6</v>
@@ -2932,7 +2932,7 @@
         <v>24</v>
       </c>
       <c r="AE5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
@@ -2959,7 +2959,7 @@
         <v>210</v>
       </c>
       <c r="AN5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO5">
         <v>160</v>
@@ -2974,7 +2974,7 @@
         <v>36</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT5">
         <v>6.4</v>
@@ -2986,7 +2986,7 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX5">
         <v>9</v>
@@ -2995,10 +2995,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA5">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -3010,13 +3010,13 @@
         <v>36</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF5">
         <v>13</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -3099,22 +3099,22 @@
         <v>348</v>
       </c>
       <c r="F6">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="G6">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H6">
         <v>6.2</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>1.06</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -3123,19 +3123,19 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
         <v>1.22</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>1.46</v>
       </c>
       <c r="Q6">
         <v>1.56</v>
       </c>
       <c r="R6">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S6">
         <v>2.44</v>
@@ -3147,10 +3147,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W6">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -3344,13 +3344,13 @@
         <v>1.67</v>
       </c>
       <c r="G7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H7">
         <v>6.8</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
         <v>3.5</v>
@@ -3362,16 +3362,16 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="O7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q7">
         <v>2.62</v>
@@ -3380,127 +3380,127 @@
         <v>1.19</v>
       </c>
       <c r="S7">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U7">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="V7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y7">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
         <v>36</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH7">
         <v>40</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL7">
         <v>85</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AP7">
-        <v>1.34</v>
+        <v>8</v>
       </c>
       <c r="AQ7">
-        <v>1.25</v>
+        <v>14</v>
       </c>
       <c r="AR7">
-        <v>1.34</v>
+        <v>5.4</v>
       </c>
       <c r="AS7">
-        <v>1.34</v>
+        <v>5.8</v>
       </c>
       <c r="AT7">
-        <v>1.34</v>
+        <v>5.1</v>
       </c>
       <c r="AU7">
-        <v>1.19</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>1.29</v>
+        <v>21</v>
       </c>
       <c r="AW7">
-        <v>1.34</v>
+        <v>5.7</v>
       </c>
       <c r="AX7">
-        <v>1.34</v>
+        <v>7.4</v>
       </c>
       <c r="AY7">
-        <v>1.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>1.29</v>
+        <v>5</v>
       </c>
       <c r="BA7">
-        <v>1.34</v>
+        <v>5.7</v>
       </c>
       <c r="BB7">
-        <v>1.26</v>
+        <v>15</v>
       </c>
       <c r="BC7">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="BD7">
-        <v>1.32</v>
+        <v>5.5</v>
       </c>
       <c r="BE7">
-        <v>1.34</v>
+        <v>5.8</v>
       </c>
       <c r="BF7">
-        <v>1.34</v>
+        <v>13</v>
       </c>
       <c r="BG7">
-        <v>1.34</v>
+        <v>5.8</v>
       </c>
       <c r="BH7">
         <v>2.98</v>
@@ -3589,49 +3589,49 @@
         <v>1.95</v>
       </c>
       <c r="H8">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J8">
         <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O8">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P8">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q8">
         <v>2.62</v>
       </c>
       <c r="R8">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T8">
         <v>2.32</v>
       </c>
       <c r="U8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W8">
         <v>2.04</v>
@@ -3643,7 +3643,7 @@
         <v>18</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA8">
         <v>1000</v>
@@ -3664,16 +3664,16 @@
         <v>11.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI8">
         <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK8">
         <v>34</v>
@@ -3691,58 +3691,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="AS8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AT8">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="AU8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AV8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AW8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="AX8">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="AY8">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="AZ8">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="BA8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="BB8">
-        <v>1.81</v>
+        <v>17.5</v>
       </c>
       <c r="BC8">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="BD8">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="BE8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="BF8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="BG8">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="BH8">
         <v>3.15</v>
@@ -3855,10 +3855,10 @@
         <v>1.45</v>
       </c>
       <c r="P9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q9">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R9">
         <v>1.2</v>
@@ -3930,61 +3930,61 @@
         <v>120</v>
       </c>
       <c r="AO9">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP9">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="AQ9">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="AR9">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="AS9">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AT9">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>2.98</v>
       </c>
       <c r="AV9">
-        <v>8.199999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="AW9">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AX9">
         <v>4.2</v>
       </c>
       <c r="AY9">
-        <v>13</v>
+        <v>3.95</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>4</v>
       </c>
       <c r="BA9">
         <v>4.4</v>
       </c>
       <c r="BB9">
+        <v>4.6</v>
+      </c>
+      <c r="BC9">
         <v>4.5</v>
       </c>
-      <c r="BC9">
-        <v>4.4</v>
-      </c>
       <c r="BD9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE9">
+        <v>4.7</v>
+      </c>
+      <c r="BF9">
         <v>4.6</v>
       </c>
-      <c r="BF9">
-        <v>4.5</v>
-      </c>
       <c r="BG9">
-        <v>17.5</v>
+        <v>4</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -4336,16 +4336,16 @@
         <v>2.64</v>
       </c>
       <c r="O11">
+        <v>1.54</v>
+      </c>
+      <c r="P11">
         <v>1.55</v>
-      </c>
-      <c r="P11">
-        <v>1.54</v>
       </c>
       <c r="Q11">
         <v>2.64</v>
       </c>
       <c r="R11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
         <v>5.3</v>
@@ -4357,7 +4357,7 @@
         <v>1.8</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W11">
         <v>1.52</v>
@@ -4366,7 +4366,7 @@
         <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>22</v>
@@ -4390,7 +4390,7 @@
         <v>20</v>
       </c>
       <c r="AG11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH11">
         <v>28</v>
@@ -4426,7 +4426,7 @@
         <v>15.5</v>
       </c>
       <c r="AS11">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT11">
         <v>7.4</v>
@@ -4438,7 +4438,7 @@
         <v>11</v>
       </c>
       <c r="AW11">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="AX11">
         <v>14.5</v>
@@ -4450,22 +4450,22 @@
         <v>19</v>
       </c>
       <c r="BA11">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB11">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BC11">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD11">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF11">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="BG11">
         <v>38</v>
@@ -4554,16 +4554,16 @@
         <v>2.02</v>
       </c>
       <c r="G12">
-        <v>5.9</v>
+        <v>110</v>
       </c>
       <c r="H12">
-        <v>1.84</v>
+        <v>1.38</v>
       </c>
       <c r="I12">
         <v>2.02</v>
       </c>
       <c r="J12">
-        <v>2.98</v>
+        <v>2.02</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -4575,7 +4575,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
         <v>1.31</v>
@@ -4584,13 +4584,13 @@
         <v>1.83</v>
       </c>
       <c r="Q12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -4602,7 +4602,7 @@
         <v>1.98</v>
       </c>
       <c r="W12">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -5298,25 +5298,25 @@
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N15">
         <v>3</v>
       </c>
       <c r="O15">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P15">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q15">
         <v>2.26</v>
       </c>
       <c r="R15">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="S15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T15">
         <v>1.9</v>
@@ -6284,7 +6284,7 @@
         <v>1.18</v>
       </c>
       <c r="S19">
-        <v>2.44</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -6490,13 +6490,13 @@
         <v>3.6</v>
       </c>
       <c r="G20">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="H20">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I20">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J20">
         <v>3.15</v>
@@ -6508,145 +6508,145 @@
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N20">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="O20">
         <v>1.41</v>
       </c>
       <c r="P20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q20">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="R20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V20">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W20">
         <v>1.34</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6971,16 +6971,16 @@
         <v>364</v>
       </c>
       <c r="F22">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G22">
         <v>110</v>
       </c>
       <c r="H22">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="I22">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J22">
         <v>1.04</v>
@@ -7216,7 +7216,7 @@
         <v>3.4</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="H23">
         <v>2.16</v>
@@ -7225,7 +7225,7 @@
         <v>2.22</v>
       </c>
       <c r="J23">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K23">
         <v>4.1</v>
@@ -7264,7 +7264,7 @@
         <v>1.81</v>
       </c>
       <c r="W23">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -7488,7 +7488,7 @@
         <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R24">
         <v>1.61</v>
@@ -7518,7 +7518,7 @@
         <v>15</v>
       </c>
       <c r="AA24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB24">
         <v>28</v>
@@ -7560,7 +7560,7 @@
         <v>48</v>
       </c>
       <c r="AO24">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AP24">
         <v>21</v>
@@ -7587,7 +7587,7 @@
         <v>12.5</v>
       </c>
       <c r="AX24">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY24">
         <v>17</v>
@@ -7599,19 +7599,19 @@
         <v>20</v>
       </c>
       <c r="BB24">
+        <v>5.7</v>
+      </c>
+      <c r="BC24">
         <v>5.4</v>
       </c>
-      <c r="BC24">
-        <v>5.1</v>
-      </c>
       <c r="BD24">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE24">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF24">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG24">
         <v>5.9</v>
@@ -7721,7 +7721,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="O25">
         <v>1.2</v>
@@ -8423,7 +8423,7 @@
         <v>370</v>
       </c>
       <c r="F28">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G28">
         <v>1.63</v>
@@ -8435,22 +8435,22 @@
         <v>6.8</v>
       </c>
       <c r="J28">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N28">
         <v>4.7</v>
       </c>
       <c r="O28">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P28">
         <v>2.26</v>
@@ -8459,13 +8459,13 @@
         <v>1.68</v>
       </c>
       <c r="R28">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S28">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T28">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U28">
         <v>2.12</v>
@@ -8474,7 +8474,7 @@
         <v>1.18</v>
       </c>
       <c r="W28">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X28">
         <v>22</v>
@@ -8555,10 +8555,10 @@
         <v>34</v>
       </c>
       <c r="AX28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY28">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ28">
         <v>17.5</v>
@@ -9152,16 +9152,16 @@
         <v>3.4</v>
       </c>
       <c r="G31">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H31">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I31">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J31">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K31">
         <v>4.1</v>
@@ -9176,19 +9176,19 @@
         <v>5.2</v>
       </c>
       <c r="O31">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P31">
         <v>2.42</v>
       </c>
       <c r="Q31">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R31">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S31">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="T31">
         <v>1.55</v>
@@ -9197,115 +9197,115 @@
         <v>2.54</v>
       </c>
       <c r="V31">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W31">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X31">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y31">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z31">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA31">
+        <v>32</v>
+      </c>
+      <c r="AB31">
+        <v>21</v>
+      </c>
+      <c r="AC31">
+        <v>9.4</v>
+      </c>
+      <c r="AD31">
+        <v>12.5</v>
+      </c>
+      <c r="AE31">
+        <v>21</v>
+      </c>
+      <c r="AF31">
+        <v>29</v>
+      </c>
+      <c r="AG31">
+        <v>17</v>
+      </c>
+      <c r="AH31">
+        <v>15.5</v>
+      </c>
+      <c r="AI31">
+        <v>32</v>
+      </c>
+      <c r="AJ31">
+        <v>60</v>
+      </c>
+      <c r="AK31">
         <v>34</v>
       </c>
-      <c r="AB31">
-        <v>19.5</v>
-      </c>
-      <c r="AC31">
-        <v>10</v>
-      </c>
-      <c r="AD31">
-        <v>14</v>
-      </c>
-      <c r="AE31">
-        <v>25</v>
-      </c>
-      <c r="AF31">
-        <v>34</v>
-      </c>
-      <c r="AG31">
-        <v>16</v>
-      </c>
-      <c r="AH31">
-        <v>16</v>
-      </c>
-      <c r="AI31">
-        <v>34</v>
-      </c>
-      <c r="AJ31">
-        <v>70</v>
-      </c>
-      <c r="AK31">
-        <v>36</v>
-      </c>
       <c r="AL31">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM31">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN31">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO31">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP31">
         <v>19.5</v>
       </c>
       <c r="AQ31">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR31">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS31">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT31">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU31">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV31">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW31">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX31">
+        <v>25</v>
+      </c>
+      <c r="AY31">
+        <v>13</v>
+      </c>
+      <c r="AZ31">
+        <v>13.5</v>
+      </c>
+      <c r="BA31">
+        <v>24</v>
+      </c>
+      <c r="BB31">
+        <v>48</v>
+      </c>
+      <c r="BC31">
+        <v>29</v>
+      </c>
+      <c r="BD31">
+        <v>32</v>
+      </c>
+      <c r="BE31">
+        <v>50</v>
+      </c>
+      <c r="BF31">
         <v>19.5</v>
-      </c>
-      <c r="AY31">
-        <v>12.5</v>
-      </c>
-      <c r="AZ31">
-        <v>12.5</v>
-      </c>
-      <c r="BA31">
-        <v>19.5</v>
-      </c>
-      <c r="BB31">
-        <v>5.3</v>
-      </c>
-      <c r="BC31">
-        <v>5</v>
-      </c>
-      <c r="BD31">
-        <v>5</v>
-      </c>
-      <c r="BE31">
-        <v>5.3</v>
-      </c>
-      <c r="BF31">
-        <v>17</v>
       </c>
       <c r="BG31">
         <v>9.6</v>
@@ -9391,22 +9391,22 @@
         <v>374</v>
       </c>
       <c r="F32">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H32">
         <v>3.8</v>
       </c>
       <c r="I32">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J32">
         <v>3.6</v>
       </c>
       <c r="K32">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -9421,7 +9421,7 @@
         <v>1.3</v>
       </c>
       <c r="P32">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q32">
         <v>1.93</v>
@@ -9436,7 +9436,7 @@
         <v>1.78</v>
       </c>
       <c r="U32">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V32">
         <v>1.3</v>
@@ -9460,7 +9460,7 @@
         <v>10</v>
       </c>
       <c r="AC32">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32">
         <v>17</v>
@@ -9469,7 +9469,7 @@
         <v>60</v>
       </c>
       <c r="AF32">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG32">
         <v>12.5</v>
@@ -9484,7 +9484,7 @@
         <v>29</v>
       </c>
       <c r="AK32">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL32">
         <v>38</v>
@@ -9505,10 +9505,10 @@
         <v>12.5</v>
       </c>
       <c r="AR32">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS32">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT32">
         <v>8.4</v>
@@ -9520,7 +9520,7 @@
         <v>13.5</v>
       </c>
       <c r="AW32">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX32">
         <v>11</v>
@@ -9532,7 +9532,7 @@
         <v>15</v>
       </c>
       <c r="BA32">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB32">
         <v>21</v>
@@ -9541,16 +9541,16 @@
         <v>18.5</v>
       </c>
       <c r="BD32">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE32">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF32">
         <v>11.5</v>
       </c>
       <c r="BG32">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -9878,10 +9878,10 @@
         <v>4</v>
       </c>
       <c r="G34">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="H34">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="I34">
         <v>1.9</v>
@@ -9899,19 +9899,19 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>1.12</v>
       </c>
       <c r="P34">
-        <v>1.57</v>
+        <v>2.78</v>
       </c>
       <c r="Q34">
         <v>1.4</v>
       </c>
       <c r="R34">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="S34">
         <v>2.04</v>
@@ -9926,7 +9926,7 @@
         <v>2.1</v>
       </c>
       <c r="W34">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -10117,10 +10117,10 @@
         <v>377</v>
       </c>
       <c r="F35">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="G35">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H35">
         <v>4</v>
@@ -10129,10 +10129,10 @@
         <v>4.4</v>
       </c>
       <c r="J35">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -10141,34 +10141,34 @@
         <v>1.04</v>
       </c>
       <c r="N35">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="O35">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P35">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Q35">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R35">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S35">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T35">
-        <v>1.62</v>
+        <v>1.03</v>
       </c>
       <c r="U35">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V35">
         <v>1.29</v>
       </c>
       <c r="W35">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X35">
         <v>21</v>
@@ -10258,7 +10258,7 @@
         <v>13.5</v>
       </c>
       <c r="BA35">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="BB35">
         <v>19</v>
@@ -10359,7 +10359,7 @@
         <v>378</v>
       </c>
       <c r="F36">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G36">
         <v>2.32</v>
@@ -10368,10 +10368,10 @@
         <v>3.25</v>
       </c>
       <c r="I36">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K36">
         <v>3.8</v>
@@ -10395,7 +10395,7 @@
         <v>1.75</v>
       </c>
       <c r="R36">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S36">
         <v>2.94</v>
@@ -10404,10 +10404,10 @@
         <v>1.66</v>
       </c>
       <c r="U36">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W36">
         <v>1.76</v>
@@ -10604,19 +10604,19 @@
         <v>3.35</v>
       </c>
       <c r="G37">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H37">
         <v>2.12</v>
       </c>
       <c r="I37">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J37">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K37">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -10643,10 +10643,10 @@
         <v>2.92</v>
       </c>
       <c r="T37">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U37">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V37">
         <v>1.79</v>
@@ -10694,7 +10694,7 @@
         <v>1000</v>
       </c>
       <c r="AK37">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AL37">
         <v>140</v>
@@ -10718,7 +10718,7 @@
         <v>13</v>
       </c>
       <c r="AS37">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT37">
         <v>13.5</v>
@@ -10727,22 +10727,22 @@
         <v>7.8</v>
       </c>
       <c r="AV37">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW37">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX37">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AY37">
         <v>13</v>
       </c>
       <c r="AZ37">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA37">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BB37">
         <v>30</v>
@@ -10751,13 +10751,13 @@
         <v>23</v>
       </c>
       <c r="BD37">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BE37">
         <v>34</v>
       </c>
       <c r="BF37">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BG37">
         <v>12</v>
@@ -10843,7 +10843,7 @@
         <v>380</v>
       </c>
       <c r="F38">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G38">
         <v>1.52</v>
@@ -10858,7 +10858,7 @@
         <v>4.8</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -10867,7 +10867,7 @@
         <v>1.04</v>
       </c>
       <c r="N38">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O38">
         <v>1.23</v>
@@ -10876,16 +10876,16 @@
         <v>2.34</v>
       </c>
       <c r="Q38">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R38">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S38">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T38">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U38">
         <v>2.08</v>
@@ -10900,7 +10900,7 @@
         <v>23</v>
       </c>
       <c r="Y38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z38">
         <v>70</v>
@@ -10912,16 +10912,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD38">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE38">
         <v>110</v>
       </c>
       <c r="AF38">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -10930,10 +10930,10 @@
         <v>23</v>
       </c>
       <c r="AI38">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ38">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK38">
         <v>15</v>
@@ -10960,10 +10960,10 @@
         <v>55</v>
       </c>
       <c r="AS38">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="AT38">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU38">
         <v>10</v>
@@ -10972,19 +10972,19 @@
         <v>24</v>
       </c>
       <c r="AW38">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="AX38">
         <v>8.6</v>
       </c>
       <c r="AY38">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ38">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA38">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BB38">
         <v>12</v>
@@ -10996,13 +10996,13 @@
         <v>27</v>
       </c>
       <c r="BE38">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BF38">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG38">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -11085,58 +11085,58 @@
         <v>381</v>
       </c>
       <c r="F39">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G39">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="H39">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="I39">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39">
         <v>4.5</v>
       </c>
       <c r="K39">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L39">
         <v>1.01</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N39">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="O39">
         <v>1.17</v>
       </c>
       <c r="P39">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="Q39">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="R39">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="S39">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V39">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W39">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -11357,31 +11357,31 @@
         <v>1.12</v>
       </c>
       <c r="P40">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q40">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="R40">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S40">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T40">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U40">
         <v>2.62</v>
       </c>
       <c r="V40">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W40">
         <v>2.68</v>
       </c>
       <c r="X40">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y40">
         <v>38</v>
@@ -11411,7 +11411,7 @@
         <v>13</v>
       </c>
       <c r="AH40">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI40">
         <v>55</v>
@@ -11429,22 +11429,22 @@
         <v>65</v>
       </c>
       <c r="AN40">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AO40">
         <v>42</v>
       </c>
       <c r="AP40">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AQ40">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AR40">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS40">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT40">
         <v>13.5</v>
@@ -11456,7 +11456,7 @@
         <v>21</v>
       </c>
       <c r="AW40">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX40">
         <v>11.5</v>
@@ -11468,7 +11468,7 @@
         <v>14.5</v>
       </c>
       <c r="BA40">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB40">
         <v>14</v>
@@ -11480,13 +11480,13 @@
         <v>19</v>
       </c>
       <c r="BE40">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF40">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG40">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -11575,7 +11575,7 @@
         <v>1.59</v>
       </c>
       <c r="H41">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -11593,7 +11593,7 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="O41">
         <v>1.2</v>
@@ -11626,7 +11626,7 @@
         <v>1000</v>
       </c>
       <c r="Y41">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z41">
         <v>1000</v>
@@ -11635,10 +11635,10 @@
         <v>1000</v>
       </c>
       <c r="AB41">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AC41">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AD41">
         <v>1000</v>
@@ -11647,25 +11647,25 @@
         <v>1000</v>
       </c>
       <c r="AF41">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AG41">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AH41">
         <v>1000</v>
       </c>
       <c r="AI41">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ41">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK41">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL41">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM41">
         <v>1000</v>
@@ -11677,58 +11677,58 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU41">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AV41">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW41">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA41">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BE41">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11835,7 +11835,7 @@
         <v>1.05</v>
       </c>
       <c r="N42">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>1.25</v>
@@ -12062,7 +12062,7 @@
         <v>5.7</v>
       </c>
       <c r="I43">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J43">
         <v>4.2</v>
@@ -12077,10 +12077,10 @@
         <v>1.05</v>
       </c>
       <c r="N43">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="O43">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P43">
         <v>2.2</v>
@@ -12101,7 +12101,7 @@
         <v>2.12</v>
       </c>
       <c r="V43">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W43">
         <v>2.44</v>
@@ -12310,7 +12310,7 @@
         <v>4.1</v>
       </c>
       <c r="K44">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L44">
         <v>1.27</v>
@@ -12334,7 +12334,7 @@
         <v>1.58</v>
       </c>
       <c r="S44">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T44">
         <v>1.6</v>
@@ -12540,13 +12540,13 @@
         <v>6.4</v>
       </c>
       <c r="G45">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H45">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="I45">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="J45">
         <v>4.9</v>
@@ -12561,34 +12561,34 @@
         <v>1.03</v>
       </c>
       <c r="N45">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O45">
         <v>1.16</v>
       </c>
       <c r="P45">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q45">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R45">
         <v>1.73</v>
       </c>
       <c r="S45">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T45">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U45">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V45">
         <v>2.84</v>
       </c>
       <c r="W45">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X45">
         <v>32</v>
@@ -12603,7 +12603,7 @@
         <v>15.5</v>
       </c>
       <c r="AB45">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AC45">
         <v>12.5</v>
@@ -12615,13 +12615,13 @@
         <v>14.5</v>
       </c>
       <c r="AF45">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG45">
         <v>26</v>
       </c>
       <c r="AH45">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI45">
         <v>26</v>
@@ -12630,16 +12630,16 @@
         <v>210</v>
       </c>
       <c r="AK45">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AL45">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM45">
         <v>95</v>
       </c>
       <c r="AN45">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO45">
         <v>5.5</v>
@@ -12782,10 +12782,10 @@
         <v>2.38</v>
       </c>
       <c r="G46">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I46">
         <v>3.3</v>
@@ -12812,7 +12812,7 @@
         <v>2.06</v>
       </c>
       <c r="Q46">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R46">
         <v>1.42</v>
@@ -12830,7 +12830,7 @@
         <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X46">
         <v>19.5</v>
@@ -12845,19 +12845,19 @@
         <v>60</v>
       </c>
       <c r="AB46">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC46">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD46">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE46">
         <v>38</v>
       </c>
       <c r="AF46">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG46">
         <v>13.5</v>
@@ -12869,10 +12869,10 @@
         <v>46</v>
       </c>
       <c r="AJ46">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK46">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL46">
         <v>42</v>
@@ -12896,7 +12896,7 @@
         <v>19.5</v>
       </c>
       <c r="AS46">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT46">
         <v>10.5</v>
@@ -12905,13 +12905,13 @@
         <v>7.4</v>
       </c>
       <c r="AV46">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW46">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX46">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY46">
         <v>10</v>
@@ -12920,19 +12920,19 @@
         <v>14</v>
       </c>
       <c r="BA46">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB46">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC46">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BD46">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE46">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF46">
         <v>13.5</v>
@@ -13045,16 +13045,16 @@
         <v>1.03</v>
       </c>
       <c r="N47">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O47">
         <v>1.18</v>
       </c>
       <c r="P47">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="Q47">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R47">
         <v>1.47</v>
@@ -13090,7 +13090,7 @@
         <v>14.5</v>
       </c>
       <c r="AC47">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD47">
         <v>14</v>
@@ -13165,7 +13165,7 @@
         <v>23</v>
       </c>
       <c r="BB47">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC47">
         <v>20</v>
@@ -13174,7 +13174,7 @@
         <v>21</v>
       </c>
       <c r="BE47">
-        <v>4.6</v>
+        <v>24</v>
       </c>
       <c r="BF47">
         <v>10</v>
@@ -13293,7 +13293,7 @@
         <v>1.32</v>
       </c>
       <c r="P48">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="Q48">
         <v>1.9</v>
@@ -13505,22 +13505,22 @@
         <v>391</v>
       </c>
       <c r="F49">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G49">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H49">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I49">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="J49">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="K49">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -13529,37 +13529,37 @@
         <v>1.03</v>
       </c>
       <c r="N49">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O49">
         <v>1.16</v>
       </c>
       <c r="P49">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q49">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R49">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="S49">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T49">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U49">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V49">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="W49">
         <v>1.13</v>
       </c>
       <c r="X49">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y49">
         <v>13</v>
@@ -13568,7 +13568,7 @@
         <v>11.5</v>
       </c>
       <c r="AA49">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB49">
         <v>36</v>
@@ -13580,7 +13580,7 @@
         <v>13</v>
       </c>
       <c r="AE49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AF49">
         <v>80</v>
@@ -13589,22 +13589,22 @@
         <v>30</v>
       </c>
       <c r="AH49">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI49">
         <v>30</v>
       </c>
       <c r="AJ49">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AK49">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AL49">
         <v>75</v>
       </c>
       <c r="AM49">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN49">
         <v>85</v>
@@ -13613,7 +13613,7 @@
         <v>4.8</v>
       </c>
       <c r="AP49">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ49">
         <v>11</v>
@@ -13622,7 +13622,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS49">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT49">
         <v>34</v>
@@ -13634,13 +13634,13 @@
         <v>9.4</v>
       </c>
       <c r="AW49">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX49">
         <v>11.5</v>
       </c>
       <c r="AY49">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ49">
         <v>19</v>
@@ -13664,7 +13664,7 @@
         <v>55</v>
       </c>
       <c r="BG49">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -13759,7 +13759,7 @@
         <v>110</v>
       </c>
       <c r="J50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K50">
         <v>320</v>
@@ -13992,16 +13992,16 @@
         <v>1.06</v>
       </c>
       <c r="G51">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="H51">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="I51">
         <v>120</v>
       </c>
       <c r="J51">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="K51">
         <v>950</v>
@@ -14013,7 +14013,7 @@
         <v>1.01</v>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="O51">
         <v>1.29</v>
@@ -14040,7 +14040,7 @@
         <v>1.01</v>
       </c>
       <c r="W51">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -14231,19 +14231,19 @@
         <v>394</v>
       </c>
       <c r="F52">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G52">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="H52">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="I52">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J52">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="K52">
         <v>3.55</v>
@@ -14252,25 +14252,25 @@
         <v>1.01</v>
       </c>
       <c r="M52">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="O52">
         <v>1.35</v>
       </c>
       <c r="P52">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R52">
         <v>1.28</v>
       </c>
       <c r="S52">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T52">
         <v>1.01</v>
@@ -14279,10 +14279,10 @@
         <v>1.01</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X52">
         <v>1000</v>
@@ -14300,7 +14300,7 @@
         <v>1000</v>
       </c>
       <c r="AC52">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD52">
         <v>1000</v>
@@ -14339,58 +14339,58 @@
         <v>1000</v>
       </c>
       <c r="AP52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU52">
         <v>1.01</v>
       </c>
       <c r="AV52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG52">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH52">
         <v>1000</v>
@@ -14506,7 +14506,7 @@
         <v>1.25</v>
       </c>
       <c r="Q53">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R53">
         <v>1.04</v>
@@ -14984,19 +14984,19 @@
         <v>1.26</v>
       </c>
       <c r="O55">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P55">
         <v>1.25</v>
       </c>
       <c r="Q55">
+        <v>1.21</v>
+      </c>
+      <c r="R55">
+        <v>1.05</v>
+      </c>
+      <c r="S55">
         <v>1.2</v>
-      </c>
-      <c r="R55">
-        <v>1.06</v>
-      </c>
-      <c r="S55">
-        <v>1.19</v>
       </c>
       <c r="T55">
         <v>1.01</v>
@@ -15925,13 +15925,13 @@
         <v>401</v>
       </c>
       <c r="F59">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G59">
         <v>1.8</v>
       </c>
       <c r="H59">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I59">
         <v>6.6</v>
@@ -15940,7 +15940,7 @@
         <v>4.1</v>
       </c>
       <c r="K59">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="L59">
         <v>1.01</v>
@@ -15949,7 +15949,7 @@
         <v>1.04</v>
       </c>
       <c r="N59">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="O59">
         <v>1.21</v>
@@ -16170,7 +16170,7 @@
         <v>1.23</v>
       </c>
       <c r="G60">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H60">
         <v>14.5</v>
@@ -16197,10 +16197,10 @@
         <v>1.15</v>
       </c>
       <c r="P60">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R60">
         <v>1.56</v>
@@ -16218,7 +16218,7 @@
         <v>1.06</v>
       </c>
       <c r="W60">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -17138,7 +17138,7 @@
         <v>2.02</v>
       </c>
       <c r="G64">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H64">
         <v>4</v>
@@ -17150,13 +17150,13 @@
         <v>3.1</v>
       </c>
       <c r="K64">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L64">
         <v>1.01</v>
       </c>
       <c r="M64">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N64">
         <v>2.56</v>
@@ -17171,7 +17171,7 @@
         <v>2.58</v>
       </c>
       <c r="R64">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S64">
         <v>5</v>
@@ -17186,7 +17186,7 @@
         <v>1.24</v>
       </c>
       <c r="W64">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X64">
         <v>1000</v>
@@ -17243,52 +17243,52 @@
         <v>1000</v>
       </c>
       <c r="AP64">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AQ64">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AR64">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AS64">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AT64">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AU64">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AV64">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AW64">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AX64">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AY64">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AZ64">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA64">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BB64">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BC64">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD64">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BE64">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BF64">
         <v>1.01</v>
@@ -17864,7 +17864,7 @@
         <v>1.72</v>
       </c>
       <c r="G67">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H67">
         <v>4.9</v>
@@ -17906,7 +17906,7 @@
         <v>1.69</v>
       </c>
       <c r="U67">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V67">
         <v>1.22</v>
@@ -17921,7 +17921,7 @@
         <v>20</v>
       </c>
       <c r="Z67">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA67">
         <v>150</v>
@@ -17939,7 +17939,7 @@
         <v>70</v>
       </c>
       <c r="AF67">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG67">
         <v>10</v>
@@ -17966,7 +17966,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO67">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP67">
         <v>17</v>
@@ -17978,7 +17978,7 @@
         <v>36</v>
       </c>
       <c r="AS67">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT67">
         <v>8.4</v>
@@ -17987,7 +17987,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV67">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW67">
         <v>55</v>
@@ -18014,13 +18014,13 @@
         <v>27</v>
       </c>
       <c r="BE67">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF67">
         <v>8</v>
       </c>
       <c r="BG67">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="BH67">
         <v>1000</v>
@@ -18133,7 +18133,7 @@
         <v>1.26</v>
       </c>
       <c r="P68">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q68">
         <v>1.76</v>
@@ -18142,13 +18142,13 @@
         <v>1.44</v>
       </c>
       <c r="S68">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T68">
         <v>1.72</v>
       </c>
       <c r="U68">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V68">
         <v>1.27</v>
@@ -18611,7 +18611,7 @@
         <v>1.01</v>
       </c>
       <c r="N70">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O70">
         <v>1.32</v>
@@ -18847,7 +18847,7 @@
         <v>3.9</v>
       </c>
       <c r="L71">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M71">
         <v>1.07</v>
@@ -18991,16 +18991,16 @@
         <v>8.4</v>
       </c>
       <c r="BH71">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI71">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ71">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK71">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL71">
         <v>1000</v>
@@ -19009,40 +19009,40 @@
         <v>1.01</v>
       </c>
       <c r="BN71">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO71">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP71">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ71">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BR71">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS71">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT71">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU71">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV71">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW71">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BX71">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY71">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ71">
         <v>0</v>
@@ -19104,7 +19104,7 @@
         <v>2.14</v>
       </c>
       <c r="Q72">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R72">
         <v>1.45</v>
@@ -19149,7 +19149,7 @@
         <v>38</v>
       </c>
       <c r="AF72">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AG72">
         <v>12.5</v>
@@ -19158,7 +19158,7 @@
         <v>16.5</v>
       </c>
       <c r="AI72">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ72">
         <v>29</v>
@@ -19167,10 +19167,10 @@
         <v>22</v>
       </c>
       <c r="AL72">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM72">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN72">
         <v>14.5</v>
@@ -19185,7 +19185,7 @@
         <v>14</v>
       </c>
       <c r="AR72">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AS72">
         <v>11</v>
@@ -19313,22 +19313,22 @@
         <v>415</v>
       </c>
       <c r="F73">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="G73">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H73">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I73">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="J73">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K73">
-        <v>3.2</v>
+        <v>19</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -19337,16 +19337,16 @@
         <v>1.01</v>
       </c>
       <c r="N73">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="O73">
         <v>1.02</v>
       </c>
       <c r="P73">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="Q73">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R73">
         <v>1.13</v>
@@ -19358,13 +19358,13 @@
         <v>1.01</v>
       </c>
       <c r="U73">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V73">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W73">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X73">
         <v>11</v>
@@ -19558,16 +19558,16 @@
         <v>1.7</v>
       </c>
       <c r="G74">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H74">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I74">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J74">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K74">
         <v>4</v>
@@ -19576,19 +19576,19 @@
         <v>1.01</v>
       </c>
       <c r="M74">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N74">
         <v>3.55</v>
       </c>
       <c r="O74">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P74">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q74">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R74">
         <v>1.33</v>
@@ -19597,22 +19597,22 @@
         <v>3.45</v>
       </c>
       <c r="T74">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="U74">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="V74">
         <v>1.18</v>
       </c>
       <c r="W74">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X74">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y74">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="Z74">
         <v>60</v>
@@ -19621,19 +19621,19 @@
         <v>210</v>
       </c>
       <c r="AB74">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AC74">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD74">
         <v>29</v>
       </c>
       <c r="AE74">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF74">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AG74">
         <v>12.5</v>
@@ -19645,13 +19645,13 @@
         <v>110</v>
       </c>
       <c r="AJ74">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AK74">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL74">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM74">
         <v>160</v>
@@ -19666,13 +19666,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ74">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR74">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS74">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT74">
         <v>6.8</v>
@@ -19681,13 +19681,13 @@
         <v>7.4</v>
       </c>
       <c r="AV74">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW74">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX74">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY74">
         <v>8.6</v>
@@ -19696,7 +19696,7 @@
         <v>18</v>
       </c>
       <c r="BA74">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB74">
         <v>15</v>
@@ -19705,16 +19705,16 @@
         <v>16</v>
       </c>
       <c r="BD74">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BE74">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF74">
         <v>8.6</v>
       </c>
       <c r="BG74">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH74">
         <v>1000</v>
@@ -19806,19 +19806,19 @@
         <v>4.8</v>
       </c>
       <c r="I75">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="J75">
         <v>3.7</v>
       </c>
       <c r="K75">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L75">
         <v>1.01</v>
       </c>
       <c r="M75">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N75">
         <v>1.01</v>
@@ -19827,136 +19827,136 @@
         <v>1.35</v>
       </c>
       <c r="P75">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q75">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="R75">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S75">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="T75">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U75">
-        <v>1.98</v>
+        <v>1.04</v>
       </c>
       <c r="V75">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W75">
         <v>2.12</v>
       </c>
       <c r="X75">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y75">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z75">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA75">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB75">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC75">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD75">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE75">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF75">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG75">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH75">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI75">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ75">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK75">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL75">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM75">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN75">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO75">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP75">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ75">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR75">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS75">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT75">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU75">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV75">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW75">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX75">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY75">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ75">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BA75">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB75">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC75">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD75">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE75">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF75">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG75">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH75">
         <v>1000</v>
@@ -20284,163 +20284,163 @@
         <v>3.7</v>
       </c>
       <c r="G77">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H77">
         <v>1.91</v>
       </c>
       <c r="I77">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J77">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K77">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="L77">
         <v>1.01</v>
       </c>
       <c r="M77">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N77">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="P77">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q77">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="R77">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S77">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T77">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="U77">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V77">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W77">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X77">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y77">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z77">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA77">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB77">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC77">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD77">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE77">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF77">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG77">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH77">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI77">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ77">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK77">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL77">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM77">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN77">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO77">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP77">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ77">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR77">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS77">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AT77">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU77">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV77">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW77">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX77">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY77">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ77">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA77">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB77">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC77">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD77">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE77">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF77">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG77">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH77">
         <v>1000</v>
@@ -20523,7 +20523,7 @@
         <v>420</v>
       </c>
       <c r="F78">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G78">
         <v>1.92</v>
@@ -20547,16 +20547,16 @@
         <v>1.02</v>
       </c>
       <c r="N78">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="O78">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P78">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Q78">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="R78">
         <v>1.78</v>
@@ -20565,16 +20565,16 @@
         <v>2.16</v>
       </c>
       <c r="T78">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U78">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="V78">
         <v>1.32</v>
       </c>
       <c r="W78">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X78">
         <v>40</v>
@@ -20765,7 +20765,7 @@
         <v>421</v>
       </c>
       <c r="F79">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G79">
         <v>2</v>
@@ -20774,7 +20774,7 @@
         <v>3.45</v>
       </c>
       <c r="I79">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J79">
         <v>4.3</v>
@@ -20789,28 +20789,28 @@
         <v>1.02</v>
       </c>
       <c r="N79">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="O79">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P79">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="Q79">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="R79">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="S79">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="T79">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U79">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="V79">
         <v>1.35</v>
@@ -20819,112 +20819,112 @@
         <v>2</v>
       </c>
       <c r="X79">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="Y79">
+        <v>24</v>
+      </c>
+      <c r="Z79">
         <v>34</v>
       </c>
-      <c r="Z79">
-        <v>48</v>
-      </c>
       <c r="AA79">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB79">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AC79">
+        <v>11.5</v>
+      </c>
+      <c r="AD79">
+        <v>16.5</v>
+      </c>
+      <c r="AE79">
+        <v>34</v>
+      </c>
+      <c r="AF79">
+        <v>17.5</v>
+      </c>
+      <c r="AG79">
+        <v>12</v>
+      </c>
+      <c r="AH79">
+        <v>15</v>
+      </c>
+      <c r="AI79">
+        <v>34</v>
+      </c>
+      <c r="AJ79">
+        <v>25</v>
+      </c>
+      <c r="AK79">
+        <v>18</v>
+      </c>
+      <c r="AL79">
+        <v>24</v>
+      </c>
+      <c r="AM79">
+        <v>55</v>
+      </c>
+      <c r="AN79">
+        <v>7.8</v>
+      </c>
+      <c r="AO79">
+        <v>21</v>
+      </c>
+      <c r="AP79">
+        <v>9</v>
+      </c>
+      <c r="AQ79">
+        <v>21</v>
+      </c>
+      <c r="AR79">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS79">
+        <v>10.5</v>
+      </c>
+      <c r="AT79">
+        <v>14.5</v>
+      </c>
+      <c r="AU79">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV79">
+        <v>14.5</v>
+      </c>
+      <c r="AW79">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX79">
         <v>15.5</v>
       </c>
-      <c r="AD79">
-        <v>23</v>
-      </c>
-      <c r="AE79">
-        <v>48</v>
-      </c>
-      <c r="AF79">
-        <v>24</v>
-      </c>
-      <c r="AG79">
-        <v>16</v>
-      </c>
-      <c r="AH79">
-        <v>20</v>
-      </c>
-      <c r="AI79">
-        <v>48</v>
-      </c>
-      <c r="AJ79">
-        <v>34</v>
-      </c>
-      <c r="AK79">
-        <v>25</v>
-      </c>
-      <c r="AL79">
-        <v>32</v>
-      </c>
-      <c r="AM79">
-        <v>65</v>
-      </c>
-      <c r="AN79">
+      <c r="AY79">
+        <v>10.5</v>
+      </c>
+      <c r="AZ79">
+        <v>13</v>
+      </c>
+      <c r="BA79">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB79">
+        <v>21</v>
+      </c>
+      <c r="BC79">
+        <v>15.5</v>
+      </c>
+      <c r="BD79">
+        <v>21</v>
+      </c>
+      <c r="BE79">
         <v>10</v>
       </c>
-      <c r="AO79">
-        <v>1000</v>
-      </c>
-      <c r="AP79">
-        <v>2.66</v>
-      </c>
-      <c r="AQ79">
-        <v>17.5</v>
-      </c>
-      <c r="AR79">
-        <v>2.66</v>
-      </c>
-      <c r="AS79">
-        <v>2.74</v>
-      </c>
-      <c r="AT79">
-        <v>2.5</v>
-      </c>
-      <c r="AU79">
-        <v>2.38</v>
-      </c>
-      <c r="AV79">
-        <v>11</v>
-      </c>
-      <c r="AW79">
-        <v>2.66</v>
-      </c>
-      <c r="AX79">
-        <v>2.52</v>
-      </c>
-      <c r="AY79">
-        <v>2.4</v>
-      </c>
-      <c r="AZ79">
-        <v>10.5</v>
-      </c>
-      <c r="BA79">
-        <v>2.66</v>
-      </c>
-      <c r="BB79">
-        <v>2.6</v>
-      </c>
-      <c r="BC79">
-        <v>2.54</v>
-      </c>
-      <c r="BD79">
-        <v>2.58</v>
-      </c>
-      <c r="BE79">
-        <v>2.7</v>
-      </c>
       <c r="BF79">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG79">
-        <v>2.82</v>
+        <v>15.5</v>
       </c>
       <c r="BH79">
         <v>1000</v>
@@ -21031,19 +21031,19 @@
         <v>1.05</v>
       </c>
       <c r="N80">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O80">
         <v>1.25</v>
       </c>
       <c r="P80">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q80">
         <v>1.74</v>
       </c>
       <c r="R80">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S80">
         <v>2.86</v>
@@ -21070,7 +21070,7 @@
         <v>22</v>
       </c>
       <c r="AA80">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB80">
         <v>13</v>
@@ -21100,7 +21100,7 @@
         <v>40</v>
       </c>
       <c r="AK80">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL80">
         <v>36</v>
@@ -21252,10 +21252,10 @@
         <v>1.51</v>
       </c>
       <c r="G81">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H81">
-        <v>6.2</v>
+        <v>1.08</v>
       </c>
       <c r="I81">
         <v>14</v>
@@ -21264,7 +21264,7 @@
         <v>4.3</v>
       </c>
       <c r="K81">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L81">
         <v>1.01</v>
@@ -21763,7 +21763,7 @@
         <v>1.26</v>
       </c>
       <c r="P83">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q83">
         <v>1.76</v>
@@ -21772,7 +21772,7 @@
         <v>1.45</v>
       </c>
       <c r="S83">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T83">
         <v>1.87</v>
@@ -22005,7 +22005,7 @@
         <v>1.15</v>
       </c>
       <c r="P84">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q84">
         <v>1.5</v>
@@ -22220,16 +22220,16 @@
         <v>2.18</v>
       </c>
       <c r="G85">
-        <v>3.15</v>
+        <v>110</v>
       </c>
       <c r="H85">
         <v>2.28</v>
       </c>
       <c r="I85">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J85">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="K85">
         <v>5.4</v>
@@ -22256,7 +22256,7 @@
         <v>1.5</v>
       </c>
       <c r="S85">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="T85">
         <v>1.01</v>
@@ -22459,13 +22459,13 @@
         <v>428</v>
       </c>
       <c r="F86">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G86">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H86">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I86">
         <v>2.38</v>
@@ -22498,7 +22498,7 @@
         <v>1.7</v>
       </c>
       <c r="S86">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T86">
         <v>1.5</v>
@@ -22507,10 +22507,10 @@
         <v>2.74</v>
       </c>
       <c r="V86">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W86">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X86">
         <v>32</v>
@@ -22525,7 +22525,7 @@
         <v>32</v>
       </c>
       <c r="AB86">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC86">
         <v>10.5</v>
@@ -22546,7 +22546,7 @@
         <v>16.5</v>
       </c>
       <c r="AI86">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ86">
         <v>55</v>
@@ -22603,13 +22603,13 @@
         <v>20</v>
       </c>
       <c r="BB86">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC86">
         <v>5.2</v>
       </c>
       <c r="BD86">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE86">
         <v>5.6</v>
@@ -22713,7 +22713,7 @@
         <v>110</v>
       </c>
       <c r="J87">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="K87">
         <v>170</v>
@@ -23185,7 +23185,7 @@
         <v>431</v>
       </c>
       <c r="F89">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G89">
         <v>1.72</v>
@@ -23200,19 +23200,19 @@
         <v>4</v>
       </c>
       <c r="K89">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L89">
         <v>1.01</v>
       </c>
       <c r="M89">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N89">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O89">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P89">
         <v>1.97</v>
@@ -23224,127 +23224,127 @@
         <v>1.38</v>
       </c>
       <c r="S89">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T89">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="U89">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V89">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W89">
         <v>2.38</v>
       </c>
       <c r="X89">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y89">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z89">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA89">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB89">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC89">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD89">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE89">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF89">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG89">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH89">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI89">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ89">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK89">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL89">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM89">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN89">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO89">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP89">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ89">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR89">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS89">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="AT89">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU89">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV89">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW89">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AX89">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY89">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ89">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA89">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB89">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC89">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD89">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE89">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BF89">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG89">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH89">
         <v>1000</v>
@@ -23493,7 +23493,7 @@
         <v>65</v>
       </c>
       <c r="AB90">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC90">
         <v>12</v>
@@ -23508,7 +23508,7 @@
         <v>20</v>
       </c>
       <c r="AG90">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH90">
         <v>18</v>
@@ -23544,7 +23544,7 @@
         <v>19.5</v>
       </c>
       <c r="AS90">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT90">
         <v>10.5</v>
@@ -23580,7 +23580,7 @@
         <v>19.5</v>
       </c>
       <c r="BE90">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF90">
         <v>9</v>
@@ -23693,10 +23693,10 @@
         <v>1.01</v>
       </c>
       <c r="N91">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="O91">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="P91">
         <v>3.6</v>
@@ -23705,10 +23705,10 @@
         <v>1.3</v>
       </c>
       <c r="R91">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S91">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="T91">
         <v>1.45</v>
@@ -23914,40 +23914,40 @@
         <v>1.45</v>
       </c>
       <c r="G92">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H92">
         <v>5.5</v>
       </c>
       <c r="I92">
+        <v>7.6</v>
+      </c>
+      <c r="J92">
+        <v>5.3</v>
+      </c>
+      <c r="K92">
+        <v>6.4</v>
+      </c>
+      <c r="L92">
+        <v>1.01</v>
+      </c>
+      <c r="M92">
+        <v>1.01</v>
+      </c>
+      <c r="N92">
         <v>7.8</v>
-      </c>
-      <c r="J92">
-        <v>4.2</v>
-      </c>
-      <c r="K92">
-        <v>8</v>
-      </c>
-      <c r="L92">
-        <v>1.01</v>
-      </c>
-      <c r="M92">
-        <v>1.01</v>
-      </c>
-      <c r="N92">
-        <v>1.01</v>
       </c>
       <c r="O92">
         <v>1.06</v>
       </c>
       <c r="P92">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q92">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S92">
         <v>1.74</v>
@@ -24395,19 +24395,19 @@
         <v>436</v>
       </c>
       <c r="F94">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="G94">
         <v>1.43</v>
       </c>
       <c r="H94">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="I94">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="J94">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="K94">
         <v>330</v>
@@ -24431,19 +24431,19 @@
         <v>1.22</v>
       </c>
       <c r="R94">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S94">
         <v>1.6</v>
       </c>
       <c r="T94">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="U94">
         <v>1.01</v>
       </c>
       <c r="V94">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W94">
         <v>3.35</v>
@@ -24640,7 +24640,7 @@
         <v>1.58</v>
       </c>
       <c r="G95">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H95">
         <v>6</v>
@@ -24685,7 +24685,7 @@
         <v>2.22</v>
       </c>
       <c r="V95">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W95">
         <v>2.58</v>
@@ -25366,10 +25366,10 @@
         <v>1.09</v>
       </c>
       <c r="G98">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="H98">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="I98">
         <v>970</v>
@@ -25605,22 +25605,22 @@
         <v>441</v>
       </c>
       <c r="F99">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G99">
         <v>1.36</v>
       </c>
       <c r="H99">
-        <v>9.4</v>
+        <v>3.8</v>
       </c>
       <c r="I99">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="J99">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="K99">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L99">
         <v>1.01</v>
@@ -25653,10 +25653,10 @@
         <v>1.87</v>
       </c>
       <c r="V99">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W99">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="X99">
         <v>1000</v>
@@ -25889,7 +25889,7 @@
         <v>2.76</v>
       </c>
       <c r="T100">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U100">
         <v>1.01</v>
@@ -26089,22 +26089,22 @@
         <v>443</v>
       </c>
       <c r="F101">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="G101">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="H101">
-        <v>5.1</v>
+        <v>2.22</v>
       </c>
       <c r="I101">
         <v>110</v>
       </c>
       <c r="J101">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="K101">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L101">
         <v>1.01</v>
@@ -26113,22 +26113,22 @@
         <v>1.01</v>
       </c>
       <c r="N101">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="O101">
         <v>1.26</v>
       </c>
       <c r="P101">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="Q101">
-        <v>1.84</v>
+        <v>1.26</v>
       </c>
       <c r="R101">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="S101">
-        <v>3</v>
+        <v>1.26</v>
       </c>
       <c r="T101">
         <v>1.01</v>
@@ -26137,10 +26137,10 @@
         <v>1.01</v>
       </c>
       <c r="V101">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W101">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X101">
         <v>1000</v>
@@ -26364,7 +26364,7 @@
         <v>1.72</v>
       </c>
       <c r="Q102">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="R102">
         <v>1.26</v>
@@ -26815,22 +26815,22 @@
         <v>446</v>
       </c>
       <c r="F104">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="G104">
-        <v>2.16</v>
+        <v>110</v>
       </c>
       <c r="H104">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="I104">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="J104">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="K104">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L104">
         <v>1.01</v>
@@ -26839,22 +26839,22 @@
         <v>1.01</v>
       </c>
       <c r="N104">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O104">
         <v>1.18</v>
       </c>
       <c r="P104">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="Q104">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="R104">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="S104">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
         <v>1.01</v>
@@ -26863,13 +26863,13 @@
         <v>1.01</v>
       </c>
       <c r="V104">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W104">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="X104">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y104">
         <v>1000</v>
@@ -26881,31 +26881,31 @@
         <v>1000</v>
       </c>
       <c r="AB104">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC104">
         <v>1000</v>
       </c>
       <c r="AD104">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE104">
         <v>1000</v>
       </c>
       <c r="AF104">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG104">
         <v>1000</v>
       </c>
       <c r="AH104">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI104">
         <v>1000</v>
       </c>
       <c r="AJ104">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK104">
         <v>1000</v>
@@ -26923,58 +26923,58 @@
         <v>1000</v>
       </c>
       <c r="AP104">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AR104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AS104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AT104">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AV104">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AW104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AX104">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="AY104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AZ104">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="BA104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BB104">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BD104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BE104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BF104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BG104">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BH104">
         <v>1000</v>
@@ -27057,7 +27057,7 @@
         <v>447</v>
       </c>
       <c r="F105">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G105">
         <v>1.8</v>
@@ -27066,13 +27066,13 @@
         <v>4.7</v>
       </c>
       <c r="I105">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J105">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K105">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L105">
         <v>1.01</v>
@@ -27081,31 +27081,31 @@
         <v>1.04</v>
       </c>
       <c r="N105">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="O105">
         <v>1.25</v>
       </c>
       <c r="P105">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q105">
         <v>1.64</v>
       </c>
       <c r="R105">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S105">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="T105">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U105">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V105">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W105">
         <v>2.24</v>
@@ -27132,7 +27132,7 @@
         <v>21</v>
       </c>
       <c r="AE105">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF105">
         <v>12</v>
@@ -27162,7 +27162,7 @@
         <v>11</v>
       </c>
       <c r="AO105">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AP105">
         <v>15.5</v>
@@ -27204,7 +27204,7 @@
         <v>17</v>
       </c>
       <c r="BC105">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD105">
         <v>1.01</v>
@@ -27338,7 +27338,7 @@
         <v>1.38</v>
       </c>
       <c r="S106">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T106">
         <v>1.01</v>
@@ -28790,7 +28790,7 @@
         <v>1.38</v>
       </c>
       <c r="S112">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T112">
         <v>1.84</v>
@@ -28811,16 +28811,16 @@
         <v>10.5</v>
       </c>
       <c r="Z112">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AA112">
         <v>24</v>
       </c>
       <c r="AB112">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AC112">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD112">
         <v>13</v>
@@ -28883,7 +28883,7 @@
         <v>16.5</v>
       </c>
       <c r="AX112">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY112">
         <v>17</v>
@@ -28892,22 +28892,22 @@
         <v>18</v>
       </c>
       <c r="BA112">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB112">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC112">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BD112">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE112">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF112">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG112">
         <v>9.800000000000001</v>
@@ -29301,7 +29301,7 @@
         <v>32</v>
       </c>
       <c r="AB114">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC114">
         <v>9</v>
@@ -29477,22 +29477,22 @@
         <v>457</v>
       </c>
       <c r="F115">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="G115">
-        <v>4.2</v>
+        <v>110</v>
       </c>
       <c r="H115">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="I115">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="J115">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="K115">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L115">
         <v>1.01</v>
@@ -29501,22 +29501,22 @@
         <v>1.02</v>
       </c>
       <c r="N115">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O115">
         <v>1.39</v>
       </c>
       <c r="P115">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q115">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="R115">
         <v>1.2</v>
       </c>
       <c r="S115">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="T115">
         <v>1.92</v>
@@ -29525,10 +29525,10 @@
         <v>1.94</v>
       </c>
       <c r="V115">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W115">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="X115">
         <v>13.5</v>
@@ -29961,7 +29961,7 @@
         <v>459</v>
       </c>
       <c r="F117">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G117">
         <v>2.44</v>
@@ -30009,7 +30009,7 @@
         <v>1.01</v>
       </c>
       <c r="V117">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W117">
         <v>1.69</v>
@@ -30445,22 +30445,22 @@
         <v>461</v>
       </c>
       <c r="F119">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="G119">
-        <v>2.14</v>
+        <v>110</v>
       </c>
       <c r="H119">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="I119">
-        <v>5.2</v>
+        <v>970</v>
       </c>
       <c r="J119">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="K119">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L119">
         <v>1.01</v>
@@ -30469,22 +30469,22 @@
         <v>1.01</v>
       </c>
       <c r="N119">
-        <v>2.92</v>
+        <v>1.24</v>
       </c>
       <c r="O119">
         <v>1.34</v>
       </c>
       <c r="P119">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q119">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="R119">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S119">
-        <v>3.25</v>
+        <v>1.34</v>
       </c>
       <c r="T119">
         <v>1.01</v>
@@ -30493,10 +30493,10 @@
         <v>1.01</v>
       </c>
       <c r="V119">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W119">
-        <v>1.88</v>
+        <v>1.02</v>
       </c>
       <c r="X119">
         <v>1000</v>
@@ -31276,7 +31276,7 @@
         <v>12</v>
       </c>
       <c r="AO122">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP122">
         <v>13</v>
@@ -31900,7 +31900,7 @@
         <v>1.19</v>
       </c>
       <c r="G125">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H125">
         <v>18</v>
@@ -31909,7 +31909,7 @@
         <v>22</v>
       </c>
       <c r="J125">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="K125">
         <v>9.6</v>
@@ -31927,10 +31927,10 @@
         <v>1.19</v>
       </c>
       <c r="P125">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q125">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="R125">
         <v>1.6</v>
@@ -31948,7 +31948,7 @@
         <v>1.04</v>
       </c>
       <c r="W125">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="X125">
         <v>34</v>
@@ -31972,7 +31972,7 @@
         <v>85</v>
       </c>
       <c r="AE125">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="AF125">
         <v>7.6</v>
@@ -32020,7 +32020,7 @@
         <v>8</v>
       </c>
       <c r="AU125">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AV125">
         <v>8.6</v>
@@ -32178,10 +32178,10 @@
         <v>1.3</v>
       </c>
       <c r="S126">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T126">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="U126">
         <v>1.9</v>
@@ -32193,13 +32193,13 @@
         <v>2.12</v>
       </c>
       <c r="X126">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y126">
         <v>16</v>
       </c>
       <c r="Z126">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA126">
         <v>160</v>
@@ -32214,7 +32214,7 @@
         <v>21</v>
       </c>
       <c r="AE126">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AF126">
         <v>11</v>
@@ -32253,10 +32253,10 @@
         <v>13.5</v>
       </c>
       <c r="AR126">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AS126">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT126">
         <v>6.8</v>
@@ -32265,10 +32265,10 @@
         <v>7.4</v>
       </c>
       <c r="AV126">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW126">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX126">
         <v>9.199999999999999</v>
@@ -32277,28 +32277,28 @@
         <v>9</v>
       </c>
       <c r="AZ126">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BA126">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB126">
         <v>17.5</v>
       </c>
       <c r="BC126">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BD126">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE126">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF126">
         <v>11</v>
       </c>
       <c r="BG126">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH126">
         <v>1000</v>
@@ -32411,10 +32411,10 @@
         <v>1.16</v>
       </c>
       <c r="P127">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q127">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R127">
         <v>1.73</v>
@@ -32489,7 +32489,7 @@
         <v>6.8</v>
       </c>
       <c r="AP127">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AQ127">
         <v>11.5</v>
@@ -32513,7 +32513,7 @@
         <v>12.5</v>
       </c>
       <c r="AX127">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="AY127">
         <v>15.5</v>
@@ -32528,7 +32528,7 @@
         <v>9.4</v>
       </c>
       <c r="BC127">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BD127">
         <v>8.4</v>
@@ -32632,7 +32632,7 @@
         <v>3.4</v>
       </c>
       <c r="I128">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J128">
         <v>3.1</v>
@@ -32656,10 +32656,10 @@
         <v>1.62</v>
       </c>
       <c r="Q128">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R128">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="S128">
         <v>4.1</v>
@@ -33352,16 +33352,16 @@
         <v>1.04</v>
       </c>
       <c r="G131">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="H131">
-        <v>2.46</v>
+        <v>1.06</v>
       </c>
       <c r="I131">
         <v>1000</v>
       </c>
       <c r="J131">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K131">
         <v>110</v>
@@ -33373,13 +33373,13 @@
         <v>1.01</v>
       </c>
       <c r="N131">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O131">
         <v>1.3</v>
       </c>
       <c r="P131">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q131">
         <v>1.9</v>
@@ -33400,7 +33400,7 @@
         <v>1.01</v>
       </c>
       <c r="W131">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="X131">
         <v>1000</v>
@@ -34317,19 +34317,19 @@
         <v>477</v>
       </c>
       <c r="F135">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="G135">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="H135">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I135">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J135">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K135">
         <v>2.94</v>
@@ -34347,10 +34347,10 @@
         <v>1.01</v>
       </c>
       <c r="P135">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q135">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="R135">
         <v>1.12</v>
@@ -34371,7 +34371,7 @@
         <v>1.01</v>
       </c>
       <c r="X135">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="Y135">
         <v>1000</v>
@@ -34428,55 +34428,55 @@
         <v>5</v>
       </c>
       <c r="AQ135">
-        <v>1.19</v>
+        <v>5.7</v>
       </c>
       <c r="AR135">
-        <v>1.19</v>
+        <v>14</v>
       </c>
       <c r="AS135">
-        <v>1.19</v>
+        <v>42</v>
       </c>
       <c r="AT135">
-        <v>1.19</v>
+        <v>5.7</v>
       </c>
       <c r="AU135">
-        <v>1.19</v>
+        <v>5.8</v>
       </c>
       <c r="AV135">
-        <v>1.19</v>
+        <v>14</v>
       </c>
       <c r="AW135">
-        <v>1.19</v>
+        <v>46</v>
       </c>
       <c r="AX135">
-        <v>1.19</v>
+        <v>13.5</v>
       </c>
       <c r="AY135">
-        <v>1.19</v>
+        <v>13.5</v>
       </c>
       <c r="AZ135">
-        <v>1.19</v>
+        <v>26</v>
       </c>
       <c r="BA135">
-        <v>1.19</v>
+        <v>90</v>
       </c>
       <c r="BB135">
-        <v>1.19</v>
+        <v>42</v>
       </c>
       <c r="BC135">
-        <v>1.19</v>
+        <v>44</v>
       </c>
       <c r="BD135">
-        <v>1.19</v>
+        <v>95</v>
       </c>
       <c r="BE135">
-        <v>1.19</v>
+        <v>100</v>
       </c>
       <c r="BF135">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BG135">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BH135">
         <v>1000</v>
@@ -35052,10 +35052,10 @@
         <v>5</v>
       </c>
       <c r="I138">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J138">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K138">
         <v>10.5</v>
@@ -35091,7 +35091,7 @@
         <v>1.01</v>
       </c>
       <c r="V138">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W138">
         <v>2.5</v>
@@ -35285,7 +35285,7 @@
         <v>481</v>
       </c>
       <c r="F139">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G139">
         <v>3.05</v>
@@ -35530,13 +35530,13 @@
         <v>6.6</v>
       </c>
       <c r="G140">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H140">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="I140">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J140">
         <v>4.2</v>
@@ -35557,7 +35557,7 @@
         <v>0</v>
       </c>
       <c r="P140">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q140">
         <v>1.86</v>
@@ -36011,22 +36011,22 @@
         <v>484</v>
       </c>
       <c r="F142">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G142">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H142">
         <v>3.55</v>
       </c>
       <c r="I142">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J142">
         <v>3.6</v>
       </c>
       <c r="K142">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="L142">
         <v>1.01</v>
@@ -36035,7 +36035,7 @@
         <v>1.01</v>
       </c>
       <c r="N142">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="O142">
         <v>1.2</v>
@@ -36044,10 +36044,10 @@
         <v>2.12</v>
       </c>
       <c r="Q142">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R142">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S142">
         <v>2.56</v>
@@ -36059,10 +36059,10 @@
         <v>1.01</v>
       </c>
       <c r="V142">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W142">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X142">
         <v>1000</v>
@@ -37469,7 +37469,7 @@
         <v>1.5</v>
       </c>
       <c r="H148">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="I148">
         <v>20</v>
@@ -37478,7 +37478,7 @@
         <v>4.8</v>
       </c>
       <c r="K148">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L148">
         <v>1.01</v>
@@ -38431,13 +38431,13 @@
         <v>494</v>
       </c>
       <c r="F152">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G152">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H152">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I152">
         <v>110</v>
@@ -38470,7 +38470,7 @@
         <v>1.17</v>
       </c>
       <c r="S152">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="T152">
         <v>1.01</v>
@@ -38694,7 +38694,7 @@
         <v>1.01</v>
       </c>
       <c r="M153">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N153">
         <v>2.58</v>
@@ -38915,16 +38915,16 @@
         <v>496</v>
       </c>
       <c r="F154">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G154">
         <v>2.7</v>
       </c>
       <c r="H154">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I154">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J154">
         <v>3.4</v>
@@ -38939,7 +38939,7 @@
         <v>1.01</v>
       </c>
       <c r="N154">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O154">
         <v>1.35</v>
@@ -38951,7 +38951,7 @@
         <v>1.49</v>
       </c>
       <c r="R154">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S154">
         <v>3.6</v>
@@ -38963,10 +38963,10 @@
         <v>2</v>
       </c>
       <c r="V154">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W154">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X154">
         <v>1000</v>
@@ -39160,19 +39160,19 @@
         <v>2.02</v>
       </c>
       <c r="G155">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H155">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I155">
         <v>4.1</v>
       </c>
       <c r="J155">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K155">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L155">
         <v>1.01</v>
@@ -39199,7 +39199,7 @@
         <v>3.3</v>
       </c>
       <c r="T155">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U155">
         <v>2.12</v>
@@ -39208,7 +39208,7 @@
         <v>1.32</v>
       </c>
       <c r="W155">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X155">
         <v>16</v>
@@ -39256,7 +39256,7 @@
         <v>36</v>
       </c>
       <c r="AM155">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN155">
         <v>14.5</v>
@@ -39271,7 +39271,7 @@
         <v>13</v>
       </c>
       <c r="AR155">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS155">
         <v>10</v>
@@ -39286,7 +39286,7 @@
         <v>14.5</v>
       </c>
       <c r="AW155">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX155">
         <v>11</v>
@@ -39298,7 +39298,7 @@
         <v>16</v>
       </c>
       <c r="BA155">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB155">
         <v>21</v>
@@ -39316,7 +39316,7 @@
         <v>10.5</v>
       </c>
       <c r="BG155">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH155">
         <v>1000</v>
@@ -39402,13 +39402,13 @@
         <v>1.58</v>
       </c>
       <c r="G156">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H156">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I156">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J156">
         <v>4</v>
@@ -39444,13 +39444,13 @@
         <v>2</v>
       </c>
       <c r="U156">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V156">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W156">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X156">
         <v>14.5</v>
@@ -39462,7 +39462,7 @@
         <v>60</v>
       </c>
       <c r="AA156">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB156">
         <v>7.8</v>
@@ -39474,7 +39474,7 @@
         <v>28</v>
       </c>
       <c r="AE156">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF156">
         <v>9</v>
@@ -39504,7 +39504,7 @@
         <v>11</v>
       </c>
       <c r="AO156">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP156">
         <v>12</v>
@@ -39641,22 +39641,22 @@
         <v>499</v>
       </c>
       <c r="F157">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="G157">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H157">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="I157">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J157">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="K157">
-        <v>3.5</v>
+        <v>180</v>
       </c>
       <c r="L157">
         <v>1.01</v>
@@ -39665,22 +39665,22 @@
         <v>1.01</v>
       </c>
       <c r="N157">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="O157">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P157">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="Q157">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="R157">
         <v>1.17</v>
       </c>
       <c r="S157">
-        <v>2.28</v>
+        <v>1.51</v>
       </c>
       <c r="T157">
         <v>1.01</v>
@@ -39689,10 +39689,10 @@
         <v>1.01</v>
       </c>
       <c r="V157">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W157">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X157">
         <v>1000</v>
@@ -39883,22 +39883,22 @@
         <v>500</v>
       </c>
       <c r="F158">
+        <v>1.11</v>
+      </c>
+      <c r="G158">
         <v>1.12</v>
       </c>
-      <c r="G158">
-        <v>1.13</v>
-      </c>
       <c r="H158">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I158">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J158">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="K158">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L158">
         <v>1.01</v>
@@ -39910,7 +39910,7 @@
         <v>6.4</v>
       </c>
       <c r="O158">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P158">
         <v>2.92</v>
@@ -39922,19 +39922,19 @@
         <v>1.76</v>
       </c>
       <c r="S158">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T158">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="U158">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V158">
         <v>1.03</v>
       </c>
       <c r="W158">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X158">
         <v>48</v>
@@ -39943,7 +39943,7 @@
         <v>95</v>
       </c>
       <c r="Z158">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="AA158">
         <v>1000</v>
@@ -39952,10 +39952,10 @@
         <v>11</v>
       </c>
       <c r="AC158">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AD158">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AE158">
         <v>1000</v>
@@ -39967,22 +39967,22 @@
         <v>17</v>
       </c>
       <c r="AH158">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AI158">
-        <v>530</v>
+        <v>590</v>
       </c>
       <c r="AJ158">
         <v>8</v>
       </c>
       <c r="AK158">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL158">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM158">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AN158">
         <v>3.25</v>
@@ -39994,10 +39994,10 @@
         <v>6.2</v>
       </c>
       <c r="AQ158">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR158">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS158">
         <v>7.2</v>
@@ -40006,7 +40006,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU158">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV158">
         <v>6.8</v>
@@ -40018,19 +40018,19 @@
         <v>6.2</v>
       </c>
       <c r="AY158">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AZ158">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA158">
         <v>7.2</v>
       </c>
       <c r="BB158">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC158">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD158">
         <v>6.6</v>
@@ -40128,19 +40128,19 @@
         <v>5.6</v>
       </c>
       <c r="G159">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H159">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I159">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J159">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K159">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L159">
         <v>1.01</v>
@@ -40149,58 +40149,58 @@
         <v>1.07</v>
       </c>
       <c r="N159">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O159">
         <v>1.32</v>
       </c>
       <c r="P159">
+        <v>1.95</v>
+      </c>
+      <c r="Q159">
+        <v>1.87</v>
+      </c>
+      <c r="R159">
+        <v>1.38</v>
+      </c>
+      <c r="S159">
+        <v>3</v>
+      </c>
+      <c r="T159">
         <v>1.94</v>
       </c>
-      <c r="Q159">
-        <v>1.96</v>
-      </c>
-      <c r="R159">
-        <v>1.37</v>
-      </c>
-      <c r="S159">
-        <v>3.4</v>
-      </c>
-      <c r="T159">
-        <v>1.91</v>
-      </c>
       <c r="U159">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V159">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="W159">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X159">
+        <v>17</v>
+      </c>
+      <c r="Y159">
+        <v>8</v>
+      </c>
+      <c r="Z159">
+        <v>10.5</v>
+      </c>
+      <c r="AA159">
         <v>17.5</v>
       </c>
-      <c r="Y159">
-        <v>8.4</v>
-      </c>
-      <c r="Z159">
-        <v>11</v>
-      </c>
-      <c r="AA159">
-        <v>19</v>
-      </c>
       <c r="AB159">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC159">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD159">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE159">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF159">
         <v>46</v>
@@ -40215,28 +40215,28 @@
         <v>40</v>
       </c>
       <c r="AJ159">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AK159">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL159">
+        <v>95</v>
+      </c>
+      <c r="AM159">
+        <v>150</v>
+      </c>
+      <c r="AN159">
         <v>110</v>
       </c>
-      <c r="AM159">
-        <v>160</v>
-      </c>
-      <c r="AN159">
-        <v>130</v>
-      </c>
       <c r="AO159">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP159">
         <v>12</v>
       </c>
       <c r="AQ159">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR159">
         <v>8.800000000000001</v>
@@ -40245,46 +40245,46 @@
         <v>15</v>
       </c>
       <c r="AT159">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU159">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV159">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW159">
         <v>16.5</v>
       </c>
       <c r="AX159">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="AY159">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ159">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA159">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BB159">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC159">
-        <v>7.4</v>
+        <v>65</v>
       </c>
       <c r="BD159">
-        <v>7.4</v>
+        <v>65</v>
       </c>
       <c r="BE159">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF159">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG159">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH159">
         <v>1000</v>
@@ -40367,13 +40367,13 @@
         <v>502</v>
       </c>
       <c r="F160">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G160">
         <v>2.08</v>
       </c>
       <c r="H160">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I160">
         <v>4.7</v>
@@ -40391,28 +40391,28 @@
         <v>1.07</v>
       </c>
       <c r="N160">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="O160">
         <v>1.31</v>
       </c>
       <c r="P160">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q160">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="R160">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S160">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T160">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U160">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V160">
         <v>1.27</v>
@@ -40421,112 +40421,112 @@
         <v>1.92</v>
       </c>
       <c r="X160">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y160">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z160">
         <v>38</v>
       </c>
       <c r="AA160">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB160">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC160">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD160">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE160">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF160">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG160">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH160">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI160">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ160">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK160">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL160">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM160">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN160">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO160">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP160">
-        <v>1.24</v>
+        <v>12</v>
       </c>
       <c r="AQ160">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR160">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="AS160">
-        <v>1.24</v>
+        <v>5.6</v>
       </c>
       <c r="AT160">
-        <v>1.11</v>
+        <v>7.8</v>
       </c>
       <c r="AU160">
-        <v>1.24</v>
+        <v>7.2</v>
       </c>
       <c r="AV160">
-        <v>1.24</v>
+        <v>15.5</v>
       </c>
       <c r="AW160">
-        <v>1.24</v>
+        <v>5.4</v>
       </c>
       <c r="AX160">
-        <v>1.24</v>
+        <v>11</v>
       </c>
       <c r="AY160">
-        <v>1.24</v>
+        <v>9</v>
       </c>
       <c r="AZ160">
-        <v>1.24</v>
+        <v>16</v>
       </c>
       <c r="BA160">
-        <v>1.24</v>
+        <v>5.5</v>
       </c>
       <c r="BB160">
-        <v>1.24</v>
+        <v>21</v>
       </c>
       <c r="BC160">
-        <v>1.24</v>
+        <v>19.5</v>
       </c>
       <c r="BD160">
-        <v>1.21</v>
+        <v>5.1</v>
       </c>
       <c r="BE160">
-        <v>1.24</v>
+        <v>5.6</v>
       </c>
       <c r="BF160">
-        <v>1.24</v>
+        <v>12</v>
       </c>
       <c r="BG160">
-        <v>1.24</v>
+        <v>5.5</v>
       </c>
       <c r="BH160">
         <v>1000</v>
@@ -40851,22 +40851,22 @@
         <v>504</v>
       </c>
       <c r="F162">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="G162">
-        <v>2.18</v>
+        <v>8.6</v>
       </c>
       <c r="H162">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="I162">
         <v>1000</v>
       </c>
       <c r="J162">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="K162">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="L162">
         <v>1.01</v>
@@ -40875,22 +40875,22 @@
         <v>1.01</v>
       </c>
       <c r="N162">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O162">
         <v>1.16</v>
       </c>
       <c r="P162">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q162">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="R162">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="S162">
-        <v>2.1</v>
+        <v>1.16</v>
       </c>
       <c r="T162">
         <v>1.01</v>
@@ -40902,7 +40902,7 @@
         <v>1.01</v>
       </c>
       <c r="W162">
-        <v>1.13</v>
+        <v>1.83</v>
       </c>
       <c r="X162">
         <v>1000</v>
@@ -41093,58 +41093,58 @@
         <v>505</v>
       </c>
       <c r="F163">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G163">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H163">
         <v>3.55</v>
       </c>
       <c r="I163">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J163">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="K163">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L163">
         <v>1.01</v>
       </c>
       <c r="M163">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N163">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O163">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="P163">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="Q163">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R163">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="S163">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="T163">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="U163">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="V163">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="W163">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X163">
         <v>9.199999999999999</v>
@@ -41153,7 +41153,7 @@
         <v>11.5</v>
       </c>
       <c r="Z163">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA163">
         <v>100</v>
@@ -41165,10 +41165,10 @@
         <v>7.8</v>
       </c>
       <c r="AD163">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE163">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF163">
         <v>14.5</v>
@@ -41201,7 +41201,7 @@
         <v>110</v>
       </c>
       <c r="AP163">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ163">
         <v>8.6</v>
@@ -41210,7 +41210,7 @@
         <v>21</v>
       </c>
       <c r="AS163">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT163">
         <v>6.4</v>
@@ -41222,7 +41222,7 @@
         <v>13.5</v>
       </c>
       <c r="AW163">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX163">
         <v>11.5</v>
@@ -41234,25 +41234,25 @@
         <v>20</v>
       </c>
       <c r="BA163">
+        <v>6.6</v>
+      </c>
+      <c r="BB163">
+        <v>6</v>
+      </c>
+      <c r="BC163">
+        <v>6</v>
+      </c>
+      <c r="BD163">
         <v>6.4</v>
       </c>
-      <c r="BB163">
-        <v>5.8</v>
-      </c>
-      <c r="BC163">
-        <v>5.9</v>
-      </c>
-      <c r="BD163">
-        <v>6.2</v>
-      </c>
       <c r="BE163">
+        <v>6.8</v>
+      </c>
+      <c r="BF163">
+        <v>6</v>
+      </c>
+      <c r="BG163">
         <v>6.6</v>
-      </c>
-      <c r="BF163">
-        <v>5.8</v>
-      </c>
-      <c r="BG163">
-        <v>6.4</v>
       </c>
       <c r="BH163">
         <v>1000</v>
@@ -41335,7 +41335,7 @@
         <v>506</v>
       </c>
       <c r="F164">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G164">
         <v>1.92</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-09.xlsx
@@ -1645,7 +1645,7 @@
     <t>Estrella Roja</t>
   </si>
   <si>
-    <t>2026-08-08 01:34:43</t>
+    <t>2026-08-08 03:59:30</t>
   </si>
 </sst>
 </file>
@@ -2239,10 +2239,10 @@
         <v>365</v>
       </c>
       <c r="F2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
         <v>3.25</v>
@@ -2263,25 +2263,25 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
         <v>2.14</v>
@@ -2311,7 +2311,7 @@
         <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE2">
         <v>40</v>
@@ -2320,7 +2320,7 @@
         <v>16</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>17.5</v>
@@ -2347,7 +2347,7 @@
         <v>40</v>
       </c>
       <c r="AP2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
         <v>11</v>
@@ -2484,43 +2484,43 @@
         <v>4.2</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="H3">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I3">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J3">
         <v>3.8</v>
       </c>
       <c r="K3">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
         <v>1.04</v>
       </c>
       <c r="N3">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
         <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S3">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -2529,10 +2529,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2723,46 +2723,46 @@
         <v>367</v>
       </c>
       <c r="F4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>3.5</v>
+      </c>
+      <c r="K4">
         <v>3.95</v>
       </c>
-      <c r="J4">
-        <v>3.6</v>
-      </c>
-      <c r="K4">
-        <v>4.3</v>
-      </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R4">
         <v>1.4</v>
       </c>
       <c r="S4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -2771,10 +2771,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2965,22 +2965,22 @@
         <v>368</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G5">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
         <v>1.48</v>
@@ -2989,40 +2989,40 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
         <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V5">
         <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
         <v>44</v>
@@ -3034,13 +3034,13 @@
         <v>7.4</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
         <v>23</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF5">
         <v>10.5</v>
@@ -3049,10 +3049,10 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AJ5">
         <v>20</v>
@@ -3061,13 +3061,13 @@
         <v>22</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AM5">
         <v>210</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO5">
         <v>130</v>
@@ -3082,7 +3082,7 @@
         <v>36</v>
       </c>
       <c r="AS5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AT5">
         <v>6.4</v>
@@ -3094,7 +3094,7 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AX5">
         <v>8.800000000000001</v>
@@ -3106,7 +3106,7 @@
         <v>19</v>
       </c>
       <c r="BA5">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -3118,13 +3118,13 @@
         <v>36</v>
       </c>
       <c r="BE5">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF5">
         <v>13</v>
       </c>
       <c r="BG5">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -3207,22 +3207,22 @@
         <v>369</v>
       </c>
       <c r="F6">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G6">
         <v>1.56</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
-        <v>8.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
         <v>1.34</v>
@@ -3240,13 +3240,13 @@
         <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -3255,7 +3255,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
         <v>2.74</v>
@@ -3449,22 +3449,22 @@
         <v>370</v>
       </c>
       <c r="F7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G7">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>7.6</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
         <v>1.58</v>
@@ -3479,7 +3479,7 @@
         <v>1.54</v>
       </c>
       <c r="P7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
         <v>2.66</v>
@@ -3488,10 +3488,10 @@
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
         <v>1.61</v>
@@ -3500,7 +3500,7 @@
         <v>1.15</v>
       </c>
       <c r="W7">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X7">
         <v>11</v>
@@ -3515,7 +3515,7 @@
         <v>360</v>
       </c>
       <c r="AB7">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AC7">
         <v>8.800000000000001</v>
@@ -3527,7 +3527,7 @@
         <v>200</v>
       </c>
       <c r="AF7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG7">
         <v>11</v>
@@ -3539,10 +3539,10 @@
         <v>210</v>
       </c>
       <c r="AJ7">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AK7">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL7">
         <v>85</v>
@@ -3563,10 +3563,10 @@
         <v>14</v>
       </c>
       <c r="AR7">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS7">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>5.1</v>
@@ -3575,10 +3575,10 @@
         <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AW7">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX7">
         <v>7.4</v>
@@ -3587,28 +3587,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BA7">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC7">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD7">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
         <v>13</v>
       </c>
       <c r="BG7">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH7">
         <v>2.98</v>
@@ -3691,31 +3691,31 @@
         <v>371</v>
       </c>
       <c r="F8">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="G8">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H8">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J8">
+        <v>3.2</v>
+      </c>
+      <c r="K8">
         <v>3.35</v>
-      </c>
-      <c r="K8">
-        <v>3.5</v>
       </c>
       <c r="L8">
         <v>1.6</v>
       </c>
       <c r="M8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N8">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O8">
         <v>1.57</v>
@@ -3730,127 +3730,127 @@
         <v>1.19</v>
       </c>
       <c r="S8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T8">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V8">
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z8">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB8">
         <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK8">
         <v>34</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP8">
-        <v>1.95</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8">
         <v>10.5</v>
       </c>
       <c r="AR8">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="AS8">
-        <v>2.44</v>
+        <v>5.1</v>
       </c>
       <c r="AT8">
-        <v>1.84</v>
+        <v>5.6</v>
       </c>
       <c r="AU8">
-        <v>2.44</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
-        <v>2.44</v>
+        <v>19.5</v>
       </c>
       <c r="AW8">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="AX8">
-        <v>2.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8">
-        <v>2.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA8">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BB8">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC8">
-        <v>2.28</v>
+        <v>4.5</v>
       </c>
       <c r="BD8">
-        <v>2.38</v>
+        <v>4.9</v>
       </c>
       <c r="BE8">
-        <v>2.44</v>
+        <v>5.1</v>
       </c>
       <c r="BF8">
-        <v>2.44</v>
+        <v>20</v>
       </c>
       <c r="BG8">
-        <v>2.44</v>
+        <v>5.1</v>
       </c>
       <c r="BH8">
         <v>3.15</v>
@@ -3933,16 +3933,16 @@
         <v>372</v>
       </c>
       <c r="F9">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="H9">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="I9">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="J9">
         <v>3.2</v>
@@ -3957,7 +3957,7 @@
         <v>1.1</v>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O9">
         <v>1.45</v>
@@ -3966,31 +3966,31 @@
         <v>1.64</v>
       </c>
       <c r="Q9">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R9">
         <v>1.23</v>
       </c>
       <c r="S9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T9">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V9">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="W9">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X9">
         <v>12</v>
       </c>
       <c r="Y9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z9">
         <v>14</v>
@@ -3999,7 +3999,7 @@
         <v>34</v>
       </c>
       <c r="AB9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC9">
         <v>7.8</v>
@@ -4011,7 +4011,7 @@
         <v>34</v>
       </c>
       <c r="AF9">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AG9">
         <v>22</v>
@@ -4023,7 +4023,7 @@
         <v>60</v>
       </c>
       <c r="AJ9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK9">
         <v>80</v>
@@ -4038,16 +4038,16 @@
         <v>110</v>
       </c>
       <c r="AO9">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AP9">
         <v>7.6</v>
       </c>
       <c r="AQ9">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9">
         <v>19</v>
@@ -4059,19 +4059,19 @@
         <v>6.6</v>
       </c>
       <c r="AV9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW9">
         <v>19</v>
       </c>
       <c r="AX9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY9">
         <v>13.5</v>
       </c>
       <c r="AZ9">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA9">
         <v>4.9</v>
@@ -4175,22 +4175,22 @@
         <v>373</v>
       </c>
       <c r="F10">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G10">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K10">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L10">
         <v>1.55</v>
@@ -4205,7 +4205,7 @@
         <v>1.54</v>
       </c>
       <c r="P10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q10">
         <v>2.68</v>
@@ -4217,16 +4217,16 @@
         <v>5.5</v>
       </c>
       <c r="T10">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X10">
         <v>11</v>
@@ -4238,7 +4238,7 @@
         <v>22</v>
       </c>
       <c r="AA10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -4253,10 +4253,10 @@
         <v>55</v>
       </c>
       <c r="AF10">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH10">
         <v>24</v>
@@ -4268,7 +4268,7 @@
         <v>60</v>
       </c>
       <c r="AK10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL10">
         <v>80</v>
@@ -4277,10 +4277,10 @@
         <v>210</v>
       </c>
       <c r="AN10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP10">
         <v>8</v>
@@ -4292,7 +4292,7 @@
         <v>15.5</v>
       </c>
       <c r="AS10">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT10">
         <v>7.4</v>
@@ -4316,19 +4316,19 @@
         <v>19</v>
       </c>
       <c r="BA10">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB10">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC10">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD10">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE10">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF10">
         <v>38</v>
@@ -4441,22 +4441,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O11">
         <v>1.25</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R11">
         <v>1.18</v>
       </c>
       <c r="S11">
-        <v>1.24</v>
+        <v>2.66</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -4662,43 +4662,43 @@
         <v>4.4</v>
       </c>
       <c r="G12">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H12">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="I12">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M12">
         <v>1.06</v>
       </c>
       <c r="N12">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P12">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="R12">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S12">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -4707,10 +4707,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4916,7 +4916,7 @@
         <v>3.4</v>
       </c>
       <c r="K13">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -5143,7 +5143,7 @@
         <v>377</v>
       </c>
       <c r="F14">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G14">
         <v>4.1</v>
@@ -5155,7 +5155,7 @@
         <v>2.46</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="K14">
         <v>4.9</v>
@@ -5167,7 +5167,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O14">
         <v>1.24</v>
@@ -5176,7 +5176,7 @@
         <v>2</v>
       </c>
       <c r="Q14">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R14">
         <v>1.39</v>
@@ -5194,7 +5194,7 @@
         <v>1.68</v>
       </c>
       <c r="W14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -5397,7 +5397,7 @@
         <v>2.58</v>
       </c>
       <c r="J15">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K15">
         <v>3.35</v>
@@ -5412,13 +5412,13 @@
         <v>3.05</v>
       </c>
       <c r="O15">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P15">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q15">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R15">
         <v>1.26</v>
@@ -5433,7 +5433,7 @@
         <v>1.96</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
         <v>1.4</v>
@@ -5902,13 +5902,13 @@
         <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R17">
         <v>1.18</v>
       </c>
       <c r="S17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -6150,7 +6150,7 @@
         <v>1.07</v>
       </c>
       <c r="S18">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T18">
         <v>1.01</v>
@@ -6356,16 +6356,16 @@
         <v>2.94</v>
       </c>
       <c r="G19">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="H19">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I19">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J19">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K19">
         <v>3.45</v>
@@ -6374,16 +6374,16 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="O19">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P19">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q19">
         <v>2.08</v>
@@ -6401,10 +6401,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W19">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -6625,16 +6625,16 @@
         <v>1.31</v>
       </c>
       <c r="P20">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Q20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R20">
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>2.78</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -6840,10 +6840,10 @@
         <v>3.6</v>
       </c>
       <c r="G21">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="H21">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I21">
         <v>2.42</v>
@@ -6855,7 +6855,7 @@
         <v>3.45</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M21">
         <v>1.1</v>
@@ -6870,7 +6870,7 @@
         <v>1.67</v>
       </c>
       <c r="Q21">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R21">
         <v>1.26</v>
@@ -6879,10 +6879,10 @@
         <v>4.3</v>
       </c>
       <c r="T21">
+        <v>1.94</v>
+      </c>
+      <c r="U21">
         <v>1.92</v>
-      </c>
-      <c r="U21">
-        <v>1.77</v>
       </c>
       <c r="V21">
         <v>1.72</v>
@@ -6903,7 +6903,7 @@
         <v>40</v>
       </c>
       <c r="AB21">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -7079,22 +7079,22 @@
         <v>385</v>
       </c>
       <c r="F22">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="G22">
-        <v>110</v>
+        <v>2.12</v>
       </c>
       <c r="H22">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I22">
-        <v>110</v>
+        <v>8.4</v>
       </c>
       <c r="J22">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="K22">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -7103,22 +7103,22 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>1.26</v>
+        <v>2.98</v>
       </c>
       <c r="O22">
         <v>1.02</v>
       </c>
       <c r="P22">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="Q22">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="R22">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S22">
-        <v>1.27</v>
+        <v>2.56</v>
       </c>
       <c r="T22">
         <v>1.01</v>
@@ -7127,10 +7127,10 @@
         <v>1.01</v>
       </c>
       <c r="V22">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -7321,10 +7321,10 @@
         <v>386</v>
       </c>
       <c r="F23">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G23">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H23">
         <v>1.71</v>
@@ -7336,7 +7336,7 @@
         <v>4.4</v>
       </c>
       <c r="K23">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -7345,16 +7345,16 @@
         <v>1.03</v>
       </c>
       <c r="N23">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O23">
         <v>1.19</v>
       </c>
       <c r="P23">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q23">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R23">
         <v>1.61</v>
@@ -7366,7 +7366,7 @@
         <v>1.62</v>
       </c>
       <c r="U23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
         <v>2.32</v>
@@ -8047,7 +8047,7 @@
         <v>389</v>
       </c>
       <c r="F26">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G26">
         <v>1.63</v>
@@ -8062,7 +8062,7 @@
         <v>4.4</v>
       </c>
       <c r="K26">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -8071,7 +8071,7 @@
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O26">
         <v>1.23</v>
@@ -8080,25 +8080,25 @@
         <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R26">
         <v>1.52</v>
       </c>
       <c r="S26">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T26">
         <v>1.79</v>
       </c>
       <c r="U26">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W26">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X26">
         <v>22</v>
@@ -8116,7 +8116,7 @@
         <v>10.5</v>
       </c>
       <c r="AC26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD26">
         <v>26</v>
@@ -8131,13 +8131,13 @@
         <v>10.5</v>
       </c>
       <c r="AH26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI26">
         <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK26">
         <v>16.5</v>
@@ -8155,7 +8155,7 @@
         <v>1000</v>
       </c>
       <c r="AP26">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ26">
         <v>20</v>
@@ -8179,7 +8179,7 @@
         <v>34</v>
       </c>
       <c r="AX26">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY26">
         <v>9</v>
@@ -8797,16 +8797,16 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="O29">
         <v>1.12</v>
       </c>
       <c r="P29">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Q29">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="R29">
         <v>1.25</v>
@@ -9051,10 +9051,10 @@
         <v>1.19</v>
       </c>
       <c r="R30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S30">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T30">
         <v>1.01</v>
@@ -9257,7 +9257,7 @@
         <v>394</v>
       </c>
       <c r="F31">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G31">
         <v>2.32</v>
@@ -9266,7 +9266,7 @@
         <v>3.25</v>
       </c>
       <c r="I31">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J31">
         <v>3.75</v>
@@ -9281,7 +9281,7 @@
         <v>1.05</v>
       </c>
       <c r="N31">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O31">
         <v>1.26</v>
@@ -9290,7 +9290,7 @@
         <v>2.12</v>
       </c>
       <c r="Q31">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R31">
         <v>1.43</v>
@@ -9308,7 +9308,7 @@
         <v>1.41</v>
       </c>
       <c r="W31">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X31">
         <v>19</v>
@@ -9341,7 +9341,7 @@
         <v>11</v>
       </c>
       <c r="AH31">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI31">
         <v>44</v>
@@ -9365,7 +9365,7 @@
         <v>29</v>
       </c>
       <c r="AP31">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ31">
         <v>13.5</v>
@@ -9505,16 +9505,16 @@
         <v>3.5</v>
       </c>
       <c r="H32">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I32">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J32">
         <v>3.95</v>
       </c>
       <c r="K32">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -9529,13 +9529,13 @@
         <v>1.2</v>
       </c>
       <c r="P32">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q32">
         <v>1.58</v>
       </c>
       <c r="R32">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S32">
         <v>2.48</v>
@@ -9544,10 +9544,10 @@
         <v>1.55</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V32">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="W32">
         <v>1.4</v>
@@ -9556,19 +9556,19 @@
         <v>27</v>
       </c>
       <c r="Y32">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z32">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AA32">
         <v>28</v>
       </c>
       <c r="AB32">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC32">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD32">
         <v>12.5</v>
@@ -9631,13 +9631,13 @@
         <v>17.5</v>
       </c>
       <c r="AX32">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY32">
         <v>13</v>
       </c>
       <c r="AZ32">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA32">
         <v>24</v>
@@ -9753,10 +9753,10 @@
         <v>4.4</v>
       </c>
       <c r="J33">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K33">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -9771,13 +9771,13 @@
         <v>1.22</v>
       </c>
       <c r="P33">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q33">
         <v>1.65</v>
       </c>
       <c r="R33">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S33">
         <v>2.6</v>
@@ -9849,7 +9849,7 @@
         <v>38</v>
       </c>
       <c r="AP33">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ33">
         <v>16.5</v>
@@ -10234,7 +10234,7 @@
         <v>3.8</v>
       </c>
       <c r="I35">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J35">
         <v>3.6</v>
@@ -10258,7 +10258,7 @@
         <v>1.89</v>
       </c>
       <c r="Q35">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R35">
         <v>1.37</v>
@@ -10473,7 +10473,7 @@
         <v>4.6</v>
       </c>
       <c r="H36">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="I36">
         <v>1.9</v>
@@ -10518,7 +10518,7 @@
         <v>2.1</v>
       </c>
       <c r="W36">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -10709,22 +10709,22 @@
         <v>400</v>
       </c>
       <c r="F37">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G37">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="H37">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="I37">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="J37">
         <v>3.7</v>
       </c>
       <c r="K37">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -10736,31 +10736,31 @@
         <v>4.4</v>
       </c>
       <c r="O37">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P37">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q37">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R37">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S37">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T37">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U37">
         <v>2.32</v>
       </c>
       <c r="V37">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W37">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X37">
         <v>20</v>
@@ -10769,13 +10769,13 @@
         <v>13</v>
       </c>
       <c r="Z37">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA37">
         <v>32</v>
       </c>
       <c r="AB37">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC37">
         <v>8.6</v>
@@ -10784,28 +10784,28 @@
         <v>12.5</v>
       </c>
       <c r="AE37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF37">
         <v>32</v>
       </c>
       <c r="AG37">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AH37">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI37">
         <v>40</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AK37">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL37">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="AM37">
         <v>1000</v>
@@ -10826,10 +10826,10 @@
         <v>13</v>
       </c>
       <c r="AS37">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT37">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU37">
         <v>7.8</v>
@@ -10838,25 +10838,25 @@
         <v>10</v>
       </c>
       <c r="AW37">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX37">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY37">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ37">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA37">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB37">
         <v>30</v>
       </c>
       <c r="BC37">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD37">
         <v>25</v>
@@ -10868,7 +10868,7 @@
         <v>21</v>
       </c>
       <c r="BG37">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH37">
         <v>1000</v>
@@ -10960,7 +10960,7 @@
         <v>7.6</v>
       </c>
       <c r="I38">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J38">
         <v>4.8</v>
@@ -10981,7 +10981,7 @@
         <v>1.23</v>
       </c>
       <c r="P38">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q38">
         <v>1.69</v>
@@ -10996,7 +10996,7 @@
         <v>1.87</v>
       </c>
       <c r="U38">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
         <v>1.14</v>
@@ -11017,7 +11017,7 @@
         <v>240</v>
       </c>
       <c r="AB38">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC38">
         <v>11</v>
@@ -11029,13 +11029,13 @@
         <v>110</v>
       </c>
       <c r="AF38">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG38">
         <v>10</v>
       </c>
       <c r="AH38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI38">
         <v>95</v>
@@ -11047,7 +11047,7 @@
         <v>15</v>
       </c>
       <c r="AL38">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM38">
         <v>120</v>
@@ -11059,7 +11059,7 @@
         <v>130</v>
       </c>
       <c r="AP38">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ38">
         <v>26</v>
@@ -11196,7 +11196,7 @@
         <v>1.78</v>
       </c>
       <c r="G39">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H39">
         <v>4.3</v>
@@ -11208,7 +11208,7 @@
         <v>4.1</v>
       </c>
       <c r="K39">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L39">
         <v>1.27</v>
@@ -11217,7 +11217,7 @@
         <v>1.02</v>
       </c>
       <c r="N39">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O39">
         <v>1.2</v>
@@ -11226,10 +11226,10 @@
         <v>2.52</v>
       </c>
       <c r="Q39">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="R39">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S39">
         <v>2.46</v>
@@ -11238,10 +11238,10 @@
         <v>1.62</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V39">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W39">
         <v>2.16</v>
@@ -11295,7 +11295,7 @@
         <v>80</v>
       </c>
       <c r="AN39">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO39">
         <v>40</v>
@@ -11307,7 +11307,7 @@
         <v>18.5</v>
       </c>
       <c r="AR39">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS39">
         <v>6.8</v>
@@ -11322,7 +11322,7 @@
         <v>15.5</v>
       </c>
       <c r="AW39">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX39">
         <v>11.5</v>
@@ -11343,16 +11343,16 @@
         <v>14.5</v>
       </c>
       <c r="BD39">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE39">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF39">
         <v>7</v>
       </c>
       <c r="BG39">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -11925,7 +11925,7 @@
         <v>1.57</v>
       </c>
       <c r="H42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I42">
         <v>7.6</v>
@@ -11985,10 +11985,10 @@
         <v>1000</v>
       </c>
       <c r="AB42">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AC42">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AD42">
         <v>1000</v>
@@ -11997,10 +11997,10 @@
         <v>1000</v>
       </c>
       <c r="AF42">
-        <v>270</v>
+        <v>16</v>
       </c>
       <c r="AG42">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AH42">
         <v>1000</v>
@@ -12009,10 +12009,10 @@
         <v>95</v>
       </c>
       <c r="AJ42">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK42">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL42">
         <v>38</v>
@@ -12027,58 +12027,58 @@
         <v>1000</v>
       </c>
       <c r="AP42">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AQ42">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="AR42">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="AS42">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="AT42">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="AU42">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AV42">
-        <v>5.2</v>
+        <v>1.59</v>
       </c>
       <c r="AW42">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="AX42">
         <v>8.199999999999999</v>
       </c>
       <c r="AY42">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AZ42">
-        <v>5.1</v>
+        <v>1.59</v>
       </c>
       <c r="BA42">
-        <v>3.45</v>
+        <v>1.57</v>
       </c>
       <c r="BB42">
-        <v>2.22</v>
+        <v>1.46</v>
       </c>
       <c r="BC42">
-        <v>2.28</v>
+        <v>1.46</v>
       </c>
       <c r="BD42">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="BE42">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="BF42">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="BG42">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -12161,7 +12161,7 @@
         <v>406</v>
       </c>
       <c r="F43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G43">
         <v>1.59</v>
@@ -12188,22 +12188,22 @@
         <v>8</v>
       </c>
       <c r="O43">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P43">
         <v>3.1</v>
       </c>
       <c r="Q43">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R43">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="S43">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T43">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="U43">
         <v>2.8</v>
@@ -12215,7 +12215,7 @@
         <v>2.68</v>
       </c>
       <c r="X43">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y43">
         <v>38</v>
@@ -12230,25 +12230,25 @@
         <v>17</v>
       </c>
       <c r="AC43">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD43">
         <v>25</v>
       </c>
       <c r="AE43">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AF43">
         <v>14.5</v>
       </c>
       <c r="AG43">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH43">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI43">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AJ43">
         <v>17.5</v>
@@ -12272,7 +12272,7 @@
         <v>32</v>
       </c>
       <c r="AQ43">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR43">
         <v>29</v>
@@ -12287,10 +12287,10 @@
         <v>11.5</v>
       </c>
       <c r="AV43">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW43">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX43">
         <v>12.5</v>
@@ -12302,7 +12302,7 @@
         <v>15</v>
       </c>
       <c r="BA43">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB43">
         <v>15</v>
@@ -12311,16 +12311,16 @@
         <v>12.5</v>
       </c>
       <c r="BD43">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE43">
         <v>27</v>
       </c>
       <c r="BF43">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG43">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -12412,7 +12412,7 @@
         <v>5.6</v>
       </c>
       <c r="I44">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J44">
         <v>4.5</v>
@@ -12430,7 +12430,7 @@
         <v>5.5</v>
       </c>
       <c r="O44">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P44">
         <v>2.48</v>
@@ -12439,10 +12439,10 @@
         <v>1.55</v>
       </c>
       <c r="R44">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S44">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T44">
         <v>1.66</v>
@@ -12454,7 +12454,7 @@
         <v>1.17</v>
       </c>
       <c r="W44">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -12645,19 +12645,19 @@
         <v>408</v>
       </c>
       <c r="F45">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="G45">
-        <v>470</v>
+        <v>100</v>
       </c>
       <c r="H45">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="I45">
-        <v>110</v>
+        <v>1.66</v>
       </c>
       <c r="J45">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="K45">
         <v>320</v>
@@ -12669,22 +12669,22 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="O45">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="P45">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q45">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="R45">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="S45">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="T45">
         <v>1.01</v>
@@ -12693,10 +12693,10 @@
         <v>1.01</v>
       </c>
       <c r="V45">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="W45">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
         <v>1000</v>
@@ -12887,22 +12887,22 @@
         <v>409</v>
       </c>
       <c r="F46">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G46">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H46">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="I46">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="J46">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K46">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12917,13 +12917,13 @@
         <v>1.16</v>
       </c>
       <c r="P46">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q46">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R46">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S46">
         <v>2.2</v>
@@ -12935,7 +12935,7 @@
         <v>2.26</v>
       </c>
       <c r="V46">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="W46">
         <v>1.13</v>
@@ -12947,13 +12947,13 @@
         <v>13</v>
       </c>
       <c r="Z46">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA46">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AB46">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AC46">
         <v>13.5</v>
@@ -12965,40 +12965,40 @@
         <v>14</v>
       </c>
       <c r="AF46">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG46">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AH46">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI46">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AJ46">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AK46">
         <v>95</v>
       </c>
       <c r="AL46">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM46">
+        <v>95</v>
+      </c>
+      <c r="AN46">
         <v>90</v>
-      </c>
-      <c r="AN46">
-        <v>85</v>
       </c>
       <c r="AO46">
         <v>4.8</v>
       </c>
       <c r="AP46">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ46">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR46">
         <v>9.800000000000001</v>
@@ -13007,7 +13007,7 @@
         <v>12</v>
       </c>
       <c r="AT46">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AU46">
         <v>12.5</v>
@@ -13019,34 +13019,34 @@
         <v>12.5</v>
       </c>
       <c r="AX46">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY46">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="AZ46">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA46">
         <v>23</v>
       </c>
       <c r="BB46">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC46">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD46">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="BE46">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF46">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BG46">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -13129,22 +13129,22 @@
         <v>410</v>
       </c>
       <c r="F47">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G47">
         <v>1.87</v>
       </c>
       <c r="H47">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I47">
         <v>6.6</v>
       </c>
       <c r="J47">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K47">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -13159,7 +13159,7 @@
         <v>1.32</v>
       </c>
       <c r="P47">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q47">
         <v>1.9</v>
@@ -13374,7 +13374,7 @@
         <v>2.4</v>
       </c>
       <c r="G48">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H48">
         <v>2.92</v>
@@ -13383,7 +13383,7 @@
         <v>3.1</v>
       </c>
       <c r="J48">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K48">
         <v>4</v>
@@ -13392,7 +13392,7 @@
         <v>1.01</v>
       </c>
       <c r="M48">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N48">
         <v>2.24</v>
@@ -13440,7 +13440,7 @@
         <v>14.5</v>
       </c>
       <c r="AC48">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD48">
         <v>14</v>
@@ -13452,7 +13452,7 @@
         <v>23</v>
       </c>
       <c r="AG48">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH48">
         <v>18.5</v>
@@ -13509,13 +13509,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ48">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA48">
         <v>23</v>
       </c>
       <c r="BB48">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BC48">
         <v>20</v>
@@ -13524,7 +13524,7 @@
         <v>21</v>
       </c>
       <c r="BE48">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BF48">
         <v>10</v>
@@ -13613,16 +13613,16 @@
         <v>412</v>
       </c>
       <c r="F49">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G49">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H49">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J49">
         <v>3.6</v>
@@ -13637,13 +13637,13 @@
         <v>1.06</v>
       </c>
       <c r="N49">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O49">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P49">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q49">
         <v>1.71</v>
@@ -13655,7 +13655,7 @@
         <v>3</v>
       </c>
       <c r="T49">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="U49">
         <v>2.28</v>
@@ -13664,10 +13664,10 @@
         <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X49">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y49">
         <v>16</v>
@@ -13730,7 +13730,7 @@
         <v>19.5</v>
       </c>
       <c r="AS49">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT49">
         <v>10.5</v>
@@ -13742,7 +13742,7 @@
         <v>12</v>
       </c>
       <c r="AW49">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX49">
         <v>14.5</v>
@@ -13754,19 +13754,19 @@
         <v>14</v>
       </c>
       <c r="BA49">
+        <v>4.8</v>
+      </c>
+      <c r="BB49">
         <v>4.7</v>
       </c>
-      <c r="BB49">
-        <v>4.6</v>
-      </c>
       <c r="BC49">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD49">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE49">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF49">
         <v>13.5</v>
@@ -13858,10 +13858,10 @@
         <v>6.4</v>
       </c>
       <c r="G50">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H50">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I50">
         <v>1.54</v>
@@ -13870,7 +13870,7 @@
         <v>4.9</v>
       </c>
       <c r="K50">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13891,7 +13891,7 @@
         <v>1.5</v>
       </c>
       <c r="R50">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S50">
         <v>2.2</v>
@@ -13906,7 +13906,7 @@
         <v>2.84</v>
       </c>
       <c r="W50">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>32</v>
@@ -13915,7 +13915,7 @@
         <v>14</v>
       </c>
       <c r="Z50">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA50">
         <v>15.5</v>
@@ -13999,19 +13999,19 @@
         <v>21</v>
       </c>
       <c r="BB50">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC50">
         <v>9.6</v>
       </c>
       <c r="BD50">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE50">
         <v>55</v>
       </c>
       <c r="BF50">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG50">
         <v>4.7</v>
@@ -14130,13 +14130,13 @@
         <v>1.25</v>
       </c>
       <c r="Q51">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="R51">
         <v>1.18</v>
       </c>
       <c r="S51">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -14339,7 +14339,7 @@
         <v>415</v>
       </c>
       <c r="F52">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G52">
         <v>2.74</v>
@@ -14354,7 +14354,7 @@
         <v>3.25</v>
       </c>
       <c r="K52">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -14363,16 +14363,16 @@
         <v>1.02</v>
       </c>
       <c r="N52">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O52">
         <v>1.35</v>
       </c>
       <c r="P52">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q52">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R52">
         <v>1.28</v>
@@ -14387,7 +14387,7 @@
         <v>1.01</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
         <v>1.58</v>
@@ -14620,7 +14620,7 @@
         <v>1.04</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T53">
         <v>1.01</v>
@@ -14823,7 +14823,7 @@
         <v>417</v>
       </c>
       <c r="F54">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G54">
         <v>2.04</v>
@@ -14838,7 +14838,7 @@
         <v>3.85</v>
       </c>
       <c r="K54">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L54">
         <v>1.01</v>
@@ -15346,7 +15346,7 @@
         <v>1.18</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>2.42</v>
       </c>
       <c r="T56">
         <v>1.01</v>
@@ -15839,7 +15839,7 @@
         <v>1.01</v>
       </c>
       <c r="V58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W58">
         <v>1.01</v>
@@ -16541,7 +16541,7 @@
         <v>1.01</v>
       </c>
       <c r="N61">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O61">
         <v>1.16</v>
@@ -16759,7 +16759,7 @@
         <v>425</v>
       </c>
       <c r="F62">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G62">
         <v>110</v>
@@ -16798,7 +16798,7 @@
         <v>1.18</v>
       </c>
       <c r="S62">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="T62">
         <v>1.01</v>
@@ -17040,7 +17040,7 @@
         <v>1.15</v>
       </c>
       <c r="S63">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="T63">
         <v>1.01</v>
@@ -17276,13 +17276,13 @@
         <v>1.25</v>
       </c>
       <c r="Q64">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="R64">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="S64">
-        <v>1.27</v>
+        <v>2.78</v>
       </c>
       <c r="T64">
         <v>1.01</v>
@@ -17500,7 +17500,7 @@
         <v>3.1</v>
       </c>
       <c r="K65">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L65">
         <v>1.01</v>
@@ -17593,52 +17593,52 @@
         <v>1000</v>
       </c>
       <c r="AP65">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="AQ65">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AR65">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AS65">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="AT65">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AU65">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AV65">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AW65">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AX65">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="AY65">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="AZ65">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="BA65">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BB65">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BC65">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BD65">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="BE65">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF65">
         <v>1.01</v>
@@ -17766,7 +17766,7 @@
         <v>1.01</v>
       </c>
       <c r="S66">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="T66">
         <v>1.01</v>
@@ -17993,19 +17993,19 @@
         <v>1.01</v>
       </c>
       <c r="N67">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O67">
         <v>1.18</v>
       </c>
       <c r="P67">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q67">
         <v>1.18</v>
       </c>
       <c r="R67">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="S67">
         <v>1.18</v>
@@ -18211,10 +18211,10 @@
         <v>431</v>
       </c>
       <c r="F68">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G68">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H68">
         <v>4.9</v>
@@ -18262,7 +18262,7 @@
         <v>1.22</v>
       </c>
       <c r="W68">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X68">
         <v>20</v>
@@ -18307,7 +18307,7 @@
         <v>17.5</v>
       </c>
       <c r="AL68">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM68">
         <v>110</v>
@@ -18334,7 +18334,7 @@
         <v>8.4</v>
       </c>
       <c r="AU68">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV68">
         <v>18</v>
@@ -18453,7 +18453,7 @@
         <v>432</v>
       </c>
       <c r="F69">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G69">
         <v>1.88</v>
@@ -18462,13 +18462,13 @@
         <v>4.4</v>
       </c>
       <c r="I69">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J69">
         <v>4</v>
       </c>
       <c r="K69">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L69">
         <v>1.01</v>
@@ -18486,7 +18486,7 @@
         <v>2.12</v>
       </c>
       <c r="Q69">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R69">
         <v>1.45</v>
@@ -18501,7 +18501,7 @@
         <v>2.2</v>
       </c>
       <c r="V69">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W69">
         <v>2.12</v>
@@ -18719,7 +18719,7 @@
         <v>1.01</v>
       </c>
       <c r="N70">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="O70">
         <v>1.32</v>
@@ -18728,13 +18728,13 @@
         <v>1.25</v>
       </c>
       <c r="Q70">
+        <v>1.31</v>
+      </c>
+      <c r="R70">
+        <v>1.07</v>
+      </c>
+      <c r="S70">
         <v>1.32</v>
-      </c>
-      <c r="R70">
-        <v>1.06</v>
-      </c>
-      <c r="S70">
-        <v>1.31</v>
       </c>
       <c r="T70">
         <v>1.01</v>
@@ -18946,19 +18946,19 @@
         <v>3.35</v>
       </c>
       <c r="I71">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J71">
         <v>3.75</v>
       </c>
       <c r="K71">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L71">
         <v>1.01</v>
       </c>
       <c r="M71">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N71">
         <v>4.3</v>
@@ -18979,7 +18979,7 @@
         <v>3</v>
       </c>
       <c r="T71">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U71">
         <v>2.32</v>
@@ -19054,7 +19054,7 @@
         <v>8</v>
       </c>
       <c r="AS71">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AT71">
         <v>11</v>
@@ -19182,37 +19182,37 @@
         <v>1.89</v>
       </c>
       <c r="G72">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H72">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I72">
         <v>4.8</v>
       </c>
       <c r="J72">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K72">
         <v>3.9</v>
       </c>
       <c r="L72">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M72">
         <v>1.07</v>
       </c>
       <c r="N72">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O72">
         <v>1.32</v>
       </c>
       <c r="P72">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q72">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R72">
         <v>1.36</v>
@@ -19230,7 +19230,7 @@
         <v>1.26</v>
       </c>
       <c r="W72">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X72">
         <v>15</v>
@@ -19245,7 +19245,7 @@
         <v>120</v>
       </c>
       <c r="AB72">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC72">
         <v>8.800000000000001</v>
@@ -19257,7 +19257,7 @@
         <v>60</v>
       </c>
       <c r="AF72">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG72">
         <v>11</v>
@@ -19281,46 +19281,46 @@
         <v>120</v>
       </c>
       <c r="AN72">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO72">
         <v>65</v>
       </c>
       <c r="AP72">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ72">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR72">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS72">
+        <v>9.6</v>
+      </c>
+      <c r="AT72">
+        <v>8</v>
+      </c>
+      <c r="AU72">
+        <v>7.4</v>
+      </c>
+      <c r="AV72">
+        <v>15</v>
+      </c>
+      <c r="AW72">
         <v>9</v>
       </c>
-      <c r="AT72">
-        <v>7.8</v>
-      </c>
-      <c r="AU72">
-        <v>7.2</v>
-      </c>
-      <c r="AV72">
-        <v>13.5</v>
-      </c>
-      <c r="AW72">
-        <v>19</v>
-      </c>
       <c r="AX72">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY72">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ72">
         <v>16</v>
       </c>
       <c r="BA72">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BB72">
         <v>17</v>
@@ -19329,28 +19329,28 @@
         <v>16</v>
       </c>
       <c r="BD72">
+        <v>8.4</v>
+      </c>
+      <c r="BE72">
+        <v>9.6</v>
+      </c>
+      <c r="BF72">
         <v>11.5</v>
       </c>
-      <c r="BE72">
+      <c r="BG72">
         <v>9</v>
       </c>
-      <c r="BF72">
-        <v>10.5</v>
-      </c>
-      <c r="BG72">
-        <v>8.4</v>
-      </c>
       <c r="BH72">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI72">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="BJ72">
         <v>10.5</v>
       </c>
       <c r="BK72">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL72">
         <v>1000</v>
@@ -19371,7 +19371,7 @@
         <v>10.5</v>
       </c>
       <c r="BR72">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS72">
         <v>21</v>
@@ -19421,7 +19421,7 @@
         <v>436</v>
       </c>
       <c r="F73">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="G73">
         <v>4</v>
@@ -19436,7 +19436,7 @@
         <v>2.72</v>
       </c>
       <c r="K73">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L73">
         <v>1.01</v>
@@ -19448,7 +19448,7 @@
         <v>2.16</v>
       </c>
       <c r="O73">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="P73">
         <v>1.37</v>
@@ -19666,19 +19666,19 @@
         <v>1.73</v>
       </c>
       <c r="G74">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H74">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I74">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J74">
         <v>3.8</v>
       </c>
       <c r="K74">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L74">
         <v>1.01</v>
@@ -19687,34 +19687,34 @@
         <v>1.08</v>
       </c>
       <c r="N74">
+        <v>3.55</v>
+      </c>
+      <c r="O74">
+        <v>1.35</v>
+      </c>
+      <c r="P74">
+        <v>1.89</v>
+      </c>
+      <c r="Q74">
+        <v>2.04</v>
+      </c>
+      <c r="R74">
+        <v>1.35</v>
+      </c>
+      <c r="S74">
         <v>3.6</v>
       </c>
-      <c r="O74">
-        <v>1.32</v>
-      </c>
-      <c r="P74">
-        <v>1.87</v>
-      </c>
-      <c r="Q74">
+      <c r="T74">
         <v>1.97</v>
       </c>
-      <c r="R74">
-        <v>1.33</v>
-      </c>
-      <c r="S74">
-        <v>3.55</v>
-      </c>
-      <c r="T74">
-        <v>1.94</v>
-      </c>
       <c r="U74">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V74">
         <v>1.19</v>
       </c>
       <c r="W74">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X74">
         <v>16.5</v>
@@ -19729,7 +19729,7 @@
         <v>190</v>
       </c>
       <c r="AB74">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC74">
         <v>10.5</v>
@@ -19741,10 +19741,10 @@
         <v>110</v>
       </c>
       <c r="AF74">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG74">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH74">
         <v>25</v>
@@ -19765,64 +19765,64 @@
         <v>150</v>
       </c>
       <c r="AN74">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO74">
         <v>140</v>
       </c>
       <c r="AP74">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ74">
         <v>16</v>
       </c>
       <c r="AR74">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS74">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AT74">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU74">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV74">
         <v>20</v>
       </c>
       <c r="AW74">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="AX74">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY74">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ74">
         <v>18</v>
       </c>
       <c r="BA74">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BB74">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC74">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD74">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE74">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BF74">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG74">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BH74">
         <v>1000</v>
@@ -19914,7 +19914,7 @@
         <v>4.8</v>
       </c>
       <c r="I75">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J75">
         <v>3.7</v>
@@ -19926,7 +19926,7 @@
         <v>1.01</v>
       </c>
       <c r="M75">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N75">
         <v>1.01</v>
@@ -19935,25 +19935,25 @@
         <v>1.35</v>
       </c>
       <c r="P75">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q75">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="R75">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S75">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="T75">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U75">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="V75">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W75">
         <v>2.12</v>
@@ -20174,13 +20174,13 @@
         <v>4.2</v>
       </c>
       <c r="O76">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P76">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q76">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="R76">
         <v>1.44</v>
@@ -20431,7 +20431,7 @@
         <v>2.58</v>
       </c>
       <c r="T77">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U77">
         <v>1.01</v>
@@ -20631,13 +20631,13 @@
         <v>441</v>
       </c>
       <c r="F78">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G78">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H78">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I78">
         <v>3.8</v>
@@ -20664,7 +20664,7 @@
         <v>2.92</v>
       </c>
       <c r="Q78">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R78">
         <v>1.79</v>
@@ -20879,7 +20879,7 @@
         <v>1.65</v>
       </c>
       <c r="H79">
-        <v>6.2</v>
+        <v>1.06</v>
       </c>
       <c r="I79">
         <v>14</v>
@@ -20888,7 +20888,7 @@
         <v>4.3</v>
       </c>
       <c r="K79">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L79">
         <v>1.01</v>
@@ -20897,7 +20897,7 @@
         <v>1.03</v>
       </c>
       <c r="N79">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="O79">
         <v>1.14</v>
@@ -20912,7 +20912,7 @@
         <v>1.62</v>
       </c>
       <c r="S79">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="T79">
         <v>1.01</v>
@@ -21115,22 +21115,22 @@
         <v>443</v>
       </c>
       <c r="F80">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G80">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H80">
         <v>3.85</v>
       </c>
       <c r="I80">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J80">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K80">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L80">
         <v>1.01</v>
@@ -21357,19 +21357,19 @@
         <v>444</v>
       </c>
       <c r="F81">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G81">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H81">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I81">
         <v>1.72</v>
       </c>
       <c r="J81">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K81">
         <v>4.4</v>
@@ -21387,7 +21387,7 @@
         <v>1.27</v>
       </c>
       <c r="P81">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q81">
         <v>1.78</v>
@@ -21399,13 +21399,13 @@
         <v>2.96</v>
       </c>
       <c r="T81">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U81">
         <v>2.12</v>
       </c>
       <c r="V81">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="W81">
         <v>1.21</v>
@@ -21438,7 +21438,7 @@
         <v>55</v>
       </c>
       <c r="AG81">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH81">
         <v>23</v>
@@ -21489,7 +21489,7 @@
         <v>15.5</v>
       </c>
       <c r="AX81">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY81">
         <v>18.5</v>
@@ -21501,19 +21501,19 @@
         <v>4.8</v>
       </c>
       <c r="BB81">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC81">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BD81">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE81">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF81">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG81">
         <v>8</v>
@@ -21841,10 +21841,10 @@
         <v>446</v>
       </c>
       <c r="F83">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G83">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H83">
         <v>2.36</v>
@@ -21892,7 +21892,7 @@
         <v>1.57</v>
       </c>
       <c r="W83">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X83">
         <v>1000</v>
@@ -22325,10 +22325,10 @@
         <v>448</v>
       </c>
       <c r="F85">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G85">
-        <v>110</v>
+        <v>3.15</v>
       </c>
       <c r="H85">
         <v>2.28</v>
@@ -22340,7 +22340,7 @@
         <v>2.28</v>
       </c>
       <c r="K85">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="L85">
         <v>1.01</v>
@@ -22358,10 +22358,10 @@
         <v>2.16</v>
       </c>
       <c r="Q85">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="R85">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S85">
         <v>2.46</v>
@@ -22576,7 +22576,7 @@
         <v>2.24</v>
       </c>
       <c r="I86">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J86">
         <v>4.1</v>
@@ -22615,7 +22615,7 @@
         <v>2.74</v>
       </c>
       <c r="V86">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W86">
         <v>1.46</v>
@@ -22833,10 +22833,10 @@
         <v>1.01</v>
       </c>
       <c r="N87">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="O87">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="P87">
         <v>3.6</v>
@@ -22848,7 +22848,7 @@
         <v>2.06</v>
       </c>
       <c r="S87">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="T87">
         <v>1.45</v>
@@ -23293,13 +23293,13 @@
         <v>452</v>
       </c>
       <c r="F89">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G89">
         <v>2.18</v>
       </c>
       <c r="H89">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I89">
         <v>3.5</v>
@@ -23314,31 +23314,31 @@
         <v>1.01</v>
       </c>
       <c r="M89">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N89">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="O89">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P89">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q89">
         <v>1.56</v>
       </c>
       <c r="R89">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="S89">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="T89">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U89">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="V89">
         <v>1.4</v>
@@ -23410,7 +23410,7 @@
         <v>19.5</v>
       </c>
       <c r="AS89">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT89">
         <v>13</v>
@@ -23419,7 +23419,7 @@
         <v>9</v>
       </c>
       <c r="AV89">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW89">
         <v>22</v>
@@ -23446,7 +23446,7 @@
         <v>19.5</v>
       </c>
       <c r="BE89">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="BF89">
         <v>9</v>
@@ -23538,16 +23538,16 @@
         <v>2.38</v>
       </c>
       <c r="G90">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H90">
         <v>2.52</v>
       </c>
       <c r="I90">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J90">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K90">
         <v>5.5</v>
@@ -23583,10 +23583,10 @@
         <v>1.01</v>
       </c>
       <c r="V90">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W90">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X90">
         <v>1000</v>
@@ -23777,7 +23777,7 @@
         <v>454</v>
       </c>
       <c r="F91">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G91">
         <v>1.71</v>
@@ -23804,19 +23804,19 @@
         <v>4</v>
       </c>
       <c r="O91">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P91">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q91">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R91">
         <v>1.4</v>
       </c>
       <c r="S91">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T91">
         <v>1.85</v>
@@ -23879,7 +23879,7 @@
         <v>140</v>
       </c>
       <c r="AN91">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO91">
         <v>120</v>
@@ -24043,19 +24043,19 @@
         <v>1.01</v>
       </c>
       <c r="N92">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O92">
         <v>1.19</v>
       </c>
       <c r="P92">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q92">
         <v>1.19</v>
       </c>
       <c r="R92">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="S92">
         <v>1.19</v>
@@ -24261,22 +24261,22 @@
         <v>456</v>
       </c>
       <c r="F93">
-        <v>1.13</v>
+        <v>7.6</v>
       </c>
       <c r="G93">
         <v>110</v>
       </c>
       <c r="H93">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="I93">
-        <v>110</v>
+        <v>1.53</v>
       </c>
       <c r="J93">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="K93">
-        <v>170</v>
+        <v>16.5</v>
       </c>
       <c r="L93">
         <v>1.01</v>
@@ -24285,34 +24285,34 @@
         <v>1.01</v>
       </c>
       <c r="N93">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="O93">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P93">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q93">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="R93">
+        <v>1.38</v>
+      </c>
+      <c r="S93">
+        <v>1.46</v>
+      </c>
+      <c r="T93">
+        <v>1.01</v>
+      </c>
+      <c r="U93">
+        <v>1.01</v>
+      </c>
+      <c r="V93">
+        <v>2.9</v>
+      </c>
+      <c r="W93">
         <v>1.05</v>
-      </c>
-      <c r="S93">
-        <v>1.32</v>
-      </c>
-      <c r="T93">
-        <v>1.01</v>
-      </c>
-      <c r="U93">
-        <v>1.01</v>
-      </c>
-      <c r="V93">
-        <v>1.12</v>
-      </c>
-      <c r="W93">
-        <v>1.01</v>
       </c>
       <c r="X93">
         <v>1000</v>
@@ -24503,22 +24503,22 @@
         <v>457</v>
       </c>
       <c r="F94">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G94">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H94">
         <v>6</v>
       </c>
       <c r="I94">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J94">
         <v>4.5</v>
       </c>
       <c r="K94">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L94">
         <v>1.01</v>
@@ -24551,10 +24551,10 @@
         <v>2.22</v>
       </c>
       <c r="V94">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W94">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X94">
         <v>25</v>
@@ -24590,19 +24590,19 @@
         <v>22</v>
       </c>
       <c r="AI94">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ94">
         <v>16</v>
       </c>
       <c r="AK94">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL94">
         <v>30</v>
       </c>
       <c r="AM94">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN94">
         <v>6.8</v>
@@ -24647,7 +24647,7 @@
         <v>50</v>
       </c>
       <c r="BB94">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC94">
         <v>13.5</v>
@@ -24656,13 +24656,13 @@
         <v>24</v>
       </c>
       <c r="BE94">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF94">
         <v>5.8</v>
       </c>
       <c r="BG94">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH94">
         <v>1000</v>
@@ -24745,19 +24745,19 @@
         <v>458</v>
       </c>
       <c r="F95">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G95">
         <v>1.43</v>
       </c>
       <c r="H95">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I95">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J95">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K95">
         <v>330</v>
@@ -24787,7 +24787,7 @@
         <v>1.6</v>
       </c>
       <c r="T95">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="U95">
         <v>1.01</v>
@@ -25232,7 +25232,7 @@
         <v>2.56</v>
       </c>
       <c r="G97">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H97">
         <v>2.4</v>
@@ -25253,22 +25253,22 @@
         <v>1.02</v>
       </c>
       <c r="N97">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O97">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P97">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q97">
         <v>1.42</v>
       </c>
       <c r="R97">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="S97">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T97">
         <v>1.42</v>
@@ -25471,19 +25471,19 @@
         <v>461</v>
       </c>
       <c r="F98">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="G98">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H98">
         <v>4</v>
       </c>
       <c r="I98">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J98">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="K98">
         <v>410</v>
@@ -25519,7 +25519,7 @@
         <v>1.01</v>
       </c>
       <c r="V98">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W98">
         <v>3.85</v>
@@ -25719,7 +25719,7 @@
         <v>320</v>
       </c>
       <c r="H99">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="I99">
         <v>970</v>
@@ -25752,7 +25752,7 @@
         <v>1.06</v>
       </c>
       <c r="S99">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T99">
         <v>1.01</v>
@@ -25955,58 +25955,58 @@
         <v>463</v>
       </c>
       <c r="F100">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="G100">
         <v>1.36</v>
       </c>
       <c r="H100">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="I100">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J100">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="K100">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L100">
         <v>1.01</v>
       </c>
       <c r="M100">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N100">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="O100">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P100">
         <v>2.74</v>
       </c>
       <c r="Q100">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R100">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S100">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="T100">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="U100">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="V100">
         <v>1.08</v>
       </c>
       <c r="W100">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="X100">
         <v>1000</v>
@@ -26021,7 +26021,7 @@
         <v>1000</v>
       </c>
       <c r="AB100">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AC100">
         <v>1000</v>
@@ -26033,10 +26033,10 @@
         <v>1000</v>
       </c>
       <c r="AF100">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="AG100">
-        <v>180</v>
+        <v>23</v>
       </c>
       <c r="AH100">
         <v>1000</v>
@@ -26045,10 +26045,10 @@
         <v>1000</v>
       </c>
       <c r="AJ100">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="AK100">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AL100">
         <v>1000</v>
@@ -26057,64 +26057,64 @@
         <v>1000</v>
       </c>
       <c r="AN100">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="AO100">
         <v>1000</v>
       </c>
       <c r="AP100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AQ100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AR100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AS100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AT100">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="AU100">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
       <c r="AV100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AW100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="AX100">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="AY100">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="AZ100">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="BA100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="BB100">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="BC100">
-        <v>2.52</v>
+        <v>1.5</v>
       </c>
       <c r="BD100">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="BE100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="BF100">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="BG100">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="BH100">
         <v>1000</v>
@@ -26197,19 +26197,19 @@
         <v>464</v>
       </c>
       <c r="F101">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G101">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="H101">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I101">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J101">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K101">
         <v>4.6</v>
@@ -26227,28 +26227,28 @@
         <v>1.18</v>
       </c>
       <c r="P101">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q101">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="R101">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S101">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="T101">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U101">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W101">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="X101">
         <v>27</v>
@@ -26260,7 +26260,7 @@
         <v>36</v>
       </c>
       <c r="AA101">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB101">
         <v>15.5</v>
@@ -26275,7 +26275,7 @@
         <v>44</v>
       </c>
       <c r="AF101">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG101">
         <v>13</v>
@@ -26314,7 +26314,7 @@
         <v>4.4</v>
       </c>
       <c r="AS101">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT101">
         <v>10</v>
@@ -26338,7 +26338,7 @@
         <v>12</v>
       </c>
       <c r="BA101">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB101">
         <v>18</v>
@@ -26439,46 +26439,46 @@
         <v>465</v>
       </c>
       <c r="F102">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="G102">
+        <v>1.84</v>
+      </c>
+      <c r="H102">
+        <v>5</v>
+      </c>
+      <c r="I102">
+        <v>6.6</v>
+      </c>
+      <c r="J102">
+        <v>1.08</v>
+      </c>
+      <c r="K102">
+        <v>4.3</v>
+      </c>
+      <c r="L102">
+        <v>1.01</v>
+      </c>
+      <c r="M102">
+        <v>1.01</v>
+      </c>
+      <c r="N102">
+        <v>3.45</v>
+      </c>
+      <c r="O102">
+        <v>1.27</v>
+      </c>
+      <c r="P102">
         <v>1.85</v>
       </c>
-      <c r="H102">
-        <v>2.22</v>
-      </c>
-      <c r="I102">
-        <v>110</v>
-      </c>
-      <c r="J102">
-        <v>2.22</v>
-      </c>
-      <c r="K102">
-        <v>950</v>
-      </c>
-      <c r="L102">
-        <v>1.01</v>
-      </c>
-      <c r="M102">
-        <v>1.01</v>
-      </c>
-      <c r="N102">
-        <v>1.26</v>
-      </c>
-      <c r="O102">
-        <v>1.26</v>
-      </c>
-      <c r="P102">
-        <v>1.25</v>
-      </c>
       <c r="Q102">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="R102">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="S102">
-        <v>1.28</v>
+        <v>3.1</v>
       </c>
       <c r="T102">
         <v>1.01</v>
@@ -26487,10 +26487,10 @@
         <v>1.01</v>
       </c>
       <c r="V102">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W102">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X102">
         <v>1000</v>
@@ -26681,10 +26681,10 @@
         <v>466</v>
       </c>
       <c r="F103">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G103">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H103">
         <v>2.4</v>
@@ -26693,10 +26693,10 @@
         <v>3</v>
       </c>
       <c r="J103">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K103">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L103">
         <v>1.01</v>
@@ -26714,7 +26714,7 @@
         <v>1.72</v>
       </c>
       <c r="Q103">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R103">
         <v>1.26</v>
@@ -26729,10 +26729,10 @@
         <v>1.01</v>
       </c>
       <c r="V103">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W103">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X103">
         <v>1000</v>
@@ -27174,13 +27174,13 @@
         <v>4.7</v>
       </c>
       <c r="I105">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J105">
         <v>4</v>
       </c>
       <c r="K105">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L105">
         <v>1.01</v>
@@ -27195,31 +27195,31 @@
         <v>1.25</v>
       </c>
       <c r="P105">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q105">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="R105">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S105">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="T105">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="U105">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="V105">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W105">
         <v>2.24</v>
       </c>
       <c r="X105">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y105">
         <v>22</v>
@@ -27240,34 +27240,34 @@
         <v>21</v>
       </c>
       <c r="AE105">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF105">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG105">
         <v>10.5</v>
       </c>
       <c r="AH105">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI105">
         <v>660</v>
       </c>
       <c r="AJ105">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK105">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL105">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM105">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN105">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO105">
         <v>95</v>
@@ -27285,16 +27285,16 @@
         <v>1.01</v>
       </c>
       <c r="AT105">
+        <v>8.6</v>
+      </c>
+      <c r="AU105">
         <v>8.4</v>
-      </c>
-      <c r="AU105">
-        <v>8.199999999999999</v>
       </c>
       <c r="AV105">
         <v>17</v>
       </c>
       <c r="AW105">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AX105">
         <v>10</v>
@@ -27303,16 +27303,16 @@
         <v>9</v>
       </c>
       <c r="AZ105">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA105">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB105">
         <v>16.5</v>
       </c>
       <c r="BC105">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD105">
         <v>1.01</v>
@@ -27891,7 +27891,7 @@
         <v>471</v>
       </c>
       <c r="F108">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G108">
         <v>3.5</v>
@@ -27906,7 +27906,7 @@
         <v>2.88</v>
       </c>
       <c r="K108">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L108">
         <v>1.01</v>
@@ -27915,7 +27915,7 @@
         <v>1.06</v>
       </c>
       <c r="N108">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O108">
         <v>1.43</v>
@@ -27924,7 +27924,7 @@
         <v>1.55</v>
       </c>
       <c r="Q108">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="R108">
         <v>1.19</v>
@@ -28157,7 +28157,7 @@
         <v>1.01</v>
       </c>
       <c r="N109">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="O109">
         <v>1.24</v>
@@ -28399,7 +28399,7 @@
         <v>1.01</v>
       </c>
       <c r="N110">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O110">
         <v>1.4</v>
@@ -28408,7 +28408,7 @@
         <v>1.25</v>
       </c>
       <c r="Q110">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R110">
         <v>1.18</v>
@@ -28620,7 +28620,7 @@
         <v>2.58</v>
       </c>
       <c r="G111">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H111">
         <v>2.82</v>
@@ -28647,16 +28647,16 @@
         <v>1.55</v>
       </c>
       <c r="P111">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q111">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R111">
         <v>1.19</v>
       </c>
       <c r="S111">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="T111">
         <v>1.01</v>
@@ -28668,7 +28668,7 @@
         <v>1.39</v>
       </c>
       <c r="W111">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X111">
         <v>1000</v>
@@ -28889,7 +28889,7 @@
         <v>1.2</v>
       </c>
       <c r="P112">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q112">
         <v>1.2</v>
@@ -29104,7 +29104,7 @@
         <v>2.54</v>
       </c>
       <c r="G113">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="H113">
         <v>2.7</v>
@@ -29125,16 +29125,16 @@
         <v>1.01</v>
       </c>
       <c r="N113">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O113">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="P113">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q113">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R113">
         <v>1.21</v>
@@ -29152,7 +29152,7 @@
         <v>1.33</v>
       </c>
       <c r="W113">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X113">
         <v>1000</v>
@@ -29343,22 +29343,22 @@
         <v>477</v>
       </c>
       <c r="F114">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="G114">
-        <v>110</v>
+        <v>4.1</v>
       </c>
       <c r="H114">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="I114">
         <v>2.38</v>
       </c>
       <c r="J114">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="K114">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L114">
         <v>1.01</v>
@@ -29367,22 +29367,22 @@
         <v>1.02</v>
       </c>
       <c r="N114">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="O114">
         <v>1.39</v>
       </c>
       <c r="P114">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q114">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R114">
         <v>1.21</v>
       </c>
       <c r="S114">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="T114">
         <v>1.92</v>
@@ -29394,10 +29394,10 @@
         <v>1.76</v>
       </c>
       <c r="W114">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X114">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y114">
         <v>10</v>
@@ -29487,16 +29487,16 @@
         <v>4.4</v>
       </c>
       <c r="BB114">
+        <v>4.6</v>
+      </c>
+      <c r="BC114">
         <v>4.5</v>
-      </c>
-      <c r="BC114">
-        <v>4.4</v>
       </c>
       <c r="BD114">
         <v>4.5</v>
       </c>
       <c r="BE114">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF114">
         <v>4.5</v>
@@ -29591,13 +29591,13 @@
         <v>3.25</v>
       </c>
       <c r="H115">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I115">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J115">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K115">
         <v>3.9</v>
@@ -29618,28 +29618,28 @@
         <v>2.18</v>
       </c>
       <c r="Q115">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R115">
         <v>1.47</v>
       </c>
       <c r="S115">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T115">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U115">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V115">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W115">
         <v>1.44</v>
       </c>
       <c r="X115">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y115">
         <v>12.5</v>
@@ -29669,7 +29669,7 @@
         <v>14</v>
       </c>
       <c r="AH115">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI115">
         <v>34</v>
@@ -29690,10 +29690,10 @@
         <v>28</v>
       </c>
       <c r="AO115">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP115">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ115">
         <v>11</v>
@@ -29723,13 +29723,13 @@
         <v>12.5</v>
       </c>
       <c r="AZ115">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA115">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB115">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC115">
         <v>29</v>
@@ -29741,7 +29741,7 @@
         <v>60</v>
       </c>
       <c r="BF115">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG115">
         <v>13</v>
@@ -29827,7 +29827,7 @@
         <v>479</v>
       </c>
       <c r="F116">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G116">
         <v>1.3</v>
@@ -29836,7 +29836,7 @@
         <v>2.86</v>
       </c>
       <c r="I116">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J116">
         <v>6.8</v>
@@ -29875,7 +29875,7 @@
         <v>1.01</v>
       </c>
       <c r="V116">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W116">
         <v>2.78</v>
@@ -30072,7 +30072,7 @@
         <v>5.1</v>
       </c>
       <c r="G117">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H117">
         <v>1.8</v>
@@ -30081,7 +30081,7 @@
         <v>1.83</v>
       </c>
       <c r="J117">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K117">
         <v>3.95</v>
@@ -30093,7 +30093,7 @@
         <v>1.07</v>
       </c>
       <c r="N117">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O117">
         <v>1.32</v>
@@ -30120,7 +30120,7 @@
         <v>2.2</v>
       </c>
       <c r="W117">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X117">
         <v>15</v>
@@ -30171,7 +30171,7 @@
         <v>130</v>
       </c>
       <c r="AN117">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AO117">
         <v>12.5</v>
@@ -30213,7 +30213,7 @@
         <v>6.4</v>
       </c>
       <c r="BB117">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC117">
         <v>7</v>
@@ -30323,10 +30323,10 @@
         <v>1.87</v>
       </c>
       <c r="J118">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K118">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L118">
         <v>1.01</v>
@@ -30341,16 +30341,16 @@
         <v>1.33</v>
       </c>
       <c r="P118">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q118">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="R118">
         <v>1.26</v>
       </c>
       <c r="S118">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T118">
         <v>1.75</v>
@@ -30553,7 +30553,7 @@
         <v>482</v>
       </c>
       <c r="F119">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G119">
         <v>1.8</v>
@@ -30562,10 +30562,10 @@
         <v>5.1</v>
       </c>
       <c r="I119">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J119">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K119">
         <v>4.1</v>
@@ -30586,7 +30586,7 @@
         <v>1.92</v>
       </c>
       <c r="Q119">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R119">
         <v>1.35</v>
@@ -30595,16 +30595,16 @@
         <v>3.4</v>
       </c>
       <c r="T119">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U119">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="V119">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W119">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X119">
         <v>14.5</v>
@@ -30616,19 +30616,19 @@
         <v>42</v>
       </c>
       <c r="AA119">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB119">
         <v>8.6</v>
       </c>
       <c r="AC119">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD119">
         <v>21</v>
       </c>
       <c r="AE119">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF119">
         <v>11</v>
@@ -30646,7 +30646,7 @@
         <v>19</v>
       </c>
       <c r="AK119">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL119">
         <v>38</v>
@@ -30700,13 +30700,13 @@
         <v>15.5</v>
       </c>
       <c r="BC119">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD119">
         <v>10</v>
       </c>
       <c r="BE119">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF119">
         <v>10</v>
@@ -30819,22 +30819,22 @@
         <v>1.01</v>
       </c>
       <c r="N120">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O120">
         <v>1.29</v>
       </c>
       <c r="P120">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q120">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="R120">
         <v>1.18</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>2.66</v>
       </c>
       <c r="T120">
         <v>1.01</v>
@@ -31282,16 +31282,16 @@
         <v>1.86</v>
       </c>
       <c r="G122">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H122">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I122">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J122">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K122">
         <v>4.4</v>
@@ -31303,22 +31303,22 @@
         <v>1.01</v>
       </c>
       <c r="N122">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O122">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P122">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Q122">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="R122">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S122">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="T122">
         <v>1.01</v>
@@ -31327,10 +31327,10 @@
         <v>1.01</v>
       </c>
       <c r="V122">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W122">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="X122">
         <v>1000</v>
@@ -31524,7 +31524,7 @@
         <v>2.48</v>
       </c>
       <c r="G123">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H123">
         <v>2.7</v>
@@ -31542,7 +31542,7 @@
         <v>1.01</v>
       </c>
       <c r="M123">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N123">
         <v>3.6</v>
@@ -31572,7 +31572,7 @@
         <v>1.44</v>
       </c>
       <c r="W123">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X123">
         <v>1000</v>
@@ -31766,19 +31766,19 @@
         <v>1.19</v>
       </c>
       <c r="G124">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="H124">
         <v>18</v>
       </c>
       <c r="I124">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J124">
         <v>8.6</v>
       </c>
       <c r="K124">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L124">
         <v>1.01</v>
@@ -31787,34 +31787,34 @@
         <v>1.03</v>
       </c>
       <c r="N124">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O124">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P124">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q124">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="R124">
         <v>1.6</v>
       </c>
       <c r="S124">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T124">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="U124">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V124">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W124">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X124">
         <v>34</v>
@@ -31823,7 +31823,7 @@
         <v>65</v>
       </c>
       <c r="Z124">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AA124">
         <v>1000</v>
@@ -31841,7 +31841,7 @@
         <v>460</v>
       </c>
       <c r="AF124">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG124">
         <v>12.5</v>
@@ -31850,10 +31850,10 @@
         <v>55</v>
       </c>
       <c r="AI124">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AJ124">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AK124">
         <v>17</v>
@@ -31874,55 +31874,55 @@
         <v>20</v>
       </c>
       <c r="AQ124">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR124">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS124">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT124">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU124">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AV124">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW124">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX124">
         <v>6.4</v>
       </c>
       <c r="AY124">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ124">
-        <v>40</v>
+        <v>8.6</v>
       </c>
       <c r="BA124">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB124">
         <v>7.4</v>
       </c>
       <c r="BC124">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD124">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE124">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF124">
         <v>3.6</v>
       </c>
       <c r="BG124">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH124">
         <v>1000</v>
@@ -32005,7 +32005,7 @@
         <v>488</v>
       </c>
       <c r="F125">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G125">
         <v>4.1</v>
@@ -32014,7 +32014,7 @@
         <v>2.02</v>
       </c>
       <c r="I125">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J125">
         <v>3.65</v>
@@ -32029,19 +32029,19 @@
         <v>1.06</v>
       </c>
       <c r="N125">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="O125">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P125">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q125">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="R125">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S125">
         <v>2.88</v>
@@ -32053,7 +32053,7 @@
         <v>1.01</v>
       </c>
       <c r="V125">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W125">
         <v>1.32</v>
@@ -32113,16 +32113,16 @@
         <v>1000</v>
       </c>
       <c r="AP125">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ125">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR125">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS125">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT125">
         <v>10</v>
@@ -32131,7 +32131,7 @@
         <v>6.4</v>
       </c>
       <c r="AV125">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW125">
         <v>17</v>
@@ -32140,19 +32140,19 @@
         <v>18.5</v>
       </c>
       <c r="AY125">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ125">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA125">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB125">
         <v>40</v>
       </c>
       <c r="BC125">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD125">
         <v>36</v>
@@ -32250,19 +32250,19 @@
         <v>1.8</v>
       </c>
       <c r="G126">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H126">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I126">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J126">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K126">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L126">
         <v>1.01</v>
@@ -32271,7 +32271,7 @@
         <v>1.09</v>
       </c>
       <c r="N126">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O126">
         <v>1.38</v>
@@ -32280,25 +32280,25 @@
         <v>1.84</v>
       </c>
       <c r="Q126">
+        <v>2.08</v>
+      </c>
+      <c r="R126">
+        <v>1.3</v>
+      </c>
+      <c r="S126">
+        <v>3.9</v>
+      </c>
+      <c r="T126">
+        <v>1.95</v>
+      </c>
+      <c r="U126">
+        <v>1.87</v>
+      </c>
+      <c r="V126">
+        <v>1.22</v>
+      </c>
+      <c r="W126">
         <v>2.1</v>
-      </c>
-      <c r="R126">
-        <v>1.28</v>
-      </c>
-      <c r="S126">
-        <v>3.95</v>
-      </c>
-      <c r="T126">
-        <v>1.97</v>
-      </c>
-      <c r="U126">
-        <v>1.85</v>
-      </c>
-      <c r="V126">
-        <v>1.2</v>
-      </c>
-      <c r="W126">
-        <v>2.12</v>
       </c>
       <c r="X126">
         <v>14</v>
@@ -32322,7 +32322,7 @@
         <v>23</v>
       </c>
       <c r="AE126">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF126">
         <v>11</v>
@@ -32334,7 +32334,7 @@
         <v>24</v>
       </c>
       <c r="AI126">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ126">
         <v>21</v>
@@ -32352,7 +32352,7 @@
         <v>15</v>
       </c>
       <c r="AO126">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP126">
         <v>10.5</v>
@@ -32361,10 +32361,10 @@
         <v>13.5</v>
       </c>
       <c r="AR126">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS126">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT126">
         <v>6.4</v>
@@ -32373,7 +32373,7 @@
         <v>7.4</v>
       </c>
       <c r="AV126">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW126">
         <v>8.6</v>
@@ -32388,7 +32388,7 @@
         <v>6.8</v>
       </c>
       <c r="BA126">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB126">
         <v>16.5</v>
@@ -32397,16 +32397,16 @@
         <v>6.6</v>
       </c>
       <c r="BD126">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE126">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF126">
         <v>11</v>
       </c>
       <c r="BG126">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH126">
         <v>1000</v>
@@ -32489,7 +32489,7 @@
         <v>490</v>
       </c>
       <c r="F127">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G127">
         <v>5.2</v>
@@ -32498,7 +32498,7 @@
         <v>1.72</v>
       </c>
       <c r="I127">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="J127">
         <v>4.3</v>
@@ -32513,7 +32513,7 @@
         <v>1.03</v>
       </c>
       <c r="N127">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O127">
         <v>1.16</v>
@@ -32522,22 +32522,22 @@
         <v>2.84</v>
       </c>
       <c r="Q127">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="R127">
         <v>1.73</v>
       </c>
       <c r="S127">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T127">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U127">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V127">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="W127">
         <v>1.23</v>
@@ -32549,22 +32549,22 @@
         <v>14.5</v>
       </c>
       <c r="Z127">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA127">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB127">
         <v>29</v>
       </c>
       <c r="AC127">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD127">
         <v>11</v>
       </c>
       <c r="AE127">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AF127">
         <v>48</v>
@@ -32579,76 +32579,76 @@
         <v>25</v>
       </c>
       <c r="AJ127">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK127">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL127">
         <v>48</v>
       </c>
       <c r="AM127">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN127">
         <v>38</v>
       </c>
       <c r="AO127">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP127">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="AQ127">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR127">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AS127">
         <v>15.5</v>
       </c>
       <c r="AT127">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="AU127">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV127">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW127">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX127">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AY127">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ127">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA127">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB127">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BC127">
         <v>40</v>
       </c>
       <c r="BD127">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BE127">
-        <v>8.6</v>
+        <v>40</v>
       </c>
       <c r="BF127">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BG127">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH127">
         <v>1000</v>
@@ -32731,22 +32731,22 @@
         <v>491</v>
       </c>
       <c r="F128">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="G128">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="H128">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="I128">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="J128">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K128">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L128">
         <v>1.01</v>
@@ -32764,13 +32764,13 @@
         <v>1.63</v>
       </c>
       <c r="Q128">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R128">
         <v>1.07</v>
       </c>
       <c r="S128">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T128">
         <v>1.01</v>
@@ -32779,10 +32779,10 @@
         <v>1.01</v>
       </c>
       <c r="V128">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="W128">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X128">
         <v>1000</v>
@@ -33239,22 +33239,22 @@
         <v>1.01</v>
       </c>
       <c r="N130">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O130">
         <v>1.3</v>
       </c>
       <c r="P130">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q130">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R130">
         <v>1.18</v>
       </c>
       <c r="S130">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T130">
         <v>1.01</v>
@@ -33708,10 +33708,10 @@
         <v>5</v>
       </c>
       <c r="I132">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="J132">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K132">
         <v>10.5</v>
@@ -33747,7 +33747,7 @@
         <v>1.01</v>
       </c>
       <c r="V132">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W132">
         <v>2.5</v>
@@ -33944,7 +33944,7 @@
         <v>2.26</v>
       </c>
       <c r="G133">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H133">
         <v>3.45</v>
@@ -33965,22 +33965,22 @@
         <v>1.01</v>
       </c>
       <c r="N133">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O133">
         <v>1.42</v>
       </c>
       <c r="P133">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q133">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R133">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="S133">
-        <v>4.1</v>
+        <v>2.24</v>
       </c>
       <c r="T133">
         <v>1.01</v>
@@ -33992,7 +33992,7 @@
         <v>1.32</v>
       </c>
       <c r="W133">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X133">
         <v>1000</v>
@@ -34183,46 +34183,46 @@
         <v>497</v>
       </c>
       <c r="F134">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G134">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="H134">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="I134">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="J134">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K134">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="L134">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M134">
         <v>1.05</v>
       </c>
       <c r="N134">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="O134">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="P134">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Q134">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="R134">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S134">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="T134">
         <v>1.01</v>
@@ -34231,10 +34231,10 @@
         <v>1.01</v>
       </c>
       <c r="V134">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="W134">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X134">
         <v>1000</v>
@@ -34306,7 +34306,7 @@
         <v>1.01</v>
       </c>
       <c r="AU134">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV134">
         <v>1.01</v>
@@ -34321,7 +34321,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ134">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA134">
         <v>1.01</v>
@@ -34431,13 +34431,13 @@
         <v>1000</v>
       </c>
       <c r="H135">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I135">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J135">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="K135">
         <v>2.94</v>
@@ -34449,16 +34449,16 @@
         <v>1.01</v>
       </c>
       <c r="N135">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="O135">
         <v>1.01</v>
       </c>
       <c r="P135">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q135">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="R135">
         <v>1.12</v>
@@ -34479,7 +34479,7 @@
         <v>1.01</v>
       </c>
       <c r="X135">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="Y135">
         <v>1000</v>
@@ -34536,55 +34536,55 @@
         <v>5</v>
       </c>
       <c r="AQ135">
-        <v>5.7</v>
+        <v>1.19</v>
       </c>
       <c r="AR135">
-        <v>14</v>
+        <v>1.19</v>
       </c>
       <c r="AS135">
-        <v>42</v>
+        <v>1.19</v>
       </c>
       <c r="AT135">
-        <v>5.7</v>
+        <v>1.19</v>
       </c>
       <c r="AU135">
-        <v>5.8</v>
+        <v>1.19</v>
       </c>
       <c r="AV135">
-        <v>14</v>
+        <v>1.19</v>
       </c>
       <c r="AW135">
-        <v>46</v>
+        <v>1.19</v>
       </c>
       <c r="AX135">
-        <v>13.5</v>
+        <v>1.19</v>
       </c>
       <c r="AY135">
-        <v>13.5</v>
+        <v>1.19</v>
       </c>
       <c r="AZ135">
-        <v>26</v>
+        <v>1.19</v>
       </c>
       <c r="BA135">
-        <v>90</v>
+        <v>1.19</v>
       </c>
       <c r="BB135">
-        <v>42</v>
+        <v>1.19</v>
       </c>
       <c r="BC135">
-        <v>44</v>
+        <v>1.19</v>
       </c>
       <c r="BD135">
-        <v>95</v>
+        <v>1.19</v>
       </c>
       <c r="BE135">
-        <v>100</v>
+        <v>1.19</v>
       </c>
       <c r="BF135">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BG135">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BH135">
         <v>1000</v>
@@ -34694,7 +34694,7 @@
         <v>1.24</v>
       </c>
       <c r="O136">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P136">
         <v>1.24</v>
@@ -34948,7 +34948,7 @@
         <v>1.12</v>
       </c>
       <c r="S137">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T137">
         <v>1.01</v>
@@ -35423,7 +35423,7 @@
         <v>0</v>
       </c>
       <c r="P139">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="Q139">
         <v>1.86</v>
@@ -35880,16 +35880,16 @@
         <v>2.46</v>
       </c>
       <c r="G141">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="H141">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="I141">
         <v>3.15</v>
       </c>
       <c r="J141">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="K141">
         <v>950</v>
@@ -35901,19 +35901,19 @@
         <v>1.06</v>
       </c>
       <c r="N141">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O141">
         <v>1.35</v>
       </c>
       <c r="P141">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q141">
         <v>1.86</v>
       </c>
       <c r="R141">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S141">
         <v>3.1</v>
@@ -35928,7 +35928,7 @@
         <v>1.46</v>
       </c>
       <c r="W141">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="X141">
         <v>1000</v>
@@ -36612,7 +36612,7 @@
         <v>2.46</v>
       </c>
       <c r="I144">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J144">
         <v>3</v>
@@ -36651,7 +36651,7 @@
         <v>1.01</v>
       </c>
       <c r="V144">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W144">
         <v>1.48</v>
@@ -37111,7 +37111,7 @@
         <v>1.01</v>
       </c>
       <c r="N146">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O146">
         <v>1.4</v>
@@ -37126,7 +37126,7 @@
         <v>1.18</v>
       </c>
       <c r="S146">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="T146">
         <v>1.01</v>
@@ -37335,7 +37335,7 @@
         <v>1.52</v>
       </c>
       <c r="H147">
-        <v>2.68</v>
+        <v>4.9</v>
       </c>
       <c r="I147">
         <v>20</v>
@@ -37344,7 +37344,7 @@
         <v>4.8</v>
       </c>
       <c r="K147">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L147">
         <v>1.01</v>
@@ -37356,7 +37356,7 @@
         <v>3.85</v>
       </c>
       <c r="O147">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P147">
         <v>1.99</v>
@@ -37622,7 +37622,7 @@
         <v>1.32</v>
       </c>
       <c r="W148">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="X148">
         <v>1000</v>
@@ -37825,7 +37825,7 @@
         <v>4.2</v>
       </c>
       <c r="J149">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="K149">
         <v>5</v>
@@ -38064,10 +38064,10 @@
         <v>2.88</v>
       </c>
       <c r="I150">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="J150">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="K150">
         <v>3.6</v>
@@ -38103,7 +38103,7 @@
         <v>1.01</v>
       </c>
       <c r="V150">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W150">
         <v>1.52</v>
@@ -38539,7 +38539,7 @@
         <v>515</v>
       </c>
       <c r="F152">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="G152">
         <v>2.22</v>
@@ -38554,13 +38554,13 @@
         <v>1.04</v>
       </c>
       <c r="K152">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="L152">
         <v>1.01</v>
       </c>
       <c r="M152">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N152">
         <v>2.58</v>
@@ -38578,7 +38578,7 @@
         <v>1.17</v>
       </c>
       <c r="S152">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="T152">
         <v>1.01</v>
@@ -38784,13 +38784,13 @@
         <v>2.46</v>
       </c>
       <c r="G153">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H153">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="I153">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J153">
         <v>3.4</v>
@@ -38829,10 +38829,10 @@
         <v>2</v>
       </c>
       <c r="V153">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W153">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X153">
         <v>1000</v>
@@ -39044,16 +39044,16 @@
         <v>1.01</v>
       </c>
       <c r="M154">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N154">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O154">
         <v>1.31</v>
       </c>
       <c r="P154">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q154">
         <v>1.91</v>
@@ -39065,7 +39065,7 @@
         <v>3.3</v>
       </c>
       <c r="T154">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U154">
         <v>1.92</v>
@@ -39268,7 +39268,7 @@
         <v>1.57</v>
       </c>
       <c r="G155">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H155">
         <v>6.8</v>
@@ -39307,16 +39307,16 @@
         <v>3.5</v>
       </c>
       <c r="T155">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U155">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V155">
         <v>1.14</v>
       </c>
       <c r="W155">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="X155">
         <v>14.5</v>
@@ -39510,13 +39510,13 @@
         <v>1.04</v>
       </c>
       <c r="G156">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H156">
         <v>1.04</v>
       </c>
       <c r="I156">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J156">
         <v>1.04</v>
@@ -39546,7 +39546,7 @@
         <v>1.18</v>
       </c>
       <c r="S156">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T156">
         <v>1.01</v>
@@ -39749,22 +39749,22 @@
         <v>520</v>
       </c>
       <c r="F157">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G157">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H157">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="I157">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J157">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="K157">
-        <v>180</v>
+        <v>3.5</v>
       </c>
       <c r="L157">
         <v>1.01</v>
@@ -39773,22 +39773,22 @@
         <v>1.01</v>
       </c>
       <c r="N157">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="O157">
         <v>1.02</v>
       </c>
       <c r="P157">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q157">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="R157">
         <v>1.17</v>
       </c>
       <c r="S157">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="T157">
         <v>1.01</v>
@@ -39797,10 +39797,10 @@
         <v>1.01</v>
       </c>
       <c r="V157">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W157">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X157">
         <v>1000</v>
@@ -39991,10 +39991,10 @@
         <v>521</v>
       </c>
       <c r="F158">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="G158">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="H158">
         <v>32</v>
@@ -40003,13 +40003,13 @@
         <v>34</v>
       </c>
       <c r="J158">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="K158">
         <v>13</v>
       </c>
       <c r="L158">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M158">
         <v>1.02</v>
@@ -40024,7 +40024,7 @@
         <v>2.92</v>
       </c>
       <c r="Q158">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R158">
         <v>1.76</v>
@@ -40033,16 +40033,16 @@
         <v>2.1</v>
       </c>
       <c r="T158">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U158">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V158">
         <v>1.03</v>
       </c>
       <c r="W158">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X158">
         <v>48</v>
@@ -40078,7 +40078,7 @@
         <v>100</v>
       </c>
       <c r="AI158">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="AJ158">
         <v>8</v>
@@ -40114,7 +40114,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU158">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="AV158">
         <v>6.6</v>
@@ -40126,7 +40126,7 @@
         <v>6.2</v>
       </c>
       <c r="AY158">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ158">
         <v>6.4</v>
@@ -40147,46 +40147,46 @@
         <v>7</v>
       </c>
       <c r="BF158">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BG158">
         <v>7</v>
       </c>
       <c r="BH158">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BI158">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BJ158">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BK158">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BL158">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="BM158">
         <v>21</v>
       </c>
       <c r="BN158">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO158">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BP158">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BQ158">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR158">
         <v>32</v>
       </c>
       <c r="BS158">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BT158">
         <v>30</v>
@@ -40195,13 +40195,13 @@
         <v>19.5</v>
       </c>
       <c r="BV158">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="BW158">
         <v>21</v>
       </c>
       <c r="BX158">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="BY158">
         <v>21</v>
@@ -40233,13 +40233,13 @@
         <v>522</v>
       </c>
       <c r="F159">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="G159">
         <v>5.7</v>
       </c>
       <c r="H159">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I159">
         <v>1.72</v>
@@ -40248,7 +40248,7 @@
         <v>4.2</v>
       </c>
       <c r="K159">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L159">
         <v>1.01</v>
@@ -40257,7 +40257,7 @@
         <v>1.07</v>
       </c>
       <c r="N159">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="O159">
         <v>1.32</v>
@@ -40266,7 +40266,7 @@
         <v>1.95</v>
       </c>
       <c r="Q159">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="R159">
         <v>1.38</v>
@@ -40275,13 +40275,13 @@
         <v>3</v>
       </c>
       <c r="T159">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U159">
         <v>1.76</v>
       </c>
       <c r="V159">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W159">
         <v>1.21</v>
@@ -40308,7 +40308,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE159">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF159">
         <v>46</v>
@@ -40332,10 +40332,10 @@
         <v>95</v>
       </c>
       <c r="AM159">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN159">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO159">
         <v>12</v>
@@ -40374,19 +40374,19 @@
         <v>19</v>
       </c>
       <c r="BA159">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BB159">
+        <v>9</v>
+      </c>
+      <c r="BC159">
+        <v>10</v>
+      </c>
+      <c r="BD159">
+        <v>10</v>
+      </c>
+      <c r="BE159">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BC159">
-        <v>65</v>
-      </c>
-      <c r="BD159">
-        <v>65</v>
-      </c>
-      <c r="BE159">
-        <v>10.5</v>
       </c>
       <c r="BF159">
         <v>8.6</v>
@@ -40475,7 +40475,7 @@
         <v>523</v>
       </c>
       <c r="F160">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G160">
         <v>2.08</v>
@@ -40484,7 +40484,7 @@
         <v>4.2</v>
       </c>
       <c r="I160">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J160">
         <v>3.5</v>
@@ -40508,19 +40508,19 @@
         <v>1.84</v>
       </c>
       <c r="Q160">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="R160">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S160">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="T160">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U160">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V160">
         <v>1.27</v>
@@ -40535,7 +40535,7 @@
         <v>15.5</v>
       </c>
       <c r="Z160">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA160">
         <v>110</v>
@@ -40592,7 +40592,7 @@
         <v>5</v>
       </c>
       <c r="AS160">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT160">
         <v>7.4</v>
@@ -40604,7 +40604,7 @@
         <v>15.5</v>
       </c>
       <c r="AW160">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX160">
         <v>11</v>
@@ -40625,10 +40625,10 @@
         <v>19.5</v>
       </c>
       <c r="BD160">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE160">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF160">
         <v>12</v>
@@ -40959,22 +40959,22 @@
         <v>525</v>
       </c>
       <c r="F162">
+        <v>1.26</v>
+      </c>
+      <c r="G162">
+        <v>1.4</v>
+      </c>
+      <c r="H162">
         <v>1.04</v>
       </c>
-      <c r="G162">
-        <v>2.22</v>
-      </c>
-      <c r="H162">
-        <v>1.83</v>
-      </c>
       <c r="I162">
         <v>1000</v>
       </c>
       <c r="J162">
-        <v>1.86</v>
+        <v>1.06</v>
       </c>
       <c r="K162">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L162">
         <v>1.01</v>
@@ -41007,7 +41007,7 @@
         <v>1.01</v>
       </c>
       <c r="V162">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W162">
         <v>1.83</v>
@@ -41201,10 +41201,10 @@
         <v>526</v>
       </c>
       <c r="F163">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G163">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H163">
         <v>3.55</v>
@@ -41225,22 +41225,22 @@
         <v>1.01</v>
       </c>
       <c r="N163">
-        <v>1.51</v>
+        <v>2.6</v>
       </c>
       <c r="O163">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P163">
         <v>1.51</v>
       </c>
       <c r="Q163">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R163">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S163">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="T163">
         <v>2.08</v>
@@ -41249,10 +41249,10 @@
         <v>1.01</v>
       </c>
       <c r="V163">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W163">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X163">
         <v>9.199999999999999</v>
@@ -41443,22 +41443,22 @@
         <v>527</v>
       </c>
       <c r="F164">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="G164">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="H164">
-        <v>5.5</v>
+        <v>2.26</v>
       </c>
       <c r="I164">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="J164">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K164">
-        <v>3.5</v>
+        <v>100</v>
       </c>
       <c r="L164">
         <v>1.01</v>
@@ -41491,10 +41491,10 @@
         <v>1.47</v>
       </c>
       <c r="V164">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W164">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X164">
         <v>1000</v>
@@ -41939,7 +41939,7 @@
         <v>110</v>
       </c>
       <c r="J166">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="K166">
         <v>3.95</v>
@@ -41972,7 +41972,7 @@
         <v>1.01</v>
       </c>
       <c r="U166">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V166">
         <v>1.34</v>
@@ -42172,7 +42172,7 @@
         <v>2.42</v>
       </c>
       <c r="G167">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="H167">
         <v>3.15</v>
@@ -42193,10 +42193,10 @@
         <v>1.1</v>
       </c>
       <c r="N167">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="O167">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="P167">
         <v>1.45</v>
@@ -42220,7 +42220,7 @@
         <v>1.37</v>
       </c>
       <c r="W167">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X167">
         <v>1000</v>
@@ -42653,19 +42653,19 @@
         <v>532</v>
       </c>
       <c r="F169">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="G169">
         <v>1000</v>
       </c>
       <c r="H169">
-        <v>3.6</v>
+        <v>1.41</v>
       </c>
       <c r="I169">
         <v>1000</v>
       </c>
       <c r="J169">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="K169">
         <v>3.5</v>
@@ -42680,19 +42680,19 @@
         <v>1.29</v>
       </c>
       <c r="O169">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P169">
         <v>1.27</v>
       </c>
       <c r="Q169">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R169">
         <v>1.27</v>
       </c>
       <c r="S169">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T169">
         <v>1.01</v>
@@ -42713,106 +42713,106 @@
         <v>1000</v>
       </c>
       <c r="Z169">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA169">
         <v>1000</v>
       </c>
       <c r="AB169">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC169">
+        <v>1000</v>
+      </c>
+      <c r="AD169">
+        <v>1000</v>
+      </c>
+      <c r="AE169">
+        <v>1000</v>
+      </c>
+      <c r="AF169">
+        <v>1000</v>
+      </c>
+      <c r="AG169">
+        <v>1000</v>
+      </c>
+      <c r="AH169">
+        <v>1000</v>
+      </c>
+      <c r="AI169">
+        <v>1000</v>
+      </c>
+      <c r="AJ169">
+        <v>1000</v>
+      </c>
+      <c r="AK169">
+        <v>1000</v>
+      </c>
+      <c r="AL169">
+        <v>1000</v>
+      </c>
+      <c r="AM169">
+        <v>1000</v>
+      </c>
+      <c r="AN169">
+        <v>1000</v>
+      </c>
+      <c r="AO169">
+        <v>1000</v>
+      </c>
+      <c r="AP169">
         <v>9.6</v>
       </c>
-      <c r="AD169">
-        <v>20</v>
-      </c>
-      <c r="AE169">
-        <v>1000</v>
-      </c>
-      <c r="AF169">
-        <v>17.5</v>
-      </c>
-      <c r="AG169">
-        <v>1000</v>
-      </c>
-      <c r="AH169">
-        <v>1000</v>
-      </c>
-      <c r="AI169">
-        <v>80</v>
-      </c>
-      <c r="AJ169">
-        <v>38</v>
-      </c>
-      <c r="AK169">
-        <v>34</v>
-      </c>
-      <c r="AL169">
-        <v>1000</v>
-      </c>
-      <c r="AM169">
-        <v>1000</v>
-      </c>
-      <c r="AN169">
-        <v>1000</v>
-      </c>
-      <c r="AO169">
-        <v>1000</v>
-      </c>
-      <c r="AP169">
-        <v>1.66</v>
-      </c>
       <c r="AQ169">
-        <v>1.66</v>
+        <v>9.4</v>
       </c>
       <c r="AR169">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AS169">
-        <v>1.66</v>
+        <v>44</v>
       </c>
       <c r="AT169">
         <v>7.4</v>
       </c>
       <c r="AU169">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AV169">
+        <v>1.54</v>
+      </c>
+      <c r="AW169">
+        <v>32</v>
+      </c>
+      <c r="AX169">
         <v>1.53</v>
       </c>
-      <c r="AW169">
-        <v>1.66</v>
-      </c>
-      <c r="AX169">
-        <v>1.52</v>
-      </c>
       <c r="AY169">
-        <v>1.66</v>
+        <v>9</v>
       </c>
       <c r="AZ169">
-        <v>1.66</v>
+        <v>16</v>
       </c>
       <c r="BA169">
-        <v>1.63</v>
+        <v>40</v>
       </c>
       <c r="BB169">
+        <v>1.6</v>
+      </c>
+      <c r="BC169">
         <v>1.59</v>
       </c>
-      <c r="BC169">
-        <v>1.58</v>
-      </c>
       <c r="BD169">
-        <v>1.66</v>
+        <v>32</v>
       </c>
       <c r="BE169">
-        <v>1.66</v>
+        <v>80</v>
       </c>
       <c r="BF169">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BG169">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BH169">
         <v>1000</v>
@@ -42916,10 +42916,10 @@
         <v>1.4</v>
       </c>
       <c r="M170">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N170">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O170">
         <v>1.42</v>
@@ -42928,7 +42928,7 @@
         <v>1.68</v>
       </c>
       <c r="Q170">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R170">
         <v>1.25</v>
@@ -42937,10 +42937,10 @@
         <v>4.3</v>
       </c>
       <c r="T170">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="U170">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V170">
         <v>1.32</v>
@@ -43173,7 +43173,7 @@
         <v>2.38</v>
       </c>
       <c r="R171">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S171">
         <v>2.38</v>
@@ -43621,7 +43621,7 @@
         <v>536</v>
       </c>
       <c r="F173">
-        <v>4.5</v>
+        <v>1.97</v>
       </c>
       <c r="G173">
         <v>5.2</v>
@@ -43902,7 +43902,7 @@
         <v>1.18</v>
       </c>
       <c r="S174">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="T174">
         <v>1.01</v>
@@ -44105,7 +44105,7 @@
         <v>538</v>
       </c>
       <c r="F175">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G175">
         <v>1.64</v>
@@ -44114,7 +44114,7 @@
         <v>6.6</v>
       </c>
       <c r="I175">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J175">
         <v>4.1</v>
@@ -44126,7 +44126,7 @@
         <v>1.01</v>
       </c>
       <c r="M175">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N175">
         <v>1.93</v>
@@ -44135,10 +44135,10 @@
         <v>1.29</v>
       </c>
       <c r="P175">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q175">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R175">
         <v>1.33</v>
@@ -44153,7 +44153,7 @@
         <v>1.01</v>
       </c>
       <c r="V175">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W175">
         <v>2.56</v>
@@ -44347,22 +44347,22 @@
         <v>539</v>
       </c>
       <c r="F176">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G176">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H176">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I176">
         <v>17</v>
       </c>
       <c r="J176">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K176">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L176">
         <v>1.01</v>
@@ -44380,7 +44380,7 @@
         <v>2.36</v>
       </c>
       <c r="Q176">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R176">
         <v>1.53</v>
@@ -44389,61 +44389,61 @@
         <v>2.58</v>
       </c>
       <c r="T176">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U176">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V176">
         <v>1.06</v>
       </c>
       <c r="W176">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X176">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y176">
         <v>46</v>
       </c>
       <c r="Z176">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AA176">
-        <v>1000</v>
+        <v>860</v>
       </c>
       <c r="AB176">
         <v>9.199999999999999</v>
       </c>
       <c r="AC176">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD176">
         <v>60</v>
       </c>
       <c r="AE176">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AF176">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG176">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH176">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI176">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AJ176">
         <v>9.4</v>
       </c>
       <c r="AK176">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL176">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM176">
         <v>270</v>
@@ -44452,43 +44452,43 @@
         <v>4.7</v>
       </c>
       <c r="AO176">
-        <v>540</v>
+        <v>430</v>
       </c>
       <c r="AP176">
         <v>19.5</v>
       </c>
       <c r="AQ176">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AR176">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS176">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT176">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU176">
         <v>13</v>
       </c>
       <c r="AV176">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="AW176">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AX176">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY176">
         <v>10</v>
       </c>
       <c r="AZ176">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BA176">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB176">
         <v>8</v>
@@ -44497,16 +44497,16 @@
         <v>12.5</v>
       </c>
       <c r="BD176">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE176">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF176">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BG176">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BH176">
         <v>1000</v>
@@ -44834,7 +44834,7 @@
         <v>2.02</v>
       </c>
       <c r="G178">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H178">
         <v>3.65</v>
@@ -44843,7 +44843,7 @@
         <v>5.4</v>
       </c>
       <c r="J178">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="K178">
         <v>3.3</v>
@@ -44879,10 +44879,10 @@
         <v>1.01</v>
       </c>
       <c r="V178">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W178">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X178">
         <v>11.5</v>
@@ -45076,13 +45076,13 @@
         <v>1.04</v>
       </c>
       <c r="G179">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H179">
         <v>1.04</v>
       </c>
       <c r="I179">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J179">
         <v>1.04</v>
